--- a/카드_아키타입/04_팩·마스크·패드.xlsx
+++ b/카드_아키타입/04_팩·마스크·패드.xlsx
@@ -1831,7 +1831,7 @@
       <row>130</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="790575"/>
+    <ext cx="1047750" cy="781050"/>
     <pic>
       <nvPicPr>
         <cNvPr id="66" name="Image 66" descr="Picture"/>

--- a/카드_아키타입/04_팩·마스크·패드.xlsx
+++ b/카드_아키타입/04_팩·마스크·패드.xlsx
@@ -328,8 +328,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>1085850</rowOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -353,8 +353,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>13</row>
-      <rowOff>1085850</rowOff>
+      <row>14</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -378,7 +378,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -403,7 +403,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -428,7 +428,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -453,7 +453,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -478,7 +478,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>27</row>
+      <row>28</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -503,8 +503,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>1085850</rowOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -528,8 +528,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>27</row>
-      <rowOff>1085850</rowOff>
+      <row>29</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -553,7 +553,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -578,7 +578,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>41</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -603,7 +603,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>41</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -628,7 +628,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>41</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -653,7 +653,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>41</row>
+      <row>43</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -678,8 +678,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>41</row>
-      <rowOff>1085850</rowOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -703,8 +703,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>41</row>
-      <rowOff>1085850</rowOff>
+      <row>44</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -728,7 +728,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -753,7 +753,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>56</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -778,7 +778,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>56</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -803,7 +803,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>56</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -828,7 +828,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>56</row>
+      <row>59</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -853,8 +853,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>56</row>
-      <rowOff>1085850</rowOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -878,8 +878,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>56</row>
-      <rowOff>1085850</rowOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -903,8 +903,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>56</row>
-      <rowOff>1085850</rowOff>
+      <row>60</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -928,7 +928,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -953,7 +953,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>71</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="885825"/>
@@ -978,7 +978,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>71</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="476250"/>
@@ -1003,7 +1003,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>71</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -1028,7 +1028,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>71</row>
+      <row>75</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -1053,8 +1053,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>71</row>
-      <rowOff>1085850</rowOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1078,8 +1078,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>71</row>
-      <rowOff>1085850</rowOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1103,8 +1103,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>71</row>
-      <rowOff>1085850</rowOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1128,8 +1128,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>71</row>
-      <rowOff>1085850</rowOff>
+      <row>76</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1153,7 +1153,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>88</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -1178,7 +1178,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>88</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1009650" cy="1047750"/>
@@ -1203,7 +1203,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>88</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="276225"/>
@@ -1228,7 +1228,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>88</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -1253,7 +1253,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>88</row>
+      <row>93</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -1278,8 +1278,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>1085850</rowOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1303,8 +1303,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>88</row>
-      <rowOff>1085850</rowOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1328,8 +1328,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>88</row>
-      <rowOff>1085850</rowOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1353,8 +1353,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>88</row>
-      <rowOff>1085850</rowOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1378,8 +1378,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>88</row>
-      <rowOff>1085850</rowOff>
+      <row>94</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1403,8 +1403,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>88</row>
-      <rowOff>2171700</rowOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1428,8 +1428,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>88</row>
-      <rowOff>2171700</rowOff>
+      <row>95</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -1453,7 +1453,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1478,7 +1478,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>101</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1503,7 +1503,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>101</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1528,7 +1528,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>101</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1553,7 +1553,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>101</row>
+      <row>108</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1578,8 +1578,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>101</row>
-      <rowOff>1085850</rowOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1603,8 +1603,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>101</row>
-      <rowOff>1085850</rowOff>
+      <row>109</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1628,7 +1628,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>114</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="876300" cy="1047750"/>
@@ -1653,7 +1653,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>114</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1678,7 +1678,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>114</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1703,7 +1703,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>114</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1728,7 +1728,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>114</row>
+      <row>122</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -1753,8 +1753,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>114</row>
-      <rowOff>1085850</rowOff>
+      <row>123</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1778,8 +1778,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>114</row>
-      <rowOff>1085850</rowOff>
+      <row>123</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -1803,7 +1803,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>130</row>
+      <row>139</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -1828,7 +1828,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>130</row>
+      <row>139</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="781050"/>
@@ -1853,7 +1853,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>130</row>
+      <row>139</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -1878,7 +1878,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>130</row>
+      <row>139</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -1903,7 +1903,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>130</row>
+      <row>139</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
@@ -1928,8 +1928,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>130</row>
-      <rowOff>1085850</rowOff>
+      <row>140</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
     <pic>
@@ -1953,8 +1953,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>130</row>
-      <rowOff>1085850</rowOff>
+      <row>140</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="990600"/>
     <pic>
@@ -1978,8 +1978,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>130</row>
-      <rowOff>1085850</rowOff>
+      <row>140</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="942975"/>
     <pic>
@@ -2003,7 +2003,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>144</row>
+      <row>154</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -2028,7 +2028,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>144</row>
+      <row>154</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2053,7 +2053,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>144</row>
+      <row>154</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2078,7 +2078,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>144</row>
+      <row>154</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2103,7 +2103,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>144</row>
+      <row>154</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2128,8 +2128,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>144</row>
-      <rowOff>1085850</rowOff>
+      <row>155</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2153,8 +2153,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>144</row>
-      <rowOff>1085850</rowOff>
+      <row>155</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2178,7 +2178,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>159</row>
+      <row>170</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -2203,7 +2203,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>159</row>
+      <row>170</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2228,7 +2228,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>159</row>
+      <row>170</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2253,7 +2253,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>159</row>
+      <row>170</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2278,7 +2278,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>159</row>
+      <row>170</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2303,8 +2303,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>159</row>
-      <rowOff>1085850</rowOff>
+      <row>171</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2328,8 +2328,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>159</row>
-      <rowOff>1085850</rowOff>
+      <row>171</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2353,7 +2353,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>173</row>
+      <row>185</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -2378,7 +2378,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>173</row>
+      <row>185</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -2403,7 +2403,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>173</row>
+      <row>185</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2428,7 +2428,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>173</row>
+      <row>185</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2453,7 +2453,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>173</row>
+      <row>185</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -2478,8 +2478,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>173</row>
-      <rowOff>1085850</rowOff>
+      <row>186</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2503,8 +2503,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>173</row>
-      <rowOff>1085850</rowOff>
+      <row>186</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -2514,181 +2514,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId93"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>187</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="9525" cy="9525"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="94" name="Image 94" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId94"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>187</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="695325" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="95" name="Image 95" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId95"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>187</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="96" name="Image 96" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId96"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>3257550</colOff>
-      <row>187</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="97" name="Image 97" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId97"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>4343400</colOff>
-      <row>187</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="98" name="Image 98" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId98"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>187</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="99" name="Image 99" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId99"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>187</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1000125"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="100" name="Image 100" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId100"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2706,14 +2531,14 @@
       <row>200</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="101" name="Image 101" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId101"/>
+    <ext cx="9525" cy="9525"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="94" name="Image 94" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId94"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2731,14 +2556,14 @@
       <row>200</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="102" name="Image 102" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId102"/>
+    <ext cx="695325" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="95" name="Image 95" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId95"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2756,14 +2581,14 @@
       <row>200</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="103" name="Image 103" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId103"/>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="96" name="Image 96" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId96"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2781,14 +2606,14 @@
       <row>200</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="104" name="Image 104" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId104"/>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="97" name="Image 97" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId97"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -2806,9 +2631,184 @@
       <row>200</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="98" name="Image 98" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId98"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>201</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="99" name="Image 99" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId99"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>201</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1000125"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="100" name="Image 100" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId100"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>214</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
       <nvPicPr>
+        <cNvPr id="101" name="Image 101" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId101"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>214</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="102" name="Image 102" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId102"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>214</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="103" name="Image 103" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId103"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>3257550</colOff>
+      <row>214</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="104" name="Image 104" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId104"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>4343400</colOff>
+      <row>214</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
         <cNvPr id="105" name="Image 105" descr="Picture"/>
         <cNvPicPr/>
       </nvPicPr>
@@ -2828,8 +2828,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>200</row>
-      <rowOff>1085850</rowOff>
+      <row>215</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2853,8 +2853,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>200</row>
-      <rowOff>1085850</rowOff>
+      <row>215</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -2864,181 +2864,6 @@
       </nvPicPr>
       <blipFill>
         <a:blip cstate="print" r:embed="rId107"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>213</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="876300" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="108" name="Image 108" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId108"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>213</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="109" name="Image 109" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId109"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>2171700</colOff>
-      <row>213</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="110" name="Image 110" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId110"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>3257550</colOff>
-      <row>213</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="111" name="Image 111" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId111"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>4343400</colOff>
-      <row>213</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="112" name="Image 112" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId112"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>213</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="113" name="Image 113" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId113"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>0</col>
-      <colOff>1085850</colOff>
-      <row>213</row>
-      <rowOff>1085850</rowOff>
-    </from>
-    <ext cx="1047750" cy="1047750"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="114" name="Image 114" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip cstate="print" r:embed="rId114"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -3056,6 +2881,181 @@
       <row>228</row>
       <rowOff>0</rowOff>
     </from>
+    <ext cx="876300" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="108" name="Image 108" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId108"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>228</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="109" name="Image 109" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId109"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>2171700</colOff>
+      <row>228</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="110" name="Image 110" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId110"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>3257550</colOff>
+      <row>228</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="111" name="Image 111" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId111"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>4343400</colOff>
+      <row>228</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="112" name="Image 112" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId112"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>229</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="113" name="Image 113" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId113"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>1085850</colOff>
+      <row>229</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1047750" cy="1047750"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="114" name="Image 114" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip cstate="print" r:embed="rId114"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>244</row>
+      <rowOff>0</rowOff>
+    </from>
     <ext cx="552450" cy="1047750"/>
     <pic>
       <nvPicPr>
@@ -3078,7 +3078,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>246</row>
+      <row>264</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="9525" cy="9525"/>
@@ -3103,7 +3103,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>246</row>
+      <row>264</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="781050" cy="1047750"/>
@@ -3128,7 +3128,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>246</row>
+      <row>264</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -3153,7 +3153,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>246</row>
+      <row>264</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -3178,7 +3178,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>246</row>
+      <row>264</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
@@ -3203,8 +3203,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>246</row>
-      <rowOff>1085850</rowOff>
+      <row>265</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3228,8 +3228,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>246</row>
-      <rowOff>1085850</rowOff>
+      <row>265</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3253,8 +3253,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>246</row>
-      <rowOff>1085850</rowOff>
+      <row>265</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3278,8 +3278,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>246</row>
-      <rowOff>1085850</rowOff>
+      <row>265</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3303,8 +3303,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>246</row>
-      <rowOff>1085850</rowOff>
+      <row>265</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3328,8 +3328,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>246</row>
-      <rowOff>2171700</rowOff>
+      <row>266</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3353,8 +3353,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>246</row>
-      <rowOff>2171700</rowOff>
+      <row>266</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3378,8 +3378,8 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>246</row>
-      <rowOff>2171700</rowOff>
+      <row>266</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3403,8 +3403,8 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>246</row>
-      <rowOff>2171700</rowOff>
+      <row>266</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3428,8 +3428,8 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>246</row>
-      <rowOff>2171700</rowOff>
+      <row>266</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3453,8 +3453,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>246</row>
-      <rowOff>3257550</rowOff>
+      <row>267</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1000125"/>
     <pic>
@@ -3478,7 +3478,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>261</row>
+      <row>282</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3503,7 +3503,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>261</row>
+      <row>282</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3528,7 +3528,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>261</row>
+      <row>282</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3553,7 +3553,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>261</row>
+      <row>282</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3578,7 +3578,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>261</row>
+      <row>282</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3603,8 +3603,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>261</row>
-      <rowOff>1085850</rowOff>
+      <row>283</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -3628,8 +3628,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>261</row>
-      <rowOff>1085850</rowOff>
+      <row>283</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -3653,7 +3653,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>274</row>
+      <row>297</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3678,7 +3678,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>274</row>
+      <row>297</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3703,7 +3703,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>274</row>
+      <row>297</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3728,7 +3728,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>274</row>
+      <row>297</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3753,7 +3753,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>274</row>
+      <row>297</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3778,8 +3778,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>274</row>
-      <rowOff>1085850</rowOff>
+      <row>298</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -3803,8 +3803,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>274</row>
-      <rowOff>1085850</rowOff>
+      <row>298</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -3828,7 +3828,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>288</row>
+      <row>312</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3853,7 +3853,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>288</row>
+      <row>312</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3878,7 +3878,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>288</row>
+      <row>312</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3903,7 +3903,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>288</row>
+      <row>312</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3928,7 +3928,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>288</row>
+      <row>312</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -3953,8 +3953,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>288</row>
-      <rowOff>1085850</rowOff>
+      <row>313</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -3978,8 +3978,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>288</row>
-      <rowOff>1085850</rowOff>
+      <row>313</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -4003,7 +4003,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>303</row>
+      <row>328</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4028,7 +4028,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>303</row>
+      <row>328</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4053,7 +4053,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>303</row>
+      <row>328</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4078,7 +4078,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>303</row>
+      <row>328</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4103,7 +4103,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>303</row>
+      <row>328</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4128,8 +4128,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>303</row>
-      <rowOff>1085850</rowOff>
+      <row>329</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -4153,8 +4153,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>303</row>
-      <rowOff>1085850</rowOff>
+      <row>329</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -4178,7 +4178,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>319</row>
+      <row>345</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4203,7 +4203,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>319</row>
+      <row>345</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4228,7 +4228,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>319</row>
+      <row>345</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4253,7 +4253,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>319</row>
+      <row>345</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4278,7 +4278,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>319</row>
+      <row>345</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4303,8 +4303,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>319</row>
-      <rowOff>1085850</rowOff>
+      <row>346</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -4328,8 +4328,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>319</row>
-      <rowOff>1085850</rowOff>
+      <row>346</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -4353,7 +4353,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>334</row>
+      <row>362</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4378,7 +4378,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>334</row>
+      <row>362</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4403,7 +4403,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>334</row>
+      <row>362</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4428,7 +4428,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>334</row>
+      <row>362</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4453,7 +4453,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>334</row>
+      <row>362</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4478,8 +4478,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>334</row>
-      <rowOff>1085850</rowOff>
+      <row>363</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -4503,8 +4503,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>334</row>
-      <rowOff>1085850</rowOff>
+      <row>363</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -4528,7 +4528,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>351</row>
+      <row>381</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4553,7 +4553,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>351</row>
+      <row>381</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4578,7 +4578,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>351</row>
+      <row>381</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4603,7 +4603,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>351</row>
+      <row>381</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4628,7 +4628,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>351</row>
+      <row>381</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4653,8 +4653,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>351</row>
-      <rowOff>1085850</rowOff>
+      <row>382</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -4678,8 +4678,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>351</row>
-      <rowOff>1085850</rowOff>
+      <row>382</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -4703,7 +4703,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>366</row>
+      <row>397</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4728,7 +4728,7 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>366</row>
+      <row>397</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4753,7 +4753,7 @@
     <from>
       <col>0</col>
       <colOff>2171700</colOff>
-      <row>366</row>
+      <row>397</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4778,7 +4778,7 @@
     <from>
       <col>0</col>
       <colOff>3257550</colOff>
-      <row>366</row>
+      <row>397</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1009650" cy="1047750"/>
@@ -4803,7 +4803,7 @@
     <from>
       <col>0</col>
       <colOff>4343400</colOff>
-      <row>366</row>
+      <row>397</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
@@ -4828,8 +4828,8 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>366</row>
-      <rowOff>1085850</rowOff>
+      <row>398</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -4853,8 +4853,8 @@
     <from>
       <col>0</col>
       <colOff>1085850</colOff>
-      <row>366</row>
-      <rowOff>1085850</rowOff>
+      <row>398</row>
+      <rowOff>0</rowOff>
     </from>
     <ext cx="1047750" cy="1047750"/>
     <pic>
@@ -5166,7 +5166,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D367"/>
+  <dimension ref="A1:D399"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -5207,7 +5207,7 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="15" customHeight="1">
+    <row r="3" ht="16" customHeight="1">
       <c r="A3" s="4" t="inlineStr">
         <is>
           <t>글루타치온</t>
@@ -5225,7 +5225,7 @@
       </c>
       <c r="D3" s="4" t="n"/>
     </row>
-    <row r="4" ht="30" customHeight="1">
+    <row r="4" ht="32" customHeight="1">
       <c r="A4" s="4" t="inlineStr">
         <is>
           <t>알부틴 리포좀</t>
@@ -5243,7 +5243,7 @@
       </c>
       <c r="D4" s="4" t="n"/>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="32" customHeight="1">
       <c r="A5" s="4" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
@@ -5265,7 +5265,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="15" customHeight="1">
+    <row r="6" ht="16" customHeight="1">
       <c r="A6" s="4" t="inlineStr">
         <is>
           <t>네롤리워터</t>
@@ -5287,7 +5287,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="15" customHeight="1">
+    <row r="7" ht="16" customHeight="1">
       <c r="A7" s="4" t="inlineStr">
         <is>
           <t>다중히아루론산</t>
@@ -5309,7 +5309,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="45" customHeight="1">
+    <row r="8" ht="48" customHeight="1">
       <c r="A8" s="4" t="inlineStr">
         <is>
           <t>1,2 헥산디올</t>
@@ -5341,7 +5341,7 @@
       <c r="C9" s="6" t="n"/>
       <c r="D9" s="6" t="n"/>
     </row>
-    <row r="10" ht="345" customHeight="1">
+    <row r="10" ht="368" customHeight="1">
       <c r="A10" s="7" t="inlineStr">
         <is>
           <t>기미잡티에 착~붙이는
@@ -5380,7 +5380,7 @@
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
     </row>
-    <row r="12" ht="150" customHeight="1">
+    <row r="12" ht="160" customHeight="1">
       <c r="A12" s="7" t="inlineStr">
         <is>
           <t>글루타치온 미백 패드 만들기
@@ -5404,158 +5404,159 @@
       <c r="C13" s="6" t="n"/>
       <c r="D13" s="6" t="n"/>
     </row>
-    <row r="14" ht="171" customHeight="1"/>
-    <row r="15" ht="6" customHeight="1"/>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
+    <row r="14" ht="85.5" customHeight="1"/>
+    <row r="15" ht="85.5" customHeight="1"/>
+    <row r="16" ht="6" customHeight="1"/>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="1" t="inlineStr">
         <is>
           <t>곡물 영양 윤패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B16" s="2" t="n"/>
-      <c r="C16" s="2" t="n"/>
-      <c r="D16" s="2" t="n"/>
-    </row>
-    <row r="17" ht="15" customHeight="1">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="B17" s="2" t="n"/>
+      <c r="C17" s="2" t="n"/>
+      <c r="D17" s="2" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C17" s="3" t="inlineStr">
+      <c r="C18" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D17" s="3" t="inlineStr">
+      <c r="D18" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+    <row r="19" ht="32" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
         <is>
           <t>슈퍼곡물 단백질추출물</t>
         </is>
       </c>
-      <c r="B18" s="8" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>단백질 케어로 / 피부에 깊은 영양</t>
         </is>
       </c>
-      <c r="D18" s="8" t="inlineStr">
+      <c r="D19" s="8" t="inlineStr">
         <is>
           <t>맥주효모추출물</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
         <is>
           <t>갈락토미세스발효여과물</t>
         </is>
       </c>
-      <c r="B19" s="8" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C19" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>발효여과물, / 보습, 탄력, 아미노산, / 미네럴 영양공급</t>
         </is>
       </c>
-      <c r="D19" s="8" t="inlineStr">
+      <c r="D20" s="8" t="inlineStr">
         <is>
           <t>비피다발효용해물</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+    <row r="21" ht="16" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
         <is>
           <t>비오틴</t>
         </is>
       </c>
-      <c r="B20" s="8" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C21" s="8" t="inlineStr">
         <is>
           <t>비타민B7, 피부 진정</t>
         </is>
       </c>
-      <c r="D20" s="8" t="n"/>
-    </row>
-    <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="D21" s="8" t="n"/>
+    </row>
+    <row r="22" ht="32" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
         <is>
           <t>덱스판테놀</t>
         </is>
       </c>
-      <c r="B21" s="8" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>비타민B5, 보습 / 식약처 기능성 고시원료</t>
         </is>
       </c>
-      <c r="D21" s="8" t="inlineStr">
+      <c r="D22" s="8" t="inlineStr">
         <is>
           <t>판테놀</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="45" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+    <row r="23" ht="48" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B22" s="8" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C22" s="8" t="inlineStr">
+      <c r="C23" s="8" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="D22" s="8" t="inlineStr">
+      <c r="D23" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="14" customHeight="1">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24" ht="14" customHeight="1">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-    </row>
-    <row r="24" ht="285" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+    </row>
+    <row r="25" ht="304" customHeight="1">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>화잘먹
 곡물 영양 패드
@@ -5578,22 +5579,22 @@
 피부를 윤기있게 가꿔줍니다.</t>
         </is>
       </c>
-      <c r="B24" s="10" t="n"/>
-      <c r="C24" s="10" t="n"/>
-      <c r="D24" s="10" t="n"/>
-    </row>
-    <row r="25" ht="14" customHeight="1">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="B25" s="10" t="n"/>
+      <c r="C25" s="10" t="n"/>
+      <c r="D25" s="10" t="n"/>
+    </row>
+    <row r="26" ht="14" customHeight="1">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-    </row>
-    <row r="26" ht="150" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+    </row>
+    <row r="27" ht="160" customHeight="1">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>1. 용기에 모든 재료를 계량한 후 섞어주세요.
 2. 다 섞일 때까지 흔들어 주세요.
@@ -5606,177 +5607,183 @@
 (매끈한 면은 에센스 팩용으로 엠보면은 각질, 노폐물 제거용으로 사용하세요.)</t>
         </is>
       </c>
-      <c r="B26" s="10" t="n"/>
-      <c r="C26" s="10" t="n"/>
-      <c r="D26" s="10" t="n"/>
-    </row>
-    <row r="27" ht="14" customHeight="1">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="B27" s="10" t="n"/>
+      <c r="C27" s="10" t="n"/>
+      <c r="D27" s="10" t="n"/>
+    </row>
+    <row r="28" ht="14" customHeight="1">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-    </row>
-    <row r="28" ht="171" customHeight="1">
-      <c r="A28" s="10" t="n"/>
-      <c r="B28" s="10" t="n"/>
-      <c r="C28" s="10" t="n"/>
-      <c r="D28" s="10" t="n"/>
-    </row>
-    <row r="29" ht="6" customHeight="1"/>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="1" t="inlineStr">
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+    </row>
+    <row r="29" ht="85.5" customHeight="1">
+      <c r="A29" s="10" t="n"/>
+      <c r="B29" s="10" t="n"/>
+      <c r="C29" s="10" t="n"/>
+      <c r="D29" s="10" t="n"/>
+    </row>
+    <row r="30" ht="85.5" customHeight="1">
+      <c r="A30" s="10" t="n"/>
+      <c r="B30" s="10" t="n"/>
+      <c r="C30" s="10" t="n"/>
+      <c r="D30" s="10" t="n"/>
+    </row>
+    <row r="31" ht="6" customHeight="1"/>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="1" t="inlineStr">
         <is>
           <t>녹차 모공 제로 패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B30" s="2" t="n"/>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n"/>
-    </row>
-    <row r="31" ht="15" customHeight="1">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="B32" s="2" t="n"/>
+      <c r="C32" s="2" t="n"/>
+      <c r="D32" s="2" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1">
+      <c r="A33" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B31" s="3" t="inlineStr">
+      <c r="B33" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C31" s="3" t="inlineStr">
+      <c r="C33" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D31" s="3" t="inlineStr">
+      <c r="D33" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="4" t="inlineStr">
+    <row r="34" ht="32" customHeight="1">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>녹차추출물</t>
         </is>
       </c>
-      <c r="B32" s="4" t="inlineStr">
+      <c r="B34" s="4" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C32" s="4" t="inlineStr">
+      <c r="C34" s="4" t="inlineStr">
         <is>
           <t>모공 탄력, / 폴리페놀 풍부</t>
         </is>
       </c>
-      <c r="D32" s="4" t="inlineStr">
+      <c r="D34" s="4" t="inlineStr">
         <is>
           <t>녹소초 추출물, / 유기농 브라이트닝 5 등.</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="15" customHeight="1">
-      <c r="A33" s="4" t="inlineStr">
+    <row r="35" ht="16" customHeight="1">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>로즈마리워터</t>
         </is>
       </c>
-      <c r="B33" s="4" t="inlineStr">
+      <c r="B35" s="4" t="inlineStr">
         <is>
           <t>55g</t>
         </is>
       </c>
-      <c r="C33" s="4" t="inlineStr">
+      <c r="C35" s="4" t="inlineStr">
         <is>
           <t>모공탄력</t>
         </is>
       </c>
-      <c r="D33" s="4" t="inlineStr">
+      <c r="D35" s="4" t="inlineStr">
         <is>
           <t>프리미엄 / 녹차워터</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="4" t="inlineStr">
+    <row r="36" ht="32" customHeight="1">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>아하바하파하 컴플렉스</t>
         </is>
       </c>
-      <c r="B34" s="4" t="inlineStr">
+      <c r="B36" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C34" s="4" t="inlineStr">
+      <c r="C36" s="4" t="inlineStr">
         <is>
           <t>AHA+ BHA+PHA 성분 / 각질제거, 노폐물정리</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n"/>
-    </row>
-    <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="D36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="32" customHeight="1">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
-      <c r="B35" s="4" t="inlineStr">
+      <c r="B37" s="4" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C35" s="4" t="inlineStr">
+      <c r="C37" s="4" t="inlineStr">
         <is>
           <t>표피~진피 수분 충전 / 고분자+중분자+저분자</t>
         </is>
       </c>
-      <c r="D35" s="4" t="inlineStr">
+      <c r="D37" s="4" t="inlineStr">
         <is>
           <t>판테놀</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="45" customHeight="1">
-      <c r="A36" s="4" t="inlineStr">
+    <row r="38" ht="48" customHeight="1">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B36" s="4" t="inlineStr">
+      <c r="B38" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C36" s="4" t="inlineStr">
+      <c r="C38" s="4" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="D36" s="4" t="inlineStr">
+      <c r="D38" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="14" customHeight="1">
-      <c r="A37" s="5" t="inlineStr">
+    <row r="39" ht="14" customHeight="1">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B37" s="6" t="n"/>
-      <c r="C37" s="6" t="n"/>
-      <c r="D37" s="6" t="n"/>
-    </row>
-    <row r="38" ht="330" customHeight="1">
-      <c r="A38" s="7" t="inlineStr">
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n"/>
+    </row>
+    <row r="40" ht="352" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>깐달걀 피부
 녹차 모공 제로 패드
@@ -5803,18 +5810,18 @@
         </is>
       </c>
     </row>
-    <row r="39" ht="14" customHeight="1">
-      <c r="A39" s="5" t="inlineStr">
+    <row r="41" ht="14" customHeight="1">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B39" s="6" t="n"/>
-      <c r="C39" s="6" t="n"/>
-      <c r="D39" s="6" t="n"/>
-    </row>
-    <row r="40" ht="135" customHeight="1">
-      <c r="A40" s="7" t="inlineStr">
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+    </row>
+    <row r="42" ht="144" customHeight="1">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>1. 용기에 모든 재료를 계량한 후 섞어주세요.
 2. 다 섞일 때까지 흔들어 주세요.
@@ -5827,190 +5834,191 @@
         </is>
       </c>
     </row>
-    <row r="41" ht="14" customHeight="1">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="43" ht="14" customHeight="1">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B41" s="6" t="n"/>
-      <c r="C41" s="6" t="n"/>
-      <c r="D41" s="6" t="n"/>
-    </row>
-    <row r="42" ht="171" customHeight="1"/>
-    <row r="43" ht="6" customHeight="1"/>
-    <row r="44" ht="22" customHeight="1">
-      <c r="A44" s="1" t="inlineStr">
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+    </row>
+    <row r="44" ht="85.5" customHeight="1"/>
+    <row r="45" ht="85.5" customHeight="1"/>
+    <row r="46" ht="6" customHeight="1"/>
+    <row r="47" ht="22" customHeight="1">
+      <c r="A47" s="1" t="inlineStr">
         <is>
           <t>히아루론산 토너 &amp; 패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B44" s="2" t="n"/>
-      <c r="C44" s="2" t="n"/>
-      <c r="D44" s="2" t="n"/>
-    </row>
-    <row r="45" ht="15" customHeight="1">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="B47" s="2" t="n"/>
+      <c r="C47" s="2" t="n"/>
+      <c r="D47" s="2" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1">
+      <c r="A48" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B45" s="3" t="inlineStr">
+      <c r="B48" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
+      <c r="C48" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D45" s="3" t="inlineStr">
+      <c r="D48" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="46" ht="45" customHeight="1">
-      <c r="A46" s="8" t="inlineStr">
+    <row r="49" ht="48" customHeight="1">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>11 히아루론산</t>
         </is>
       </c>
-      <c r="B46" s="8" t="inlineStr">
+      <c r="B49" s="8" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C46" s="8" t="inlineStr">
+      <c r="C49" s="8" t="inlineStr">
         <is>
           <t>크기가 다른 11가지 히아루론산으로 피부 속부터 겉까지 수분채움, 단독 사용 가능</t>
         </is>
       </c>
-      <c r="D46" s="8" t="inlineStr">
+      <c r="D49" s="8" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="45" customHeight="1">
-      <c r="A47" s="8" t="inlineStr">
+    <row r="50" ht="48" customHeight="1">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>아미노산17 컴플렉스</t>
         </is>
       </c>
-      <c r="B47" s="8" t="inlineStr">
+      <c r="B50" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C47" s="8" t="inlineStr">
+      <c r="C50" s="8" t="inlineStr">
         <is>
           <t>실제 피부 각질층 아미노산 구성과 유사한 17가지 아미노산, 보습·톤오버 유도·재생·톤업</t>
         </is>
       </c>
-      <c r="D47" s="8" t="n"/>
-    </row>
-    <row r="48" ht="15" customHeight="1">
-      <c r="A48" s="8" t="inlineStr">
+      <c r="D50" s="8" t="n"/>
+    </row>
+    <row r="51" ht="16" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B48" s="8" t="inlineStr">
+      <c r="B51" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C48" s="8" t="inlineStr">
+      <c r="C51" s="8" t="inlineStr">
         <is>
           <t>비타민B3, 식약처 미백 고시 원료</t>
         </is>
       </c>
-      <c r="D48" s="8" t="inlineStr">
+      <c r="D51" s="8" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="8" t="inlineStr">
+    <row r="52" ht="32" customHeight="1">
+      <c r="A52" s="8" t="inlineStr">
         <is>
           <t>네롤리워터</t>
         </is>
       </c>
-      <c r="B49" s="8" t="inlineStr">
+      <c r="B52" s="8" t="inlineStr">
         <is>
           <t>66g</t>
         </is>
       </c>
-      <c r="C49" s="8" t="inlineStr">
+      <c r="C52" s="8" t="inlineStr">
         <is>
           <t>오렌지꽃수, 수분, 진정, 결케어 도움</t>
         </is>
       </c>
-      <c r="D49" s="8" t="inlineStr">
+      <c r="D52" s="8" t="inlineStr">
         <is>
           <t>로즈워터, 정제수</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="8" t="inlineStr">
+    <row r="53" ht="32" customHeight="1">
+      <c r="A53" s="8" t="inlineStr">
         <is>
           <t>에코 보습제</t>
         </is>
       </c>
-      <c r="B50" s="8" t="inlineStr">
+      <c r="B53" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C50" s="8" t="inlineStr">
+      <c r="C53" s="8" t="inlineStr">
         <is>
           <t>옥수수 발효 보습제, 가볍고 오래가는 보습</t>
         </is>
       </c>
-      <c r="D50" s="8" t="inlineStr">
+      <c r="D53" s="8" t="inlineStr">
         <is>
           <t>낫또 모이스트</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="45" customHeight="1">
-      <c r="A51" s="8" t="inlineStr">
+    <row r="54" ht="48" customHeight="1">
+      <c r="A54" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B51" s="8" t="inlineStr">
+      <c r="B54" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C51" s="8" t="inlineStr">
+      <c r="C54" s="8" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="D51" s="8" t="inlineStr">
+      <c r="D54" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="14" customHeight="1">
-      <c r="A52" s="5" t="inlineStr">
+    <row r="55" ht="14" customHeight="1">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B52" s="6" t="n"/>
-      <c r="C52" s="6" t="n"/>
-      <c r="D52" s="6" t="n"/>
-    </row>
-    <row r="53" ht="300" customHeight="1">
-      <c r="A53" s="9" t="inlineStr">
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n"/>
+    </row>
+    <row r="56" ht="320" customHeight="1">
+      <c r="A56" s="9" t="inlineStr">
         <is>
           <t>11겹으로 촘촘하게 채워 피부 속까지 수분 충전!
 히아루론산 토너 &amp; 패드
@@ -6034,22 +6042,22 @@
 히아루론산 토너 &amp; 패드</t>
         </is>
       </c>
-      <c r="B53" s="10" t="n"/>
-      <c r="C53" s="10" t="n"/>
-      <c r="D53" s="10" t="n"/>
-    </row>
-    <row r="54" ht="14" customHeight="1">
-      <c r="A54" s="5" t="inlineStr">
+      <c r="B56" s="10" t="n"/>
+      <c r="C56" s="10" t="n"/>
+      <c r="D56" s="10" t="n"/>
+    </row>
+    <row r="57" ht="14" customHeight="1">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B54" s="6" t="n"/>
-      <c r="C54" s="6" t="n"/>
-      <c r="D54" s="6" t="n"/>
-    </row>
-    <row r="55" ht="105" customHeight="1">
-      <c r="A55" s="9" t="inlineStr">
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+    </row>
+    <row r="58" ht="112" customHeight="1">
+      <c r="A58" s="9" t="inlineStr">
         <is>
           <t>1. 용기에 모든 재료를 계량한 후 섞어주세요.
 2. 다 섞일 때까지 흔들어 주세요.
@@ -6059,203 +6067,209 @@
 1~2장씩 '양면 순면 패드'를 사용하세요. 집게사용으로 더욱 위생적으로 사용할 수 있어요.</t>
         </is>
       </c>
-      <c r="B55" s="10" t="n"/>
-      <c r="C55" s="10" t="n"/>
-      <c r="D55" s="10" t="n"/>
-    </row>
-    <row r="56" ht="14" customHeight="1">
-      <c r="A56" s="5" t="inlineStr">
+      <c r="B58" s="10" t="n"/>
+      <c r="C58" s="10" t="n"/>
+      <c r="D58" s="10" t="n"/>
+    </row>
+    <row r="59" ht="14" customHeight="1">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B56" s="6" t="n"/>
-      <c r="C56" s="6" t="n"/>
-      <c r="D56" s="6" t="n"/>
-    </row>
-    <row r="57" ht="171" customHeight="1">
-      <c r="A57" s="10" t="n"/>
-      <c r="B57" s="10" t="n"/>
-      <c r="C57" s="10" t="n"/>
-      <c r="D57" s="10" t="n"/>
-    </row>
-    <row r="58" ht="6" customHeight="1"/>
-    <row r="59" ht="22" customHeight="1">
-      <c r="A59" s="1" t="inlineStr">
+      <c r="B59" s="6" t="n"/>
+      <c r="C59" s="6" t="n"/>
+      <c r="D59" s="6" t="n"/>
+    </row>
+    <row r="60" ht="85.5" customHeight="1">
+      <c r="A60" s="10" t="n"/>
+      <c r="B60" s="10" t="n"/>
+      <c r="C60" s="10" t="n"/>
+      <c r="D60" s="10" t="n"/>
+    </row>
+    <row r="61" ht="85.5" customHeight="1">
+      <c r="A61" s="10" t="n"/>
+      <c r="B61" s="10" t="n"/>
+      <c r="C61" s="10" t="n"/>
+      <c r="D61" s="10" t="n"/>
+    </row>
+    <row r="62" ht="6" customHeight="1"/>
+    <row r="63" ht="22" customHeight="1">
+      <c r="A63" s="1" t="inlineStr">
         <is>
           <t>쿠퍼모근튼튼에센스&amp;팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B59" s="2" t="n"/>
-      <c r="C59" s="2" t="n"/>
-      <c r="D59" s="2" t="n"/>
-    </row>
-    <row r="60" ht="15" customHeight="1">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="B63" s="2" t="n"/>
+      <c r="C63" s="2" t="n"/>
+      <c r="D63" s="2" t="n"/>
+    </row>
+    <row r="64" ht="15" customHeight="1">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B60" s="3" t="inlineStr">
+      <c r="B64" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C60" s="3" t="inlineStr">
+      <c r="C64" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D60" s="3" t="inlineStr">
+      <c r="D64" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="4" t="inlineStr">
+    <row r="65" ht="32" customHeight="1">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>편백워터</t>
         </is>
       </c>
-      <c r="B61" s="4" t="inlineStr">
+      <c r="B65" s="4" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C61" s="4" t="inlineStr">
+      <c r="C65" s="4" t="inlineStr">
         <is>
           <t>편백잎을 수증기증류, 아주 소량의 피톤치드함유</t>
         </is>
       </c>
-      <c r="D61" s="4" t="inlineStr">
+      <c r="D65" s="4" t="inlineStr">
         <is>
           <t>로즈마리워터</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="60" customHeight="1">
-      <c r="A62" s="4" t="inlineStr">
+    <row r="66" ht="64" customHeight="1">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>알로에모이스트</t>
         </is>
       </c>
-      <c r="B62" s="4" t="inlineStr">
+      <c r="B66" s="4" t="inlineStr">
         <is>
           <t>45g</t>
         </is>
       </c>
-      <c r="C62" s="4" t="inlineStr">
+      <c r="C66" s="4" t="inlineStr">
         <is>
           <t>점도, 수분공급, 진정</t>
         </is>
       </c>
-      <c r="D62" s="4" t="inlineStr">
+      <c r="D66" s="4" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="45" customHeight="1">
-      <c r="A63" s="4" t="inlineStr">
+    <row r="67" ht="48" customHeight="1">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B63" s="4" t="inlineStr">
+      <c r="B67" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C63" s="4" t="inlineStr">
+      <c r="C67" s="4" t="inlineStr">
         <is>
           <t>녹황색채소유래, 비타민B3, / 미백기능성 원료이기도 / 하지만 피부장벽을 강화효과</t>
         </is>
       </c>
-      <c r="D63" s="4" t="inlineStr">
+      <c r="D67" s="4" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="60" customHeight="1">
-      <c r="A64" s="4" t="inlineStr">
+    <row r="68" ht="64" customHeight="1">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>윤모생기추출물</t>
         </is>
       </c>
-      <c r="B64" s="4" t="inlineStr">
+      <c r="B68" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C64" s="4" t="inlineStr">
+      <c r="C68" s="4" t="inlineStr">
         <is>
           <t>호호바, 에스피노질리아, 호두, 아보카도,알로에, 캐모마일, 네틀, 엘더베리, 감국,만형자, 측백엽, 천궁, 백지, 세신,상백피, 한련초 추출물</t>
         </is>
       </c>
-      <c r="D64" s="4" t="inlineStr">
+      <c r="D68" s="4" t="inlineStr">
         <is>
           <t>진한 적하수오추출물,녹차추출물, 에스피노질리아, 네틀추출물 등...</t>
         </is>
       </c>
     </row>
-    <row r="65" ht="15" customHeight="1">
-      <c r="A65" s="4" t="inlineStr">
+    <row r="69" ht="16" customHeight="1">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>쿠퍼펩타이드</t>
         </is>
       </c>
-      <c r="B65" s="4" t="inlineStr">
+      <c r="B69" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
+      <c r="C69" s="4" t="inlineStr">
         <is>
           <t>두피를 두껍게</t>
         </is>
       </c>
-      <c r="D65" s="4" t="inlineStr">
+      <c r="D69" s="4" t="inlineStr">
         <is>
           <t>펩타이드 류</t>
         </is>
       </c>
     </row>
-    <row r="66" ht="60" customHeight="1">
-      <c r="A66" s="4" t="inlineStr">
+    <row r="70" ht="64" customHeight="1">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B66" s="4" t="inlineStr">
+      <c r="B70" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C66" s="4" t="inlineStr">
+      <c r="C70" s="4" t="inlineStr">
         <is>
           <t>천연허브유래 균번식 억제제 복합처방</t>
         </is>
       </c>
-      <c r="D66" s="4" t="inlineStr">
+      <c r="D70" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="67" ht="14" customHeight="1">
-      <c r="A67" s="5" t="inlineStr">
+    <row r="71" ht="14" customHeight="1">
+      <c r="A71" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B67" s="6" t="n"/>
-      <c r="C67" s="6" t="n"/>
-      <c r="D67" s="6" t="n"/>
-    </row>
-    <row r="68" ht="150" customHeight="1">
-      <c r="A68" s="7" t="inlineStr">
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n"/>
+    </row>
+    <row r="72" ht="160" customHeight="1">
+      <c r="A72" s="7" t="inlineStr">
         <is>
           <t>영양이 많고 좋은 땅에서 나무가 잘 자라듯 두피와 모발도 마찬가지입니다.
 두피가 건강해야 힘이 있고 윤기있는 모발이 잘 자랍니다.
@@ -6270,18 +6284,18 @@
         </is>
       </c>
     </row>
-    <row r="69" ht="14" customHeight="1">
-      <c r="A69" s="5" t="inlineStr">
+    <row r="73" ht="14" customHeight="1">
+      <c r="A73" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B69" s="6" t="n"/>
-      <c r="C69" s="6" t="n"/>
-      <c r="D69" s="6" t="n"/>
-    </row>
-    <row r="70" ht="120" customHeight="1">
-      <c r="A70" s="7" t="inlineStr">
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n"/>
+    </row>
+    <row r="74" ht="128" customHeight="1">
+      <c r="A74" s="7" t="inlineStr">
         <is>
           <t>초정밀 만들기과정
 1.편백워터
@@ -6293,238 +6307,239 @@
         </is>
       </c>
     </row>
-    <row r="71" ht="14" customHeight="1">
-      <c r="A71" s="5" t="inlineStr">
+    <row r="75" ht="14" customHeight="1">
+      <c r="A75" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B71" s="6" t="n"/>
-      <c r="C71" s="6" t="n"/>
-      <c r="D71" s="6" t="n"/>
-    </row>
-    <row r="72" ht="171" customHeight="1"/>
-    <row r="73" ht="6" customHeight="1"/>
-    <row r="74" ht="22" customHeight="1">
-      <c r="A74" s="1" t="inlineStr">
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n"/>
+      <c r="D75" s="6" t="n"/>
+    </row>
+    <row r="76" ht="85.5" customHeight="1"/>
+    <row r="77" ht="85.5" customHeight="1"/>
+    <row r="78" ht="6" customHeight="1"/>
+    <row r="79" ht="22" customHeight="1">
+      <c r="A79" s="1" t="inlineStr">
         <is>
           <t>생기수분 부활초 수면팩    [오일/유화제]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B74" s="2" t="n"/>
-      <c r="C74" s="2" t="n"/>
-      <c r="D74" s="2" t="n"/>
-    </row>
-    <row r="75" ht="15" customHeight="1">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="B79" s="2" t="n"/>
+      <c r="C79" s="2" t="n"/>
+      <c r="D79" s="2" t="n"/>
+    </row>
+    <row r="80" ht="15" customHeight="1">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B75" s="3" t="inlineStr">
+      <c r="B80" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C75" s="3" t="inlineStr">
+      <c r="C80" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D75" s="3" t="inlineStr">
+      <c r="D80" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="8" t="inlineStr">
+    <row r="81" ht="32" customHeight="1">
+      <c r="A81" s="8" t="inlineStr">
         <is>
           <t>로즈힙오일</t>
         </is>
       </c>
-      <c r="B76" s="8" t="inlineStr">
+      <c r="B81" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C76" s="8" t="inlineStr">
+      <c r="C81" s="8" t="inlineStr">
         <is>
           <t>리놀렌산풍부, / 주름노화관리 도움</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D81" s="8" t="inlineStr">
         <is>
           <t>골든호호바 또는 / 원하는 베이스오일</t>
         </is>
       </c>
     </row>
-    <row r="77" ht="45" customHeight="1">
-      <c r="A77" s="8" t="inlineStr">
+    <row r="82" ht="48" customHeight="1">
+      <c r="A82" s="8" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B77" s="8" t="inlineStr">
+      <c r="B82" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C77" s="8" t="inlineStr">
+      <c r="C82" s="8" t="inlineStr">
         <is>
           <t>자체 점증, 보습, 수분공급</t>
         </is>
       </c>
-      <c r="D77" s="8" t="inlineStr">
+      <c r="D82" s="8" t="inlineStr">
         <is>
           <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="78" ht="60" customHeight="1">
-      <c r="A78" s="8" t="inlineStr">
+    <row r="83" ht="64" customHeight="1">
+      <c r="A83" s="8" t="inlineStr">
         <is>
           <t>알로에모이스트</t>
         </is>
       </c>
-      <c r="B78" s="8" t="inlineStr">
+      <c r="B83" s="8" t="inlineStr">
         <is>
           <t>68g</t>
         </is>
       </c>
-      <c r="C78" s="8" t="inlineStr">
+      <c r="C83" s="8" t="inlineStr">
         <is>
           <t>순수한 물, / 완성품의 색을 고르게.</t>
         </is>
       </c>
-      <c r="D78" s="8" t="inlineStr">
+      <c r="D83" s="8" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="8" t="inlineStr">
+    <row r="84" ht="32" customHeight="1">
+      <c r="A84" s="8" t="inlineStr">
         <is>
           <t>부활초 줄기세포 / (캘러스) 배양액</t>
         </is>
       </c>
-      <c r="B79" s="8" t="inlineStr">
+      <c r="B84" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C79" s="8" t="inlineStr">
+      <c r="C84" s="8" t="inlineStr">
         <is>
           <t>부활초 캘러스 배양 추출물</t>
         </is>
       </c>
-      <c r="D79" s="8" t="inlineStr">
+      <c r="D84" s="8" t="inlineStr">
         <is>
           <t>인삼줄기세포, / 장미줄기세포 등</t>
         </is>
       </c>
     </row>
-    <row r="80" ht="45" customHeight="1">
-      <c r="A80" s="8" t="inlineStr">
+    <row r="85" ht="48" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
         <is>
           <t>트레할로스</t>
         </is>
       </c>
-      <c r="B80" s="8" t="inlineStr">
+      <c r="B85" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C80" s="8" t="inlineStr">
+      <c r="C85" s="8" t="inlineStr">
         <is>
           <t>보습, 탈취</t>
         </is>
       </c>
-      <c r="D80" s="8" t="inlineStr">
+      <c r="D85" s="8" t="inlineStr">
         <is>
           <t>낫또모이스트, / 판테놀, 리피듀어, / 히아루론산 등</t>
         </is>
       </c>
     </row>
-    <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="8" t="inlineStr">
+    <row r="86" ht="32" customHeight="1">
+      <c r="A86" s="8" t="inlineStr">
         <is>
           <t>알파비사보롤</t>
         </is>
       </c>
-      <c r="B81" s="8" t="inlineStr">
+      <c r="B86" s="8" t="inlineStr">
         <is>
           <t>1g / (40방울)</t>
         </is>
       </c>
-      <c r="C81" s="8" t="inlineStr">
+      <c r="C86" s="8" t="inlineStr">
         <is>
           <t>오일, 에코인증, / 미백 트러블진정 성분 / Candeia Tree에서 추출</t>
         </is>
       </c>
-      <c r="D81" s="8" t="inlineStr">
+      <c r="D86" s="8" t="inlineStr">
         <is>
           <t>알부틴</t>
         </is>
       </c>
     </row>
-    <row r="82" ht="45" customHeight="1">
-      <c r="A82" s="8" t="inlineStr">
+    <row r="87" ht="48" customHeight="1">
+      <c r="A87" s="8" t="inlineStr">
         <is>
           <t>수용성보존제</t>
         </is>
       </c>
-      <c r="B82" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C82" s="8" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
         <is>
           <t>식물복합추출물 / 균번식 억제제</t>
         </is>
       </c>
-      <c r="D82" s="8" t="inlineStr">
+      <c r="D87" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제, / 나트로틱스 / (워터류1g 줄이고 2g)</t>
         </is>
       </c>
     </row>
-    <row r="83" ht="15" customHeight="1">
-      <c r="A83" s="8" t="inlineStr">
+    <row r="88" ht="16" customHeight="1">
+      <c r="A88" s="8" t="inlineStr">
         <is>
           <t>만다린EO</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B88" s="8" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>귤껍질오일</t>
         </is>
       </c>
-      <c r="D83" s="8" t="inlineStr">
+      <c r="D88" s="8" t="inlineStr">
         <is>
           <t>원하는 아로마오일</t>
         </is>
       </c>
     </row>
-    <row r="84" ht="14" customHeight="1">
-      <c r="A84" s="5" t="inlineStr">
+    <row r="89" ht="14" customHeight="1">
+      <c r="A89" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B84" s="6" t="n"/>
-      <c r="C84" s="6" t="n"/>
-      <c r="D84" s="6" t="n"/>
-    </row>
-    <row r="85" ht="135" customHeight="1">
-      <c r="A85" s="9" t="inlineStr">
+      <c r="B89" s="6" t="n"/>
+      <c r="C89" s="6" t="n"/>
+      <c r="D89" s="6" t="n"/>
+    </row>
+    <row r="90" ht="144" customHeight="1">
+      <c r="A90" s="9" t="inlineStr">
         <is>
           <t>부활초는 건조한 사막에서 자라는데
 가물면 잎이 공처럼 둥글게 말려
@@ -6537,22 +6552,22 @@
 [ 계량] 1. 알로에모이스트와 오일/유화제를 각각 다른 비커에 계량해주세요.</t>
         </is>
       </c>
-      <c r="B85" s="10" t="n"/>
-      <c r="C85" s="10" t="n"/>
-      <c r="D85" s="10" t="n"/>
-    </row>
-    <row r="86" ht="14" customHeight="1">
-      <c r="A86" s="5" t="inlineStr">
+      <c r="B90" s="10" t="n"/>
+      <c r="C90" s="10" t="n"/>
+      <c r="D90" s="10" t="n"/>
+    </row>
+    <row r="91" ht="14" customHeight="1">
+      <c r="A91" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B86" s="6" t="n"/>
-      <c r="C86" s="6" t="n"/>
-      <c r="D86" s="6" t="n"/>
-    </row>
-    <row r="87" ht="210" customHeight="1">
-      <c r="A87" s="9" t="inlineStr">
+      <c r="B91" s="6" t="n"/>
+      <c r="C91" s="6" t="n"/>
+      <c r="D91" s="6" t="n"/>
+    </row>
+    <row r="92" ht="224" customHeight="1">
+      <c r="A92" s="9" t="inlineStr">
         <is>
           <t>2. 알로에모이스트를 골고루 섞으면서 70°C정도로 데워주세요.
 [데우기]
@@ -6569,155 +6584,167 @@
 9..용기에 넣어주면 완성.</t>
         </is>
       </c>
-      <c r="B87" s="10" t="n"/>
-      <c r="C87" s="10" t="n"/>
-      <c r="D87" s="10" t="n"/>
-    </row>
-    <row r="88" ht="14" customHeight="1">
-      <c r="A88" s="5" t="inlineStr">
+      <c r="B92" s="10" t="n"/>
+      <c r="C92" s="10" t="n"/>
+      <c r="D92" s="10" t="n"/>
+    </row>
+    <row r="93" ht="14" customHeight="1">
+      <c r="A93" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B88" s="6" t="n"/>
-      <c r="C88" s="6" t="n"/>
-      <c r="D88" s="6" t="n"/>
-    </row>
-    <row r="89" ht="256.5" customHeight="1">
-      <c r="A89" s="10" t="n"/>
-      <c r="B89" s="10" t="n"/>
-      <c r="C89" s="10" t="n"/>
-      <c r="D89" s="10" t="n"/>
-    </row>
-    <row r="90" ht="6" customHeight="1"/>
-    <row r="91" ht="22" customHeight="1">
-      <c r="A91" s="1" t="inlineStr">
+      <c r="B93" s="6" t="n"/>
+      <c r="C93" s="6" t="n"/>
+      <c r="D93" s="6" t="n"/>
+    </row>
+    <row r="94" ht="85.5" customHeight="1">
+      <c r="A94" s="10" t="n"/>
+      <c r="B94" s="10" t="n"/>
+      <c r="C94" s="10" t="n"/>
+      <c r="D94" s="10" t="n"/>
+    </row>
+    <row r="95" ht="85.5" customHeight="1">
+      <c r="A95" s="10" t="n"/>
+      <c r="B95" s="10" t="n"/>
+      <c r="C95" s="10" t="n"/>
+      <c r="D95" s="10" t="n"/>
+    </row>
+    <row r="96" ht="85.5" customHeight="1">
+      <c r="A96" s="10" t="n"/>
+      <c r="B96" s="10" t="n"/>
+      <c r="C96" s="10" t="n"/>
+      <c r="D96" s="10" t="n"/>
+    </row>
+    <row r="97" ht="6" customHeight="1"/>
+    <row r="98" ht="22" customHeight="1">
+      <c r="A98" s="1" t="inlineStr">
         <is>
           <t>맑아지는 노니팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B91" s="2" t="n"/>
-      <c r="C91" s="2" t="n"/>
-      <c r="D91" s="2" t="n"/>
-    </row>
-    <row r="92" ht="15" customHeight="1">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="B98" s="2" t="n"/>
+      <c r="C98" s="2" t="n"/>
+      <c r="D98" s="2" t="n"/>
+    </row>
+    <row r="99" ht="15" customHeight="1">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B92" s="3" t="inlineStr">
+      <c r="B99" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C92" s="3" t="inlineStr">
+      <c r="C99" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D92" s="3" t="inlineStr">
+      <c r="D99" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="93" ht="15" customHeight="1">
-      <c r="A93" s="4" t="inlineStr">
+    <row r="100" ht="16" customHeight="1">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>노니분말</t>
         </is>
       </c>
-      <c r="B93" s="4" t="inlineStr">
+      <c r="B100" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C93" s="4" t="inlineStr">
+      <c r="C100" s="4" t="inlineStr">
         <is>
           <t>티스푼 1</t>
         </is>
       </c>
-      <c r="D93" s="4" t="n"/>
-    </row>
-    <row r="94" ht="15" customHeight="1">
-      <c r="A94" s="4" t="inlineStr">
+      <c r="D100" s="4" t="n"/>
+    </row>
+    <row r="101" ht="16" customHeight="1">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>오트밀분말</t>
         </is>
       </c>
-      <c r="B94" s="4" t="inlineStr">
+      <c r="B101" s="4" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C94" s="4" t="inlineStr">
+      <c r="C101" s="4" t="inlineStr">
         <is>
           <t>티스푼 1</t>
         </is>
       </c>
-      <c r="D94" s="4" t="inlineStr">
+      <c r="D101" s="4" t="inlineStr">
         <is>
           <t>밀가루^^</t>
         </is>
       </c>
     </row>
-    <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="4" t="inlineStr">
+    <row r="102" ht="32" customHeight="1">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>노니추출물</t>
         </is>
       </c>
-      <c r="B95" s="4" t="inlineStr">
+      <c r="B102" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C95" s="4" t="inlineStr">
+      <c r="C102" s="4" t="inlineStr">
         <is>
           <t>분말들의 2배, / 마요네즈 농도로 맞춰주세요.</t>
         </is>
       </c>
-      <c r="D95" s="4" t="inlineStr">
+      <c r="D102" s="4" t="inlineStr">
         <is>
           <t>노니주스</t>
         </is>
       </c>
     </row>
-    <row r="96" ht="45" customHeight="1">
-      <c r="A96" s="4" t="inlineStr">
+    <row r="103" ht="48" customHeight="1">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>에센셜오일</t>
         </is>
       </c>
-      <c r="B96" s="4" t="inlineStr">
+      <c r="B103" s="4" t="inlineStr">
         <is>
           <t>2방울 내외</t>
         </is>
       </c>
-      <c r="C96" s="4" t="inlineStr">
+      <c r="C103" s="4" t="inlineStr">
         <is>
           <t>아래표를 참고하세요. / 좋아하거나 가지고 있는 / 오일 한가지 넣어도 됩니다.</t>
         </is>
       </c>
-      <c r="D96" s="4" t="inlineStr">
+      <c r="D103" s="4" t="inlineStr">
         <is>
           <t>아로마테라피효과 / 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="97" ht="14" customHeight="1">
-      <c r="A97" s="5" t="inlineStr">
+    <row r="104" ht="14" customHeight="1">
+      <c r="A104" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B97" s="6" t="n"/>
-      <c r="C97" s="6" t="n"/>
-      <c r="D97" s="6" t="n"/>
-    </row>
-    <row r="98" ht="240" customHeight="1">
-      <c r="A98" s="7" t="inlineStr">
+      <c r="B104" s="6" t="n"/>
+      <c r="C104" s="6" t="n"/>
+      <c r="D104" s="6" t="n"/>
+    </row>
+    <row r="105" ht="256" customHeight="1">
+      <c r="A105" s="7" t="inlineStr">
         <is>
           <t>노니는 열대지방의 과일 중 하나로
 신이 주신 열매라는 별칭이 있을 정도로
@@ -6738,18 +6765,18 @@
         </is>
       </c>
     </row>
-    <row r="99" ht="14" customHeight="1">
-      <c r="A99" s="5" t="inlineStr">
+    <row r="106" ht="14" customHeight="1">
+      <c r="A106" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B99" s="6" t="n"/>
-      <c r="C99" s="6" t="n"/>
-      <c r="D99" s="6" t="n"/>
-    </row>
-    <row r="100" ht="105" customHeight="1">
-      <c r="A100" s="7" t="inlineStr">
+      <c r="B106" s="6" t="n"/>
+      <c r="C106" s="6" t="n"/>
+      <c r="D106" s="6" t="n"/>
+    </row>
+    <row r="107" ht="112" customHeight="1">
+      <c r="A107" s="7" t="inlineStr">
         <is>
           <t>1.노니분말과 오트밀분말을 계량하고
 2. 마요네즈농도가 되도록 추출물을 넣어주세요.
@@ -6761,150 +6788,151 @@
         </is>
       </c>
     </row>
-    <row r="101" ht="14" customHeight="1">
-      <c r="A101" s="5" t="inlineStr">
+    <row r="108" ht="14" customHeight="1">
+      <c r="A108" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B101" s="6" t="n"/>
-      <c r="C101" s="6" t="n"/>
-      <c r="D101" s="6" t="n"/>
-    </row>
-    <row r="102" ht="171" customHeight="1"/>
-    <row r="103" ht="6" customHeight="1"/>
-    <row r="104" ht="22" customHeight="1">
-      <c r="A104" s="1" t="inlineStr">
+      <c r="B108" s="6" t="n"/>
+      <c r="C108" s="6" t="n"/>
+      <c r="D108" s="6" t="n"/>
+    </row>
+    <row r="109" ht="85.5" customHeight="1"/>
+    <row r="110" ht="85.5" customHeight="1"/>
+    <row r="111" ht="6" customHeight="1"/>
+    <row r="112" ht="22" customHeight="1">
+      <c r="A112" s="1" t="inlineStr">
         <is>
           <t>어성 진정 팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B104" s="2" t="n"/>
-      <c r="C104" s="2" t="n"/>
-      <c r="D104" s="2" t="n"/>
-    </row>
-    <row r="105" ht="15" customHeight="1">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="B112" s="2" t="n"/>
+      <c r="C112" s="2" t="n"/>
+      <c r="D112" s="2" t="n"/>
+    </row>
+    <row r="113" ht="15" customHeight="1">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B105" s="3" t="inlineStr">
+      <c r="B113" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C105" s="3" t="inlineStr">
+      <c r="C113" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D105" s="3" t="inlineStr">
+      <c r="D113" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="106" ht="45" customHeight="1">
-      <c r="A106" s="8" t="inlineStr">
+    <row r="114" ht="48" customHeight="1">
+      <c r="A114" s="8" t="inlineStr">
         <is>
           <t>어성초분말</t>
         </is>
       </c>
-      <c r="B106" s="8" t="inlineStr">
+      <c r="B114" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C106" s="8" t="inlineStr">
+      <c r="C114" s="8" t="inlineStr">
         <is>
           <t>티스푼 1</t>
         </is>
       </c>
-      <c r="D106" s="8" t="inlineStr">
+      <c r="D114" s="8" t="inlineStr">
         <is>
           <t>녹차, 병풀, 알란토인,카렌듈라추출물, 유기농 프레쉬 5솔루션 등</t>
         </is>
       </c>
     </row>
-    <row r="107" ht="15" customHeight="1">
-      <c r="A107" s="8" t="inlineStr">
+    <row r="115" ht="16" customHeight="1">
+      <c r="A115" s="8" t="inlineStr">
         <is>
           <t>오트밀분말</t>
         </is>
       </c>
-      <c r="B107" s="8" t="inlineStr">
+      <c r="B115" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C107" s="8" t="inlineStr">
+      <c r="C115" s="8" t="inlineStr">
         <is>
           <t>티스푼 1</t>
         </is>
       </c>
-      <c r="D107" s="8" t="inlineStr">
+      <c r="D115" s="8" t="inlineStr">
         <is>
           <t>밀가루^^</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="8" t="inlineStr">
+    <row r="116" ht="32" customHeight="1">
+      <c r="A116" s="8" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
-      <c r="B108" s="8" t="inlineStr">
+      <c r="B116" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C108" s="8" t="inlineStr">
+      <c r="C116" s="8" t="inlineStr">
         <is>
           <t>분말들의 2배, / 마요네즈 농도로 맞춰주세요.</t>
         </is>
       </c>
-      <c r="D108" s="8" t="inlineStr">
+      <c r="D116" s="8" t="inlineStr">
         <is>
           <t>정제수, / 로즈워터 등</t>
         </is>
       </c>
     </row>
-    <row r="109" ht="60" customHeight="1">
-      <c r="A109" s="8" t="inlineStr">
+    <row r="117" ht="64" customHeight="1">
+      <c r="A117" s="8" t="inlineStr">
         <is>
           <t>(라벤더) / 에센셜오일</t>
         </is>
       </c>
-      <c r="B109" s="8" t="inlineStr">
+      <c r="B117" s="8" t="inlineStr">
         <is>
           <t>0~2방울</t>
         </is>
       </c>
-      <c r="C109" s="8" t="inlineStr">
+      <c r="C117" s="8" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="D109" s="8" t="inlineStr">
+      <c r="D117" s="8" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="110" ht="14" customHeight="1">
-      <c r="A110" s="5" t="inlineStr">
+    <row r="118" ht="14" customHeight="1">
+      <c r="A118" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B110" s="6" t="n"/>
-      <c r="C110" s="6" t="n"/>
-      <c r="D110" s="6" t="n"/>
-    </row>
-    <row r="111" ht="360" customHeight="1">
-      <c r="A111" s="9" t="inlineStr">
+      <c r="B118" s="6" t="n"/>
+      <c r="C118" s="6" t="n"/>
+      <c r="D118" s="6" t="n"/>
+    </row>
+    <row r="119" ht="384" customHeight="1">
+      <c r="A119" s="9" t="inlineStr">
         <is>
           <t>무제 문서
 어성초 =약모밀
@@ -6932,22 +6960,22 @@
 만들기 과정 *1회분량입니다. 팩할 때마다 만들어주세요.</t>
         </is>
       </c>
-      <c r="B111" s="10" t="n"/>
-      <c r="C111" s="10" t="n"/>
-      <c r="D111" s="10" t="n"/>
-    </row>
-    <row r="112" ht="14" customHeight="1">
-      <c r="A112" s="5" t="inlineStr">
+      <c r="B119" s="10" t="n"/>
+      <c r="C119" s="10" t="n"/>
+      <c r="D119" s="10" t="n"/>
+    </row>
+    <row r="120" ht="14" customHeight="1">
+      <c r="A120" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B112" s="6" t="n"/>
-      <c r="C112" s="6" t="n"/>
-      <c r="D112" s="6" t="n"/>
-    </row>
-    <row r="113" ht="135" customHeight="1">
-      <c r="A113" s="9" t="inlineStr">
+      <c r="B120" s="6" t="n"/>
+      <c r="C120" s="6" t="n"/>
+      <c r="D120" s="6" t="n"/>
+    </row>
+    <row r="121" ht="144" customHeight="1">
+      <c r="A121" s="9" t="inlineStr">
         <is>
           <t>1.어성초분말과 오트밀분말을
 계량하고
@@ -6960,221 +6988,227 @@
 6. 씻어주세요. 너무 오랫동안 있으면오히려 피부에 자극이 될 수 있어요.</t>
         </is>
       </c>
-      <c r="B113" s="10" t="n"/>
-      <c r="C113" s="10" t="n"/>
-      <c r="D113" s="10" t="n"/>
-    </row>
-    <row r="114" ht="14" customHeight="1">
-      <c r="A114" s="5" t="inlineStr">
+      <c r="B121" s="10" t="n"/>
+      <c r="C121" s="10" t="n"/>
+      <c r="D121" s="10" t="n"/>
+    </row>
+    <row r="122" ht="14" customHeight="1">
+      <c r="A122" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B114" s="6" t="n"/>
-      <c r="C114" s="6" t="n"/>
-      <c r="D114" s="6" t="n"/>
-    </row>
-    <row r="115" ht="171" customHeight="1">
-      <c r="A115" s="10" t="n"/>
-      <c r="B115" s="10" t="n"/>
-      <c r="C115" s="10" t="n"/>
-      <c r="D115" s="10" t="n"/>
-    </row>
-    <row r="116" ht="6" customHeight="1"/>
-    <row r="117" ht="22" customHeight="1">
-      <c r="A117" s="1" t="inlineStr">
+      <c r="B122" s="6" t="n"/>
+      <c r="C122" s="6" t="n"/>
+      <c r="D122" s="6" t="n"/>
+    </row>
+    <row r="123" ht="85.5" customHeight="1">
+      <c r="A123" s="10" t="n"/>
+      <c r="B123" s="10" t="n"/>
+      <c r="C123" s="10" t="n"/>
+      <c r="D123" s="10" t="n"/>
+    </row>
+    <row r="124" ht="85.5" customHeight="1">
+      <c r="A124" s="10" t="n"/>
+      <c r="B124" s="10" t="n"/>
+      <c r="C124" s="10" t="n"/>
+      <c r="D124" s="10" t="n"/>
+    </row>
+    <row r="125" ht="6" customHeight="1"/>
+    <row r="126" ht="22" customHeight="1">
+      <c r="A126" s="1" t="inlineStr">
         <is>
           <t>보톡스 수면팩    [오일류]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B117" s="2" t="n"/>
-      <c r="C117" s="2" t="n"/>
-      <c r="D117" s="2" t="n"/>
-    </row>
-    <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="B126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n"/>
+    </row>
+    <row r="127" ht="15" customHeight="1">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B118" s="3" t="inlineStr">
+      <c r="B127" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C118" s="3" t="inlineStr">
+      <c r="C127" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D118" s="3" t="inlineStr">
+      <c r="D127" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="119" ht="45" customHeight="1">
-      <c r="A119" s="4" t="inlineStr">
+    <row r="128" ht="48" customHeight="1">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t>캐모마일인퓨즈오일</t>
         </is>
       </c>
-      <c r="B119" s="4" t="inlineStr">
+      <c r="B128" s="4" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C119" s="4" t="inlineStr">
+      <c r="C128" s="4" t="inlineStr">
         <is>
           <t>인퓨즈오일, 오일에 캐모마일드라이허브를 담군 후 유효성분을 우려냄.</t>
         </is>
       </c>
-      <c r="D119" s="4" t="inlineStr">
+      <c r="D128" s="4" t="inlineStr">
         <is>
           <t>햄프씨드오일, 보리지,달맞이,동백, 카렌듈라, 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="120" ht="45" customHeight="1">
-      <c r="A120" s="4" t="inlineStr">
+    <row r="129" ht="48" customHeight="1">
+      <c r="A129" s="4" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B120" s="4" t="inlineStr">
+      <c r="B129" s="4" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C120" s="4" t="inlineStr">
+      <c r="C129" s="4" t="inlineStr">
         <is>
           <t>오일과 물의 분리를 저지, 올리브오일 유래</t>
         </is>
       </c>
-      <c r="D120" s="4" t="inlineStr">
+      <c r="D129" s="4" t="inlineStr">
         <is>
           <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="121" ht="60" customHeight="1">
-      <c r="A121" s="4" t="inlineStr">
+    <row r="130" ht="64" customHeight="1">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B121" s="4" t="inlineStr">
+      <c r="B130" s="4" t="inlineStr">
         <is>
           <t>75g</t>
         </is>
       </c>
-      <c r="C121" s="4" t="inlineStr">
+      <c r="C130" s="4" t="inlineStr">
         <is>
           <t>자체 점증, 보습, 수분공급</t>
         </is>
       </c>
-      <c r="D121" s="4" t="inlineStr">
+      <c r="D130" s="4" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="122" ht="30" customHeight="1">
-      <c r="A122" s="4" t="inlineStr">
+    <row r="131" ht="32" customHeight="1">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>세라마이드리퀴드 / (수용성)</t>
         </is>
       </c>
-      <c r="B122" s="4" t="inlineStr">
+      <c r="B131" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C122" s="4" t="inlineStr">
+      <c r="C131" s="4" t="inlineStr">
         <is>
           <t>피부보호막, 촉촉함이 오래오래</t>
         </is>
       </c>
-      <c r="D122" s="4" t="n"/>
-    </row>
-    <row r="123" ht="30" customHeight="1">
-      <c r="A123" s="4" t="inlineStr">
+      <c r="D131" s="4" t="n"/>
+    </row>
+    <row r="132" ht="32" customHeight="1">
+      <c r="A132" s="4" t="inlineStr">
         <is>
           <t>보톡스펩타이드</t>
         </is>
       </c>
-      <c r="B123" s="4" t="inlineStr">
+      <c r="B132" s="4" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C123" s="4" t="inlineStr">
+      <c r="C132" s="4" t="inlineStr">
         <is>
           <t>헥사펩타이드, / 보톡스와 같이 노화,탄력관리 펩타이드</t>
         </is>
       </c>
-      <c r="D123" s="4" t="inlineStr">
+      <c r="D132" s="4" t="inlineStr">
         <is>
           <t>아데노신, / EGF등</t>
         </is>
       </c>
     </row>
-    <row r="124" ht="45" customHeight="1">
-      <c r="A124" s="4" t="inlineStr">
+    <row r="133" ht="48" customHeight="1">
+      <c r="A133" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B124" s="4" t="inlineStr">
+      <c r="B133" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C124" s="4" t="inlineStr">
+      <c r="C133" s="4" t="inlineStr">
         <is>
           <t>균번식억제</t>
         </is>
       </c>
-      <c r="D124" s="4" t="inlineStr">
+      <c r="D133" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (알로에베라겔의 양을 74g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="125" ht="30" customHeight="1">
-      <c r="A125" s="4" t="inlineStr">
+    <row r="134" ht="32" customHeight="1">
+      <c r="A134" s="4" t="inlineStr">
         <is>
           <t>라벤더에센셜오일</t>
         </is>
       </c>
-      <c r="B125" s="4" t="inlineStr">
+      <c r="B134" s="4" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C125" s="4" t="inlineStr">
+      <c r="C134" s="4" t="inlineStr">
         <is>
           <t>숙면,진정, 아로마테라피효과</t>
         </is>
       </c>
-      <c r="D125" s="4" t="inlineStr">
+      <c r="D134" s="4" t="inlineStr">
         <is>
           <t>오렌지, 로먼카모마일EO등</t>
         </is>
       </c>
     </row>
-    <row r="126" ht="14" customHeight="1">
-      <c r="A126" s="5" t="inlineStr">
+    <row r="135" ht="14" customHeight="1">
+      <c r="A135" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B126" s="6" t="n"/>
-      <c r="C126" s="6" t="n"/>
-      <c r="D126" s="6" t="n"/>
-    </row>
-    <row r="127" ht="240" customHeight="1">
-      <c r="A127" s="7" t="inlineStr">
+      <c r="B135" s="6" t="n"/>
+      <c r="C135" s="6" t="n"/>
+      <c r="D135" s="6" t="n"/>
+    </row>
+    <row r="136" ht="256" customHeight="1">
+      <c r="A136" s="7" t="inlineStr">
         <is>
           <t>팩이라고하면 얼굴에 붙이는 시트마스크를 떠올리는데
 붙인 상태에서 잠시지만 자연스러운 생활이 불가능하고 시간이 지난 후 간단 클렌징을 해야합니다.
@@ -7193,18 +7227,18 @@
         </is>
       </c>
     </row>
-    <row r="128" ht="14" customHeight="1">
-      <c r="A128" s="5" t="inlineStr">
+    <row r="137" ht="14" customHeight="1">
+      <c r="A137" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B128" s="6" t="n"/>
-      <c r="C128" s="6" t="n"/>
-      <c r="D128" s="6" t="n"/>
-    </row>
-    <row r="129" ht="120" customHeight="1">
-      <c r="A129" s="7" t="inlineStr">
+      <c r="B137" s="6" t="n"/>
+      <c r="C137" s="6" t="n"/>
+      <c r="D137" s="6" t="n"/>
+    </row>
+    <row r="138" ht="128" customHeight="1">
+      <c r="A138" s="7" t="inlineStr">
         <is>
           <t>만들기과정
 1.알로에모이스트와 오일/유화제를 계량합니다.
@@ -7216,172 +7250,173 @@
         </is>
       </c>
     </row>
-    <row r="130" ht="14" customHeight="1">
-      <c r="A130" s="5" t="inlineStr">
+    <row r="139" ht="14" customHeight="1">
+      <c r="A139" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B130" s="6" t="n"/>
-      <c r="C130" s="6" t="n"/>
-      <c r="D130" s="6" t="n"/>
-    </row>
-    <row r="131" ht="171" customHeight="1"/>
-    <row r="132" ht="6" customHeight="1"/>
-    <row r="133" ht="22" customHeight="1">
-      <c r="A133" s="1" t="inlineStr">
+      <c r="B139" s="6" t="n"/>
+      <c r="C139" s="6" t="n"/>
+      <c r="D139" s="6" t="n"/>
+    </row>
+    <row r="140" ht="85.5" customHeight="1"/>
+    <row r="141" ht="85.5" customHeight="1"/>
+    <row r="142" ht="6" customHeight="1"/>
+    <row r="143" ht="22" customHeight="1">
+      <c r="A143" s="1" t="inlineStr">
         <is>
           <t>슈퍼아쿠아 에센스/마스크팩(트러블용)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B133" s="2" t="n"/>
-      <c r="C133" s="2" t="n"/>
-      <c r="D133" s="2" t="n"/>
-    </row>
-    <row r="134" ht="15" customHeight="1">
-      <c r="A134" s="3" t="inlineStr">
+      <c r="B143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n"/>
+    </row>
+    <row r="144" ht="15" customHeight="1">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B134" s="3" t="inlineStr">
+      <c r="B144" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C134" s="3" t="inlineStr">
+      <c r="C144" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D134" s="3" t="inlineStr">
+      <c r="D144" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="135" ht="30" customHeight="1">
-      <c r="A135" s="8" t="inlineStr">
+    <row r="145" ht="32" customHeight="1">
+      <c r="A145" s="8" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔</t>
         </is>
       </c>
-      <c r="B135" s="8" t="inlineStr">
+      <c r="B145" s="8" t="inlineStr">
         <is>
           <t>60g</t>
         </is>
       </c>
-      <c r="C135" s="8" t="inlineStr">
+      <c r="C145" s="8" t="inlineStr">
         <is>
           <t>수분공급,젤타입, 자체점도, 점도조절제역할 ,진정</t>
         </is>
       </c>
-      <c r="D135" s="8" t="inlineStr">
+      <c r="D145" s="8" t="inlineStr">
         <is>
           <t>로즈플라워겔, / 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="136" ht="30" customHeight="1">
-      <c r="A136" s="8" t="inlineStr">
+    <row r="146" ht="32" customHeight="1">
+      <c r="A146" s="8" t="inlineStr">
         <is>
           <t>편백워터</t>
         </is>
       </c>
-      <c r="B136" s="8" t="inlineStr">
+      <c r="B146" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C136" s="8" t="inlineStr">
+      <c r="C146" s="8" t="inlineStr">
         <is>
           <t>여드름, 트러블 피부에 좋은 편백를 수증기증류법.</t>
         </is>
       </c>
-      <c r="D136" s="8" t="inlineStr">
+      <c r="D146" s="8" t="inlineStr">
         <is>
           <t>위치헤이즐워터</t>
         </is>
       </c>
     </row>
-    <row r="137" ht="15" customHeight="1">
-      <c r="A137" s="8" t="inlineStr">
+    <row r="147" ht="16" customHeight="1">
+      <c r="A147" s="8" t="inlineStr">
         <is>
           <t>진한 ~어성초추출물</t>
         </is>
       </c>
-      <c r="B137" s="8" t="inlineStr">
+      <c r="B147" s="8" t="inlineStr">
         <is>
           <t>18g</t>
         </is>
       </c>
-      <c r="C137" s="8" t="inlineStr">
+      <c r="C147" s="8" t="inlineStr">
         <is>
           <t>트러블진정 등</t>
         </is>
       </c>
-      <c r="D137" s="8" t="inlineStr">
+      <c r="D147" s="8" t="inlineStr">
         <is>
           <t>카렌듈라추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="138" ht="15" customHeight="1">
-      <c r="A138" s="8" t="inlineStr">
+    <row r="148" ht="16" customHeight="1">
+      <c r="A148" s="8" t="inlineStr">
         <is>
           <t>진한~녹차추출물</t>
         </is>
       </c>
-      <c r="B138" s="8" t="inlineStr">
+      <c r="B148" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C138" s="8" t="inlineStr">
+      <c r="C148" s="8" t="inlineStr">
         <is>
           <t>다량의 폴리페놀성분, 진정</t>
         </is>
       </c>
-      <c r="D138" s="8" t="inlineStr">
+      <c r="D148" s="8" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
     </row>
-    <row r="139" ht="45" customHeight="1">
-      <c r="A139" s="8" t="inlineStr">
+    <row r="149" ht="48" customHeight="1">
+      <c r="A149" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B139" s="8" t="inlineStr">
+      <c r="B149" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C139" s="8" t="inlineStr">
+      <c r="C149" s="8" t="inlineStr">
         <is>
           <t>복합균번식억제제</t>
         </is>
       </c>
-      <c r="D139" s="8" t="inlineStr">
+      <c r="D149" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (편백워터의 양을 9g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="140" ht="14" customHeight="1">
-      <c r="A140" s="5" t="inlineStr">
+    <row r="150" ht="14" customHeight="1">
+      <c r="A150" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B140" s="6" t="n"/>
-      <c r="C140" s="6" t="n"/>
-      <c r="D140" s="6" t="n"/>
-    </row>
-    <row r="141" ht="135" customHeight="1">
-      <c r="A141" s="9" t="inlineStr">
+      <c r="B150" s="6" t="n"/>
+      <c r="C150" s="6" t="n"/>
+      <c r="D150" s="6" t="n"/>
+    </row>
+    <row r="151" ht="144" customHeight="1">
+      <c r="A151" s="9" t="inlineStr">
         <is>
           <t>어떤 제품을 발라도 피부에 변화가 느껴지지 않을 때가 있습니다. 이는 피부가 집중 케어를 원한다는
 신호인데요.. 이때 손쉽게 선택할 수 있는 것이 시트 마스크. 피부가 당기거나 각질이 일어났을 때 짧은
@@ -7392,22 +7427,22 @@
 유지할 수 있습니다.</t>
         </is>
       </c>
-      <c r="B141" s="10" t="n"/>
-      <c r="C141" s="10" t="n"/>
-      <c r="D141" s="10" t="n"/>
-    </row>
-    <row r="142" ht="14" customHeight="1">
-      <c r="A142" s="5" t="inlineStr">
+      <c r="B151" s="10" t="n"/>
+      <c r="C151" s="10" t="n"/>
+      <c r="D151" s="10" t="n"/>
+    </row>
+    <row r="152" ht="14" customHeight="1">
+      <c r="A152" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B142" s="6" t="n"/>
-      <c r="C142" s="6" t="n"/>
-      <c r="D142" s="6" t="n"/>
-    </row>
-    <row r="143" ht="225" customHeight="1">
-      <c r="A143" s="9" t="inlineStr">
+      <c r="B152" s="6" t="n"/>
+      <c r="C152" s="6" t="n"/>
+      <c r="D152" s="6" t="n"/>
+    </row>
+    <row r="153" ht="240" customHeight="1">
+      <c r="A153" s="9" t="inlineStr">
         <is>
           <t>만들기과정
 1.알로에모이스트를 계량하고
@@ -7425,203 +7460,209 @@
 5.주2~3회 마스팩을 10~15분간 하면 촉촉한 피부를 유지할 수 있다.</t>
         </is>
       </c>
-      <c r="B143" s="10" t="n"/>
-      <c r="C143" s="10" t="n"/>
-      <c r="D143" s="10" t="n"/>
-    </row>
-    <row r="144" ht="14" customHeight="1">
-      <c r="A144" s="5" t="inlineStr">
+      <c r="B153" s="10" t="n"/>
+      <c r="C153" s="10" t="n"/>
+      <c r="D153" s="10" t="n"/>
+    </row>
+    <row r="154" ht="14" customHeight="1">
+      <c r="A154" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B144" s="6" t="n"/>
-      <c r="C144" s="6" t="n"/>
-      <c r="D144" s="6" t="n"/>
-    </row>
-    <row r="145" ht="171" customHeight="1">
-      <c r="A145" s="10" t="n"/>
-      <c r="B145" s="10" t="n"/>
-      <c r="C145" s="10" t="n"/>
-      <c r="D145" s="10" t="n"/>
-    </row>
-    <row r="146" ht="6" customHeight="1"/>
-    <row r="147" ht="22" customHeight="1">
-      <c r="A147" s="1" t="inlineStr">
+      <c r="B154" s="6" t="n"/>
+      <c r="C154" s="6" t="n"/>
+      <c r="D154" s="6" t="n"/>
+    </row>
+    <row r="155" ht="85.5" customHeight="1">
+      <c r="A155" s="10" t="n"/>
+      <c r="B155" s="10" t="n"/>
+      <c r="C155" s="10" t="n"/>
+      <c r="D155" s="10" t="n"/>
+    </row>
+    <row r="156" ht="85.5" customHeight="1">
+      <c r="A156" s="10" t="n"/>
+      <c r="B156" s="10" t="n"/>
+      <c r="C156" s="10" t="n"/>
+      <c r="D156" s="10" t="n"/>
+    </row>
+    <row r="157" ht="6" customHeight="1"/>
+    <row r="158" ht="22" customHeight="1">
+      <c r="A158" s="1" t="inlineStr">
         <is>
           <t>슈퍼아쿠아 에센스/마스크팩(화이트)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B147" s="2" t="n"/>
-      <c r="C147" s="2" t="n"/>
-      <c r="D147" s="2" t="n"/>
-    </row>
-    <row r="148" ht="15" customHeight="1">
-      <c r="A148" s="3" t="inlineStr">
+      <c r="B158" s="2" t="n"/>
+      <c r="C158" s="2" t="n"/>
+      <c r="D158" s="2" t="n"/>
+    </row>
+    <row r="159" ht="15" customHeight="1">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B148" s="3" t="inlineStr">
+      <c r="B159" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C148" s="3" t="inlineStr">
+      <c r="C159" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D148" s="3" t="inlineStr">
+      <c r="D159" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="149" ht="30" customHeight="1">
-      <c r="A149" s="4" t="inlineStr">
+    <row r="160" ht="32" customHeight="1">
+      <c r="A160" s="4" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔</t>
         </is>
       </c>
-      <c r="B149" s="4" t="inlineStr">
+      <c r="B160" s="4" t="inlineStr">
         <is>
           <t>50g</t>
         </is>
       </c>
-      <c r="C149" s="4" t="inlineStr">
+      <c r="C160" s="4" t="inlineStr">
         <is>
           <t>수분공급, 진정, 젤타입, 자체점도</t>
         </is>
       </c>
-      <c r="D149" s="4" t="inlineStr">
+      <c r="D160" s="4" t="inlineStr">
         <is>
           <t>로즈플라워겔. / 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="4" t="inlineStr">
+    <row r="161" ht="16" customHeight="1">
+      <c r="A161" s="4" t="inlineStr">
         <is>
           <t>네롤리워터</t>
         </is>
       </c>
-      <c r="B150" s="4" t="inlineStr">
+      <c r="B161" s="4" t="inlineStr">
         <is>
           <t>16g</t>
         </is>
       </c>
-      <c r="C150" s="4" t="inlineStr">
+      <c r="C161" s="4" t="inlineStr">
         <is>
           <t>오렌지꽃 수증기추출, 진정</t>
         </is>
       </c>
-      <c r="D150" s="4" t="inlineStr">
+      <c r="D161" s="4" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
     </row>
-    <row r="151" ht="30" customHeight="1">
-      <c r="A151" s="4" t="inlineStr">
+    <row r="162" ht="32" customHeight="1">
+      <c r="A162" s="4" t="inlineStr">
         <is>
           <t>화이텐스</t>
         </is>
       </c>
-      <c r="B151" s="4" t="inlineStr">
+      <c r="B162" s="4" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C151" s="4" t="inlineStr">
+      <c r="C162" s="4" t="inlineStr">
         <is>
           <t>상황버섯,노란만병초, 프로폴리스 등 복합추출물</t>
         </is>
       </c>
-      <c r="D151" s="4" t="inlineStr">
+      <c r="D162" s="4" t="inlineStr">
         <is>
           <t>감초, 녹차, 오이추출물 등</t>
         </is>
       </c>
     </row>
-    <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="4" t="inlineStr">
+    <row r="163" ht="16" customHeight="1">
+      <c r="A163" s="4" t="inlineStr">
         <is>
           <t>상백피추출물</t>
         </is>
       </c>
-      <c r="B152" s="4" t="inlineStr">
+      <c r="B163" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C152" s="4" t="inlineStr">
+      <c r="C163" s="4" t="inlineStr">
         <is>
           <t>뽕나무뿌리껍질 추출성분</t>
         </is>
       </c>
-      <c r="D152" s="4" t="inlineStr">
+      <c r="D163" s="4" t="inlineStr">
         <is>
           <t>감초, 녹차추출물</t>
         </is>
       </c>
     </row>
-    <row r="153" ht="60" customHeight="1">
-      <c r="A153" s="4" t="inlineStr">
+    <row r="164" ht="64" customHeight="1">
+      <c r="A164" s="4" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
-      <c r="B153" s="4" t="inlineStr">
+      <c r="B164" s="4" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C153" s="4" t="inlineStr">
+      <c r="C164" s="4" t="inlineStr">
         <is>
           <t>고보습, 점도조절</t>
         </is>
       </c>
-      <c r="D153" s="4" t="inlineStr">
+      <c r="D164" s="4" t="inlineStr">
         <is>
           <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
         </is>
       </c>
     </row>
-    <row r="154" ht="45" customHeight="1">
-      <c r="A154" s="4" t="inlineStr">
+    <row r="165" ht="48" customHeight="1">
+      <c r="A165" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B154" s="4" t="inlineStr">
+      <c r="B165" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C154" s="4" t="inlineStr">
+      <c r="C165" s="4" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="D154" s="4" t="inlineStr">
+      <c r="D165" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (네롤리워터의 양을 15g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="155" ht="14" customHeight="1">
-      <c r="A155" s="5" t="inlineStr">
+    <row r="166" ht="14" customHeight="1">
+      <c r="A166" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B155" s="6" t="n"/>
-      <c r="C155" s="6" t="n"/>
-      <c r="D155" s="6" t="n"/>
-    </row>
-    <row r="156" ht="210" customHeight="1">
-      <c r="A156" s="7" t="inlineStr">
+      <c r="B166" s="6" t="n"/>
+      <c r="C166" s="6" t="n"/>
+      <c r="D166" s="6" t="n"/>
+    </row>
+    <row r="167" ht="224" customHeight="1">
+      <c r="A167" s="7" t="inlineStr">
         <is>
           <t>어떤 제품을 발라도 피부에 변화가 느껴지지 않을 때가 있습니다. 이는 피부가 집중 케어를 원한다는
 신호인데요.. 이때 손쉽게 선택할 수 있는 것이 시트 마스크. 피부가 당기거나 각질이 일어났을 때 짧은
@@ -7638,18 +7679,18 @@
         </is>
       </c>
     </row>
-    <row r="157" ht="14" customHeight="1">
-      <c r="A157" s="5" t="inlineStr">
+    <row r="168" ht="14" customHeight="1">
+      <c r="A168" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B157" s="6" t="n"/>
-      <c r="C157" s="6" t="n"/>
-      <c r="D157" s="6" t="n"/>
-    </row>
-    <row r="158" ht="225" customHeight="1">
-      <c r="A158" s="7" t="inlineStr">
+      <c r="B168" s="6" t="n"/>
+      <c r="C168" s="6" t="n"/>
+      <c r="D168" s="6" t="n"/>
+    </row>
+    <row r="169" ht="240" customHeight="1">
+      <c r="A169" s="7" t="inlineStr">
         <is>
           <t>만들기과정
 1.알로에모이스트를 계량하고
@@ -7668,172 +7709,173 @@
         </is>
       </c>
     </row>
-    <row r="159" ht="14" customHeight="1">
-      <c r="A159" s="5" t="inlineStr">
+    <row r="170" ht="14" customHeight="1">
+      <c r="A170" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B159" s="6" t="n"/>
-      <c r="C159" s="6" t="n"/>
-      <c r="D159" s="6" t="n"/>
-    </row>
-    <row r="160" ht="171" customHeight="1"/>
-    <row r="161" ht="6" customHeight="1"/>
-    <row r="162" ht="22" customHeight="1">
-      <c r="A162" s="1" t="inlineStr">
+      <c r="B170" s="6" t="n"/>
+      <c r="C170" s="6" t="n"/>
+      <c r="D170" s="6" t="n"/>
+    </row>
+    <row r="171" ht="85.5" customHeight="1"/>
+    <row r="172" ht="85.5" customHeight="1"/>
+    <row r="173" ht="6" customHeight="1"/>
+    <row r="174" ht="22" customHeight="1">
+      <c r="A174" s="1" t="inlineStr">
         <is>
           <t>슈퍼아쿠아 에센스/마스크팩(건성노화)    ↗ 원본</t>
         </is>
       </c>
-      <c r="B162" s="2" t="n"/>
-      <c r="C162" s="2" t="n"/>
-      <c r="D162" s="2" t="n"/>
-    </row>
-    <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="3" t="inlineStr">
+      <c r="B174" s="2" t="n"/>
+      <c r="C174" s="2" t="n"/>
+      <c r="D174" s="2" t="n"/>
+    </row>
+    <row r="175" ht="15" customHeight="1">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B163" s="3" t="inlineStr">
+      <c r="B175" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C163" s="3" t="inlineStr">
+      <c r="C175" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D163" s="3" t="inlineStr">
+      <c r="D175" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="164" ht="60" customHeight="1">
-      <c r="A164" s="8" t="inlineStr">
+    <row r="176" ht="64" customHeight="1">
+      <c r="A176" s="8" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
-      <c r="B164" s="8" t="inlineStr">
+      <c r="B176" s="8" t="inlineStr">
         <is>
           <t>30g</t>
         </is>
       </c>
-      <c r="C164" s="8" t="inlineStr">
+      <c r="C176" s="8" t="inlineStr">
         <is>
           <t>고보습, 점도조절</t>
         </is>
       </c>
-      <c r="D164" s="8" t="inlineStr">
+      <c r="D176" s="8" t="inlineStr">
         <is>
           <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
         </is>
       </c>
     </row>
-    <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="8" t="inlineStr">
+    <row r="177" ht="16" customHeight="1">
+      <c r="A177" s="8" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B165" s="8" t="inlineStr">
+      <c r="B177" s="8" t="inlineStr">
         <is>
           <t>51g</t>
         </is>
       </c>
-      <c r="C165" s="8" t="inlineStr">
+      <c r="C177" s="8" t="inlineStr">
         <is>
           <t>장미꽃잎 수증기추출, 진정</t>
         </is>
       </c>
-      <c r="D165" s="8" t="inlineStr">
+      <c r="D177" s="8" t="inlineStr">
         <is>
           <t>네롤리워터</t>
         </is>
       </c>
     </row>
-    <row r="166" ht="30" customHeight="1">
-      <c r="A166" s="8" t="inlineStr">
+    <row r="178" ht="32" customHeight="1">
+      <c r="A178" s="8" t="inlineStr">
         <is>
           <t>아카시아콜라겐</t>
         </is>
       </c>
-      <c r="B166" s="8" t="inlineStr">
+      <c r="B178" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C166" s="8" t="inlineStr">
+      <c r="C178" s="8" t="inlineStr">
         <is>
           <t>아카시아꽃추출 콜라겐</t>
         </is>
       </c>
-      <c r="D166" s="8" t="inlineStr">
+      <c r="D178" s="8" t="inlineStr">
         <is>
           <t>콜라겐, 마린콜라겐,식물성 플라센타 등</t>
         </is>
       </c>
     </row>
-    <row r="167" ht="30" customHeight="1">
-      <c r="A167" s="8" t="inlineStr">
+    <row r="179" ht="32" customHeight="1">
+      <c r="A179" s="8" t="inlineStr">
         <is>
           <t>아데노신</t>
         </is>
       </c>
-      <c r="B167" s="8" t="inlineStr">
+      <c r="B179" s="8" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C167" s="8" t="inlineStr">
+      <c r="C179" s="8" t="inlineStr">
         <is>
           <t>식약청고시 노화탄력성분.</t>
         </is>
       </c>
-      <c r="D167" s="8" t="inlineStr">
+      <c r="D179" s="8" t="inlineStr">
         <is>
           <t>EGF, 아세틸헥사펩타이드,달팽이추출물등</t>
         </is>
       </c>
     </row>
-    <row r="168" ht="45" customHeight="1">
-      <c r="A168" s="8" t="inlineStr">
+    <row r="180" ht="48" customHeight="1">
+      <c r="A180" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B168" s="8" t="inlineStr">
+      <c r="B180" s="8" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C168" s="8" t="inlineStr">
+      <c r="C180" s="8" t="inlineStr">
         <is>
           <t>균번식억제</t>
         </is>
       </c>
-      <c r="D168" s="8" t="inlineStr">
+      <c r="D180" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (로즈워터의 양을 50g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="169" ht="14" customHeight="1">
-      <c r="A169" s="5" t="inlineStr">
+    <row r="181" ht="14" customHeight="1">
+      <c r="A181" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B169" s="6" t="n"/>
-      <c r="C169" s="6" t="n"/>
-      <c r="D169" s="6" t="n"/>
-    </row>
-    <row r="170" ht="195" customHeight="1">
-      <c r="A170" s="9" t="inlineStr">
+      <c r="B181" s="6" t="n"/>
+      <c r="C181" s="6" t="n"/>
+      <c r="D181" s="6" t="n"/>
+    </row>
+    <row r="182" ht="208" customHeight="1">
+      <c r="A182" s="9" t="inlineStr">
         <is>
           <t>어떤 제품을 발라도 피부에 변화가 느껴지지 않을 때가 있습니다.
 이는 피부가 집중 케어를 원한다는 신호인데요..
@@ -7850,22 +7892,22 @@
 유지할 수 있습니다.</t>
         </is>
       </c>
-      <c r="B170" s="10" t="n"/>
-      <c r="C170" s="10" t="n"/>
-      <c r="D170" s="10" t="n"/>
-    </row>
-    <row r="171" ht="14" customHeight="1">
-      <c r="A171" s="5" t="inlineStr">
+      <c r="B182" s="10" t="n"/>
+      <c r="C182" s="10" t="n"/>
+      <c r="D182" s="10" t="n"/>
+    </row>
+    <row r="183" ht="14" customHeight="1">
+      <c r="A183" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B171" s="6" t="n"/>
-      <c r="C171" s="6" t="n"/>
-      <c r="D171" s="6" t="n"/>
-    </row>
-    <row r="172" ht="180" customHeight="1">
-      <c r="A172" s="9" t="inlineStr">
+      <c r="B183" s="6" t="n"/>
+      <c r="C183" s="6" t="n"/>
+      <c r="D183" s="6" t="n"/>
+    </row>
+    <row r="184" ht="192" customHeight="1">
+      <c r="A184" s="9" t="inlineStr">
         <is>
           <t>만들기과정
 1.히아루론산을 계량하고
@@ -7877,181 +7919,187 @@
 5.주2~3회 마스팩을 10~15분간 하면 촉촉한 피부를 유지할 수 있다.</t>
         </is>
       </c>
-      <c r="B172" s="10" t="n"/>
-      <c r="C172" s="10" t="n"/>
-      <c r="D172" s="10" t="n"/>
-    </row>
-    <row r="173" ht="14" customHeight="1">
-      <c r="A173" s="5" t="inlineStr">
+      <c r="B184" s="10" t="n"/>
+      <c r="C184" s="10" t="n"/>
+      <c r="D184" s="10" t="n"/>
+    </row>
+    <row r="185" ht="14" customHeight="1">
+      <c r="A185" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B173" s="6" t="n"/>
-      <c r="C173" s="6" t="n"/>
-      <c r="D173" s="6" t="n"/>
-    </row>
-    <row r="174" ht="171" customHeight="1">
-      <c r="A174" s="10" t="n"/>
-      <c r="B174" s="10" t="n"/>
-      <c r="C174" s="10" t="n"/>
-      <c r="D174" s="10" t="n"/>
-    </row>
-    <row r="175" ht="6" customHeight="1"/>
-    <row r="176" ht="22" customHeight="1">
-      <c r="A176" s="1" t="inlineStr">
+      <c r="B185" s="6" t="n"/>
+      <c r="C185" s="6" t="n"/>
+      <c r="D185" s="6" t="n"/>
+    </row>
+    <row r="186" ht="85.5" customHeight="1">
+      <c r="A186" s="10" t="n"/>
+      <c r="B186" s="10" t="n"/>
+      <c r="C186" s="10" t="n"/>
+      <c r="D186" s="10" t="n"/>
+    </row>
+    <row r="187" ht="85.5" customHeight="1">
+      <c r="A187" s="10" t="n"/>
+      <c r="B187" s="10" t="n"/>
+      <c r="C187" s="10" t="n"/>
+      <c r="D187" s="10" t="n"/>
+    </row>
+    <row r="188" ht="6" customHeight="1"/>
+    <row r="189" ht="22" customHeight="1">
+      <c r="A189" s="1" t="inlineStr">
         <is>
           <t>달팽이수딩세럼/마스크팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B176" s="2" t="n"/>
-      <c r="C176" s="2" t="n"/>
-      <c r="D176" s="2" t="n"/>
-    </row>
-    <row r="177" ht="15" customHeight="1">
-      <c r="A177" s="3" t="inlineStr">
+      <c r="B189" s="2" t="n"/>
+      <c r="C189" s="2" t="n"/>
+      <c r="D189" s="2" t="n"/>
+    </row>
+    <row r="190" ht="15" customHeight="1">
+      <c r="A190" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B177" s="3" t="inlineStr">
+      <c r="B190" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C177" s="3" t="inlineStr">
+      <c r="C190" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D177" s="3" t="inlineStr">
+      <c r="D190" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="178" ht="30" customHeight="1">
-      <c r="A178" s="4" t="inlineStr">
+    <row r="191" ht="32" customHeight="1">
+      <c r="A191" s="4" t="inlineStr">
         <is>
           <t>허브누리 / 알로에베라겔</t>
         </is>
       </c>
-      <c r="B178" s="4" t="inlineStr">
+      <c r="B191" s="4" t="inlineStr">
         <is>
           <t>60g</t>
         </is>
       </c>
-      <c r="C178" s="4" t="inlineStr">
+      <c r="C191" s="4" t="inlineStr">
         <is>
           <t>젤타입, 자체점도, 수분공급, 진정^^</t>
         </is>
       </c>
-      <c r="D178" s="4" t="inlineStr">
+      <c r="D191" s="4" t="inlineStr">
         <is>
           <t>로즈플라워겔, / 네롤리플라워겔</t>
         </is>
       </c>
     </row>
-    <row r="179" ht="15" customHeight="1">
-      <c r="A179" s="4" t="inlineStr">
+    <row r="192" ht="16" customHeight="1">
+      <c r="A192" s="4" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B179" s="4" t="inlineStr">
+      <c r="B192" s="4" t="inlineStr">
         <is>
           <t>14g</t>
         </is>
       </c>
-      <c r="C179" s="4" t="inlineStr">
+      <c r="C192" s="4" t="inlineStr">
         <is>
           <t>장미꽃잎 수증기추출, 진정</t>
         </is>
       </c>
-      <c r="D179" s="4" t="inlineStr">
+      <c r="D192" s="4" t="inlineStr">
         <is>
           <t>원하는 플로랄워터</t>
         </is>
       </c>
     </row>
-    <row r="180" ht="75" customHeight="1">
-      <c r="A180" s="4" t="inlineStr">
+    <row r="193" ht="80" customHeight="1">
+      <c r="A193" s="4" t="inlineStr">
         <is>
           <t>달팽이점액추출물</t>
         </is>
       </c>
-      <c r="B180" s="4" t="inlineStr">
+      <c r="B193" s="4" t="inlineStr">
         <is>
           <t>15g</t>
         </is>
       </c>
-      <c r="C180" s="4" t="inlineStr">
+      <c r="C193" s="4" t="inlineStr">
         <is>
           <t>달팽이가 움직일 때 몸에서 나오는 끈끈한 점액을 뮤신이라하는데 당과 면역단백질이 결합해 생긴 물질로 피부 수분을 유지하고 피부 유해물질로부터 면역강화</t>
         </is>
       </c>
-      <c r="D180" s="4" t="inlineStr">
+      <c r="D193" s="4" t="inlineStr">
         <is>
           <t>EGF, 아세틸헥사펩타이드, 콜라겐 등등...</t>
         </is>
       </c>
     </row>
-    <row r="181" ht="15" customHeight="1">
-      <c r="A181" s="4" t="inlineStr">
+    <row r="194" ht="16" customHeight="1">
+      <c r="A194" s="4" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
-      <c r="B181" s="4" t="inlineStr">
+      <c r="B194" s="4" t="inlineStr">
         <is>
           <t>8g</t>
         </is>
       </c>
-      <c r="C181" s="4" t="inlineStr">
+      <c r="C194" s="4" t="inlineStr">
         <is>
           <t>보습제</t>
         </is>
       </c>
-      <c r="D181" s="4" t="inlineStr">
+      <c r="D194" s="4" t="inlineStr">
         <is>
           <t>글리세린, 리피듀어</t>
         </is>
       </c>
     </row>
-    <row r="182" ht="45" customHeight="1">
-      <c r="A182" s="4" t="inlineStr">
+    <row r="195" ht="48" customHeight="1">
+      <c r="A195" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B182" s="4" t="inlineStr">
+      <c r="B195" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C182" s="4" t="inlineStr">
+      <c r="C195" s="4" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="D182" s="4" t="inlineStr">
+      <c r="D195" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올2g / (로즈워터의 양을 13g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="183" ht="14" customHeight="1">
-      <c r="A183" s="5" t="inlineStr">
+    <row r="196" ht="14" customHeight="1">
+      <c r="A196" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B183" s="6" t="n"/>
-      <c r="C183" s="6" t="n"/>
-      <c r="D183" s="6" t="n"/>
-    </row>
-    <row r="184" ht="330" customHeight="1">
-      <c r="A184" s="7" t="inlineStr">
+      <c r="B196" s="6" t="n"/>
+      <c r="C196" s="6" t="n"/>
+      <c r="D196" s="6" t="n"/>
+    </row>
+    <row r="197" ht="352" customHeight="1">
+      <c r="A197" s="7" t="inlineStr">
         <is>
           <t>겨울철에는 조금만 방심해도 각질과 주름이 순식간에 모습을 드러내는 요즘입니다.
 바르는 것보다 중요한 것이 물마시기인 것 같습니다.
@@ -8073,18 +8121,18 @@
         </is>
       </c>
     </row>
-    <row r="185" ht="14" customHeight="1">
-      <c r="A185" s="5" t="inlineStr">
+    <row r="198" ht="14" customHeight="1">
+      <c r="A198" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B185" s="6" t="n"/>
-      <c r="C185" s="6" t="n"/>
-      <c r="D185" s="6" t="n"/>
-    </row>
-    <row r="186" ht="180" customHeight="1">
-      <c r="A186" s="7" t="inlineStr">
+      <c r="B198" s="6" t="n"/>
+      <c r="C198" s="6" t="n"/>
+      <c r="D198" s="6" t="n"/>
+    </row>
+    <row r="199" ht="192" customHeight="1">
+      <c r="A199" s="7" t="inlineStr">
         <is>
           <t>만들기과정
 1.알로에모이스트를 계량하고
@@ -8097,150 +8145,151 @@
         </is>
       </c>
     </row>
-    <row r="187" ht="14" customHeight="1">
-      <c r="A187" s="5" t="inlineStr">
+    <row r="200" ht="14" customHeight="1">
+      <c r="A200" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B187" s="6" t="n"/>
-      <c r="C187" s="6" t="n"/>
-      <c r="D187" s="6" t="n"/>
-    </row>
-    <row r="188" ht="171" customHeight="1"/>
-    <row r="189" ht="6" customHeight="1"/>
-    <row r="190" ht="22" customHeight="1">
-      <c r="A190" s="1" t="inlineStr">
+      <c r="B200" s="6" t="n"/>
+      <c r="C200" s="6" t="n"/>
+      <c r="D200" s="6" t="n"/>
+    </row>
+    <row r="201" ht="85.5" customHeight="1"/>
+    <row r="202" ht="85.5" customHeight="1"/>
+    <row r="203" ht="6" customHeight="1"/>
+    <row r="204" ht="22" customHeight="1">
+      <c r="A204" s="1" t="inlineStr">
         <is>
           <t>피테 90 에센스&amp; 멀티 패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B190" s="2" t="n"/>
-      <c r="C190" s="2" t="n"/>
-      <c r="D190" s="2" t="n"/>
-    </row>
-    <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="3" t="inlineStr">
+      <c r="B204" s="2" t="n"/>
+      <c r="C204" s="2" t="n"/>
+      <c r="D204" s="2" t="n"/>
+    </row>
+    <row r="205" ht="15" customHeight="1">
+      <c r="A205" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B191" s="3" t="inlineStr">
+      <c r="B205" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C191" s="3" t="inlineStr">
+      <c r="C205" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D191" s="3" t="inlineStr">
+      <c r="D205" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="192" ht="45" customHeight="1">
-      <c r="A192" s="8" t="inlineStr">
+    <row r="206" ht="48" customHeight="1">
+      <c r="A206" s="8" t="inlineStr">
         <is>
           <t>갈락토미세스 발효여과물</t>
         </is>
       </c>
-      <c r="B192" s="8" t="inlineStr">
+      <c r="B206" s="8" t="inlineStr">
         <is>
           <t>117g</t>
         </is>
       </c>
-      <c r="C192" s="8" t="inlineStr">
+      <c r="C206" s="8" t="inlineStr">
         <is>
           <t>90%, 누룩(천연효모)발효여과물, / 보습, 탄력, 아미노산, 미네럴 영양 공급</t>
         </is>
       </c>
-      <c r="D192" s="8" t="inlineStr">
+      <c r="D206" s="8" t="inlineStr">
         <is>
           <t>사카로미세스 / 발효여과물, / 원하는 워터</t>
         </is>
       </c>
     </row>
-    <row r="193" ht="30" customHeight="1">
-      <c r="A193" s="8" t="inlineStr">
+    <row r="207" ht="32" customHeight="1">
+      <c r="A207" s="8" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B193" s="8" t="inlineStr">
+      <c r="B207" s="8" t="inlineStr">
         <is>
           <t>6g</t>
         </is>
       </c>
-      <c r="C193" s="8" t="inlineStr">
+      <c r="C207" s="8" t="inlineStr">
         <is>
           <t>5%, 비타민B3, 식약처 인증 미백원료, / 피부장벽강화, 트러블 완화</t>
         </is>
       </c>
-      <c r="D193" s="8" t="inlineStr">
+      <c r="D207" s="8" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="194" ht="30" customHeight="1">
-      <c r="A194" s="8" t="inlineStr">
+    <row r="208" ht="32" customHeight="1">
+      <c r="A208" s="8" t="inlineStr">
         <is>
           <t>화이트 컴플렉스 6</t>
         </is>
       </c>
-      <c r="B194" s="8" t="inlineStr">
+      <c r="B208" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C194" s="8" t="inlineStr">
+      <c r="C208" s="8" t="inlineStr">
         <is>
           <t>5가지 콩과 갈근 / 특허 균주를 통한 발효로 / 미백, 주름 효능 극대화</t>
         </is>
       </c>
-      <c r="D194" s="8" t="inlineStr">
+      <c r="D208" s="8" t="inlineStr">
         <is>
           <t>글루타치온, 알부틴</t>
         </is>
       </c>
     </row>
-    <row r="195" ht="60" customHeight="1">
-      <c r="A195" s="8" t="inlineStr">
+    <row r="209" ht="64" customHeight="1">
+      <c r="A209" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B195" s="8" t="inlineStr">
+      <c r="B209" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C195" s="8" t="inlineStr">
+      <c r="C209" s="8" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="D195" s="8" t="inlineStr">
+      <c r="D209" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="196" ht="14" customHeight="1">
-      <c r="A196" s="5" t="inlineStr">
+    <row r="210" ht="14" customHeight="1">
+      <c r="A210" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B196" s="6" t="n"/>
-      <c r="C196" s="6" t="n"/>
-      <c r="D196" s="6" t="n"/>
-    </row>
-    <row r="197" ht="315" customHeight="1">
-      <c r="A197" s="9" t="inlineStr">
+      <c r="B210" s="6" t="n"/>
+      <c r="C210" s="6" t="n"/>
+      <c r="D210" s="6" t="n"/>
+    </row>
+    <row r="211" ht="336" customHeight="1">
+      <c r="A211" s="9" t="inlineStr">
         <is>
           <t>무제 문서
 무제 문서
@@ -8262,22 +8311,22 @@
 가장 좋은 효모를 찾아낸 것이 바로 갈락토미세스입니다. 이 레시피 그대로 미스트, 토너 패드 등으로 활용할 수 있어요.</t>
         </is>
       </c>
-      <c r="B197" s="10" t="n"/>
-      <c r="C197" s="10" t="n"/>
-      <c r="D197" s="10" t="n"/>
-    </row>
-    <row r="198" ht="14" customHeight="1">
-      <c r="A198" s="5" t="inlineStr">
+      <c r="B211" s="10" t="n"/>
+      <c r="C211" s="10" t="n"/>
+      <c r="D211" s="10" t="n"/>
+    </row>
+    <row r="212" ht="14" customHeight="1">
+      <c r="A212" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B198" s="6" t="n"/>
-      <c r="C198" s="6" t="n"/>
-      <c r="D198" s="6" t="n"/>
-    </row>
-    <row r="199" ht="165" customHeight="1">
-      <c r="A199" s="9" t="inlineStr">
+      <c r="B212" s="6" t="n"/>
+      <c r="C212" s="6" t="n"/>
+      <c r="D212" s="6" t="n"/>
+    </row>
+    <row r="213" ht="176" customHeight="1">
+      <c r="A213" s="9" t="inlineStr">
         <is>
           <t>피테90 에센스 만들기
 1. 분량의 갈락...을 넣고
@@ -8291,159 +8340,165 @@
 엠보면은 각질, 노폐물 제거용으로 사용하세요.)</t>
         </is>
       </c>
-      <c r="B199" s="10" t="n"/>
-      <c r="C199" s="10" t="n"/>
-      <c r="D199" s="10" t="n"/>
-    </row>
-    <row r="200" ht="14" customHeight="1">
-      <c r="A200" s="5" t="inlineStr">
+      <c r="B213" s="10" t="n"/>
+      <c r="C213" s="10" t="n"/>
+      <c r="D213" s="10" t="n"/>
+    </row>
+    <row r="214" ht="14" customHeight="1">
+      <c r="A214" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B200" s="6" t="n"/>
-      <c r="C200" s="6" t="n"/>
-      <c r="D200" s="6" t="n"/>
-    </row>
-    <row r="201" ht="171" customHeight="1">
-      <c r="A201" s="10" t="n"/>
-      <c r="B201" s="10" t="n"/>
-      <c r="C201" s="10" t="n"/>
-      <c r="D201" s="10" t="n"/>
-    </row>
-    <row r="202" ht="6" customHeight="1"/>
-    <row r="203" ht="22" customHeight="1">
-      <c r="A203" s="1" t="inlineStr">
+      <c r="B214" s="6" t="n"/>
+      <c r="C214" s="6" t="n"/>
+      <c r="D214" s="6" t="n"/>
+    </row>
+    <row r="215" ht="85.5" customHeight="1">
+      <c r="A215" s="10" t="n"/>
+      <c r="B215" s="10" t="n"/>
+      <c r="C215" s="10" t="n"/>
+      <c r="D215" s="10" t="n"/>
+    </row>
+    <row r="216" ht="85.5" customHeight="1">
+      <c r="A216" s="10" t="n"/>
+      <c r="B216" s="10" t="n"/>
+      <c r="C216" s="10" t="n"/>
+      <c r="D216" s="10" t="n"/>
+    </row>
+    <row r="217" ht="6" customHeight="1"/>
+    <row r="218" ht="22" customHeight="1">
+      <c r="A218" s="1" t="inlineStr">
         <is>
           <t>어성 진정 팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B203" s="2" t="n"/>
-      <c r="C203" s="2" t="n"/>
-      <c r="D203" s="2" t="n"/>
-    </row>
-    <row r="204" ht="15" customHeight="1">
-      <c r="A204" s="3" t="inlineStr">
+      <c r="B218" s="2" t="n"/>
+      <c r="C218" s="2" t="n"/>
+      <c r="D218" s="2" t="n"/>
+    </row>
+    <row r="219" ht="15" customHeight="1">
+      <c r="A219" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B204" s="3" t="inlineStr">
+      <c r="B219" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C204" s="3" t="inlineStr">
+      <c r="C219" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D204" s="3" t="inlineStr">
+      <c r="D219" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="205" ht="45" customHeight="1">
-      <c r="A205" s="4" t="inlineStr">
+    <row r="220" ht="48" customHeight="1">
+      <c r="A220" s="4" t="inlineStr">
         <is>
           <t>어성초분말</t>
         </is>
       </c>
-      <c r="B205" s="4" t="inlineStr">
+      <c r="B220" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C205" s="4" t="inlineStr">
+      <c r="C220" s="4" t="inlineStr">
         <is>
           <t>티스푼 1</t>
         </is>
       </c>
-      <c r="D205" s="4" t="inlineStr">
+      <c r="D220" s="4" t="inlineStr">
         <is>
           <t>녹차, 병풀, 알란토인,카렌듈라추출물, 유기농 프레쉬 5솔루션 등</t>
         </is>
       </c>
     </row>
-    <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="4" t="inlineStr">
+    <row r="221" ht="16" customHeight="1">
+      <c r="A221" s="4" t="inlineStr">
         <is>
           <t>오트밀분말</t>
         </is>
       </c>
-      <c r="B206" s="4" t="inlineStr">
+      <c r="B221" s="4" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C206" s="4" t="inlineStr">
+      <c r="C221" s="4" t="inlineStr">
         <is>
           <t>티스푼 1</t>
         </is>
       </c>
-      <c r="D206" s="4" t="inlineStr">
+      <c r="D221" s="4" t="inlineStr">
         <is>
           <t>밀가루^^</t>
         </is>
       </c>
     </row>
-    <row r="207" ht="30" customHeight="1">
-      <c r="A207" s="4" t="inlineStr">
+    <row r="222" ht="32" customHeight="1">
+      <c r="A222" s="4" t="inlineStr">
         <is>
           <t>어성초추출물</t>
         </is>
       </c>
-      <c r="B207" s="4" t="inlineStr">
+      <c r="B222" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C207" s="4" t="inlineStr">
+      <c r="C222" s="4" t="inlineStr">
         <is>
           <t>분말들의 2배, / 마요네즈 농도로 맞춰주세요.</t>
         </is>
       </c>
-      <c r="D207" s="4" t="inlineStr">
+      <c r="D222" s="4" t="inlineStr">
         <is>
           <t>정제수, / 로즈워터 등</t>
         </is>
       </c>
     </row>
-    <row r="208" ht="60" customHeight="1">
-      <c r="A208" s="4" t="inlineStr">
+    <row r="223" ht="64" customHeight="1">
+      <c r="A223" s="4" t="inlineStr">
         <is>
           <t>(라벤더) / 에센셜오일</t>
         </is>
       </c>
-      <c r="B208" s="4" t="inlineStr">
+      <c r="B223" s="4" t="inlineStr">
         <is>
           <t>0~2방울</t>
         </is>
       </c>
-      <c r="C208" s="4" t="inlineStr">
+      <c r="C223" s="4" t="inlineStr">
         <is>
           <t>라벤더허브에서 수증기추출법으로 추출하는 과정에서 생기는 부산물, 라벤더허브의 수용성성분이 다량 녹아있다. 모든피부적합. 진정</t>
         </is>
       </c>
-      <c r="D208" s="4" t="inlineStr">
+      <c r="D223" s="4" t="inlineStr">
         <is>
           <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
         </is>
       </c>
     </row>
-    <row r="209" ht="14" customHeight="1">
-      <c r="A209" s="5" t="inlineStr">
+    <row r="224" ht="14" customHeight="1">
+      <c r="A224" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B209" s="6" t="n"/>
-      <c r="C209" s="6" t="n"/>
-      <c r="D209" s="6" t="n"/>
-    </row>
-    <row r="210" ht="360" customHeight="1">
-      <c r="A210" s="7" t="inlineStr">
+      <c r="B224" s="6" t="n"/>
+      <c r="C224" s="6" t="n"/>
+      <c r="D224" s="6" t="n"/>
+    </row>
+    <row r="225" ht="384" customHeight="1">
+      <c r="A225" s="7" t="inlineStr">
         <is>
           <t>무제 문서
 어성초 =약모밀
@@ -8472,18 +8527,18 @@
         </is>
       </c>
     </row>
-    <row r="211" ht="14" customHeight="1">
-      <c r="A211" s="5" t="inlineStr">
+    <row r="226" ht="14" customHeight="1">
+      <c r="A226" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B211" s="6" t="n"/>
-      <c r="C211" s="6" t="n"/>
-      <c r="D211" s="6" t="n"/>
-    </row>
-    <row r="212" ht="135" customHeight="1">
-      <c r="A212" s="7" t="inlineStr">
+      <c r="B226" s="6" t="n"/>
+      <c r="C226" s="6" t="n"/>
+      <c r="D226" s="6" t="n"/>
+    </row>
+    <row r="227" ht="144" customHeight="1">
+      <c r="A227" s="7" t="inlineStr">
         <is>
           <t>1.어성초분말과 오트밀분말을
 계량하고
@@ -8497,238 +8552,239 @@
         </is>
       </c>
     </row>
-    <row r="213" ht="14" customHeight="1">
-      <c r="A213" s="5" t="inlineStr">
+    <row r="228" ht="14" customHeight="1">
+      <c r="A228" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B213" s="6" t="n"/>
-      <c r="C213" s="6" t="n"/>
-      <c r="D213" s="6" t="n"/>
-    </row>
-    <row r="214" ht="171" customHeight="1"/>
-    <row r="215" ht="6" customHeight="1"/>
-    <row r="216" ht="22" customHeight="1">
-      <c r="A216" s="1" t="inlineStr">
+      <c r="B228" s="6" t="n"/>
+      <c r="C228" s="6" t="n"/>
+      <c r="D228" s="6" t="n"/>
+    </row>
+    <row r="229" ht="85.5" customHeight="1"/>
+    <row r="230" ht="85.5" customHeight="1"/>
+    <row r="231" ht="6" customHeight="1"/>
+    <row r="232" ht="22" customHeight="1">
+      <c r="A232" s="1" t="inlineStr">
         <is>
           <t>콜라겐 에센스팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B216" s="2" t="n"/>
-      <c r="C216" s="2" t="n"/>
-      <c r="D216" s="2" t="n"/>
-    </row>
-    <row r="217" ht="15" customHeight="1">
-      <c r="A217" s="3" t="inlineStr">
+      <c r="B232" s="2" t="n"/>
+      <c r="C232" s="2" t="n"/>
+      <c r="D232" s="2" t="n"/>
+    </row>
+    <row r="233" ht="15" customHeight="1">
+      <c r="A233" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B217" s="3" t="inlineStr">
+      <c r="B233" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C217" s="3" t="inlineStr">
+      <c r="C233" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D217" s="3" t="inlineStr">
+      <c r="D233" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="218" ht="60" customHeight="1">
-      <c r="A218" s="8" t="inlineStr">
+    <row r="234" ht="64" customHeight="1">
+      <c r="A234" s="8" t="inlineStr">
         <is>
           <t>알로에베라겔</t>
         </is>
       </c>
-      <c r="B218" s="8" t="inlineStr">
+      <c r="B234" s="8" t="inlineStr">
         <is>
           <t>43.79%</t>
         </is>
       </c>
-      <c r="C218" s="8" t="inlineStr">
+      <c r="C234" s="8" t="inlineStr">
         <is>
           <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. / 남은 재료 활용 팁 : 젤타입스킨으로 사용가능, / 헤어에센스로 사용가능.</t>
         </is>
       </c>
-      <c r="D218" s="8" t="inlineStr">
+      <c r="D234" s="8" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="219" ht="45" customHeight="1">
-      <c r="A219" s="8" t="inlineStr">
+    <row r="235" ht="48" customHeight="1">
+      <c r="A235" s="8" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B219" s="8" t="inlineStr">
+      <c r="B235" s="8" t="inlineStr">
         <is>
           <t>43.79%</t>
         </is>
       </c>
-      <c r="C219" s="8" t="inlineStr">
+      <c r="C235" s="8" t="inlineStr">
         <is>
           <t>장미꽃잎을 수증기추출, 장미꽃의 수용성성분이 다량함유, 진정, 수분공급, 아로마테라피</t>
         </is>
       </c>
-      <c r="D219" s="8" t="inlineStr">
+      <c r="D235" s="8" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="220" ht="30" customHeight="1">
-      <c r="A220" s="8" t="inlineStr">
+    <row r="236" ht="48" customHeight="1">
+      <c r="A236" s="8" t="inlineStr">
         <is>
           <t>만다린EO</t>
         </is>
       </c>
-      <c r="B220" s="8" t="inlineStr">
+      <c r="B236" s="8" t="inlineStr">
         <is>
           <t>0.27%</t>
         </is>
       </c>
-      <c r="C220" s="8" t="inlineStr">
+      <c r="C236" s="8" t="inlineStr">
         <is>
           <t>귤껍질오일, / 임신기간 영아에게 안전하게 사용, / 모든 피부사용</t>
         </is>
       </c>
-      <c r="D220" s="8" t="inlineStr">
+      <c r="D236" s="8" t="inlineStr">
         <is>
           <t>오렌지, 버가못, 그레이프프룻 등 감귤류 오일</t>
         </is>
       </c>
     </row>
-    <row r="221" ht="45" customHeight="1">
-      <c r="A221" s="8" t="inlineStr">
+    <row r="237" ht="64" customHeight="1">
+      <c r="A237" s="8" t="inlineStr">
         <is>
           <t>자스민 EO</t>
         </is>
       </c>
-      <c r="B221" s="8" t="inlineStr">
+      <c r="B237" s="8" t="inlineStr">
         <is>
           <t>0.11%</t>
         </is>
       </c>
-      <c r="C221" s="8" t="inlineStr">
+      <c r="C237" s="8" t="inlineStr">
         <is>
           <t>자스민꽃을 용매추출. 이국적이고 달콤한 꽃향, 모든 피부에 유효, 건조하고 손상된 피부 민감성 피부에 적합</t>
         </is>
       </c>
-      <c r="D221" s="8" t="inlineStr">
+      <c r="D237" s="8" t="inlineStr">
         <is>
           <t>라벤더, 로즈제라늄, 로즈우드 등 원하는 EO</t>
         </is>
       </c>
     </row>
-    <row r="222" ht="90" customHeight="1">
-      <c r="A222" s="8" t="inlineStr">
+    <row r="238" ht="96" customHeight="1">
+      <c r="A238" s="8" t="inlineStr">
         <is>
           <t>코엔자임Q10</t>
         </is>
       </c>
-      <c r="B222" s="8" t="inlineStr">
+      <c r="B238" s="8" t="inlineStr">
         <is>
           <t>3.28%</t>
         </is>
       </c>
-      <c r="C222" s="8" t="inlineStr">
+      <c r="C238" s="8" t="inlineStr">
         <is>
           <t>수용성, 비타민Q, 나이를 먹어 코엔자임Q10의 생산이 감소되면 피부의 탄력을 유지하는 콜라겐, 엘라스틴과 보습성분인 히아루론산을 생산하는 기능이 떨어져 새로 생산해 내지 못하고 소비만 하게 됩니다.</t>
         </is>
       </c>
-      <c r="D222" s="8" t="inlineStr">
+      <c r="D238" s="8" t="inlineStr">
         <is>
           <t>콜라겐,플라센타</t>
         </is>
       </c>
     </row>
-    <row r="223" ht="30" customHeight="1">
-      <c r="A223" s="8" t="inlineStr">
+    <row r="239" ht="32" customHeight="1">
+      <c r="A239" s="8" t="inlineStr">
         <is>
           <t>아카시아콜라겐</t>
         </is>
       </c>
-      <c r="B223" s="8" t="inlineStr">
+      <c r="B239" s="8" t="inlineStr">
         <is>
           <t>4.38%</t>
         </is>
       </c>
-      <c r="C223" s="8" t="inlineStr">
+      <c r="C239" s="8" t="inlineStr">
         <is>
           <t>아카시아꽃에서 추출한 콜라겐.</t>
         </is>
       </c>
-      <c r="D223" s="8" t="inlineStr">
+      <c r="D239" s="8" t="inlineStr">
         <is>
           <t>콜라겐, 마린콜라겐,식물성 플라센타 등</t>
         </is>
       </c>
     </row>
-    <row r="224" ht="60" customHeight="1">
-      <c r="A224" s="8" t="inlineStr">
+    <row r="240" ht="64" customHeight="1">
+      <c r="A240" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B224" s="8" t="inlineStr">
+      <c r="B240" s="8" t="inlineStr">
         <is>
           <t>2.19%</t>
         </is>
       </c>
-      <c r="C224" s="8" t="inlineStr">
+      <c r="C240" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 / 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
         </is>
       </c>
-      <c r="D224" s="8" t="inlineStr">
+      <c r="D240" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="225" ht="60" customHeight="1">
-      <c r="A225" s="8" t="inlineStr">
+    <row r="241" ht="64" customHeight="1">
+      <c r="A241" s="8" t="inlineStr">
         <is>
           <t>토코페롤</t>
         </is>
       </c>
-      <c r="B225" s="8" t="inlineStr">
+      <c r="B241" s="8" t="inlineStr">
         <is>
           <t>2.19%</t>
         </is>
       </c>
-      <c r="C225" s="8" t="inlineStr">
+      <c r="C241" s="8" t="inlineStr">
         <is>
           <t>토코페롤, 지용성 보존제, 산화방지, 탄력,천연비타민E는 특유의 냄새가 있습니다. 감안하시고 대체해서 사용하세요.</t>
         </is>
       </c>
-      <c r="D225" s="8" t="inlineStr">
+      <c r="D241" s="8" t="inlineStr">
         <is>
           <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
         </is>
       </c>
     </row>
-    <row r="226" ht="14" customHeight="1">
-      <c r="A226" s="5" t="inlineStr">
+    <row r="242" ht="14" customHeight="1">
+      <c r="A242" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B226" s="6" t="n"/>
-      <c r="C226" s="6" t="n"/>
-      <c r="D226" s="6" t="n"/>
-    </row>
-    <row r="227" ht="135" customHeight="1">
-      <c r="A227" s="9" t="inlineStr">
+      <c r="B242" s="6" t="n"/>
+      <c r="C242" s="6" t="n"/>
+      <c r="D242" s="6" t="n"/>
+    </row>
+    <row r="243" ht="144" customHeight="1">
+      <c r="A243" s="9" t="inlineStr">
         <is>
           <t>만들기 방법
 1. 알로에겔이랑 로즈워터 계량하세요.
@@ -8741,261 +8797,261 @@
 8. 완성! 냉동보관 권해 드립니다.</t>
         </is>
       </c>
-      <c r="B227" s="10" t="n"/>
-      <c r="C227" s="10" t="n"/>
-      <c r="D227" s="10" t="n"/>
-    </row>
-    <row r="228" ht="14" customHeight="1">
-      <c r="A228" s="5" t="inlineStr">
+      <c r="B243" s="10" t="n"/>
+      <c r="C243" s="10" t="n"/>
+      <c r="D243" s="10" t="n"/>
+    </row>
+    <row r="244" ht="14" customHeight="1">
+      <c r="A244" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B228" s="6" t="n"/>
-      <c r="C228" s="6" t="n"/>
-      <c r="D228" s="6" t="n"/>
-    </row>
-    <row r="229" ht="85.5" customHeight="1">
-      <c r="A229" s="10" t="n"/>
-      <c r="B229" s="10" t="n"/>
-      <c r="C229" s="10" t="n"/>
-      <c r="D229" s="10" t="n"/>
-    </row>
-    <row r="230" ht="6" customHeight="1"/>
-    <row r="231" ht="22" customHeight="1">
-      <c r="A231" s="1" t="inlineStr">
+      <c r="B244" s="6" t="n"/>
+      <c r="C244" s="6" t="n"/>
+      <c r="D244" s="6" t="n"/>
+    </row>
+    <row r="245" ht="85.5" customHeight="1">
+      <c r="A245" s="10" t="n"/>
+      <c r="B245" s="10" t="n"/>
+      <c r="C245" s="10" t="n"/>
+      <c r="D245" s="10" t="n"/>
+    </row>
+    <row r="246" ht="6" customHeight="1"/>
+    <row r="247" ht="22" customHeight="1">
+      <c r="A247" s="1" t="inlineStr">
         <is>
           <t>화산송이 마스크팩    ↗ 원본</t>
         </is>
       </c>
-      <c r="B231" s="2" t="n"/>
-      <c r="C231" s="2" t="n"/>
-      <c r="D231" s="2" t="n"/>
-    </row>
-    <row r="232" ht="15" customHeight="1">
-      <c r="A232" s="3" t="inlineStr">
+      <c r="B247" s="2" t="n"/>
+      <c r="C247" s="2" t="n"/>
+      <c r="D247" s="2" t="n"/>
+    </row>
+    <row r="248" ht="15" customHeight="1">
+      <c r="A248" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B232" s="3" t="inlineStr">
+      <c r="B248" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C232" s="3" t="inlineStr">
+      <c r="C248" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D232" s="3" t="inlineStr">
+      <c r="D248" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="233" ht="30" customHeight="1">
-      <c r="A233" s="4" t="inlineStr">
+    <row r="249" ht="32" customHeight="1">
+      <c r="A249" s="4" t="inlineStr">
         <is>
           <t>골든 호호바오일</t>
         </is>
       </c>
-      <c r="B233" s="4" t="inlineStr">
+      <c r="B249" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C233" s="4" t="inlineStr">
+      <c r="C249" s="4" t="inlineStr">
         <is>
           <t>가벼운 오일, 콩과식물, / 피지와 성분과 흡사</t>
         </is>
       </c>
-      <c r="D233" s="4" t="inlineStr">
+      <c r="D249" s="4" t="inlineStr">
         <is>
           <t>마카다미아넛오일, / 아몬드, 살구씨 오일 등</t>
         </is>
       </c>
     </row>
-    <row r="234" ht="45" customHeight="1">
-      <c r="A234" s="4" t="inlineStr">
+    <row r="250" ht="48" customHeight="1">
+      <c r="A250" s="4" t="inlineStr">
         <is>
           <t>올리브유화왁스</t>
         </is>
       </c>
-      <c r="B234" s="4" t="inlineStr">
+      <c r="B250" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C234" s="4" t="inlineStr">
+      <c r="C250" s="4" t="inlineStr">
         <is>
           <t>에코인증. 오일과 물이 분리되지 / 않도록 도와줌.</t>
         </is>
       </c>
-      <c r="D234" s="4" t="inlineStr">
+      <c r="D250" s="4" t="inlineStr">
         <is>
           <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
-    <row r="235" ht="30" customHeight="1">
-      <c r="A235" s="4" t="inlineStr">
+    <row r="251" ht="32" customHeight="1">
+      <c r="A251" s="4" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B235" s="4" t="inlineStr">
+      <c r="B251" s="4" t="inlineStr">
         <is>
           <t>24g</t>
         </is>
       </c>
-      <c r="C235" s="4" t="inlineStr">
+      <c r="C251" s="4" t="inlineStr">
         <is>
           <t>장미수</t>
         </is>
       </c>
-      <c r="D235" s="4" t="inlineStr">
+      <c r="D251" s="4" t="inlineStr">
         <is>
           <t>원하는 플로럴워터 / 네롤리워터</t>
         </is>
       </c>
     </row>
-    <row r="236" ht="60" customHeight="1">
-      <c r="A236" s="4" t="inlineStr">
+    <row r="252" ht="64" customHeight="1">
+      <c r="A252" s="4" t="inlineStr">
         <is>
           <t>알로에모이스트</t>
         </is>
       </c>
-      <c r="B236" s="4" t="inlineStr">
+      <c r="B252" s="4" t="inlineStr">
         <is>
           <t>20g</t>
         </is>
       </c>
-      <c r="C236" s="4" t="inlineStr">
+      <c r="C252" s="4" t="inlineStr">
         <is>
           <t>수분공급, 자체점도 화산송이를 / 골고루 분산시키는 역할.</t>
         </is>
       </c>
-      <c r="D236" s="4" t="inlineStr">
+      <c r="D252" s="4" t="inlineStr">
         <is>
           <t>조금더 묽은 타입을 원하시면 80g 중 일부를 로즈워터,네롤리워터 등 대체가능</t>
         </is>
       </c>
     </row>
-    <row r="237" ht="15" customHeight="1">
-      <c r="A237" s="4" t="inlineStr">
+    <row r="253" ht="16" customHeight="1">
+      <c r="A253" s="4" t="inlineStr">
         <is>
           <t>바이오디톡스</t>
         </is>
       </c>
-      <c r="B237" s="4" t="inlineStr">
+      <c r="B253" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C237" s="4" t="inlineStr">
+      <c r="C253" s="4" t="inlineStr">
         <is>
           <t>모공 세정해독효소 활성화, 항산화</t>
         </is>
       </c>
-      <c r="D237" s="4" t="n"/>
-    </row>
-    <row r="238" ht="60" customHeight="1">
-      <c r="A238" s="4" t="inlineStr">
+      <c r="D253" s="4" t="n"/>
+    </row>
+    <row r="254" ht="64" customHeight="1">
+      <c r="A254" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B238" s="4" t="inlineStr">
+      <c r="B254" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C238" s="4" t="inlineStr">
+      <c r="C254" s="4" t="inlineStr">
         <is>
           <t>한방 복합 추출물, 균번식억제</t>
         </is>
       </c>
-      <c r="D238" s="4" t="inlineStr">
+      <c r="D254" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="239" ht="30" customHeight="1">
-      <c r="A239" s="4" t="inlineStr">
+    <row r="255" ht="32" customHeight="1">
+      <c r="A255" s="4" t="inlineStr">
         <is>
           <t>(에센셜오일)</t>
         </is>
       </c>
-      <c r="B239" s="4" t="inlineStr">
+      <c r="B255" s="4" t="inlineStr">
         <is>
           <t>5방울</t>
         </is>
       </c>
-      <c r="C239" s="4" t="inlineStr">
+      <c r="C255" s="4" t="inlineStr">
         <is>
           <t>무향을 원하시면 넣지 / 않아도 됩니다.</t>
         </is>
       </c>
-      <c r="D239" s="4" t="inlineStr">
+      <c r="D255" s="4" t="inlineStr">
         <is>
           <t>아로마테라피효과 / 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
-    <row r="240" ht="60" customHeight="1">
-      <c r="A240" s="4" t="inlineStr">
+    <row r="256" ht="64" customHeight="1">
+      <c r="A256" s="4" t="inlineStr">
         <is>
           <t>제주화산송이</t>
         </is>
       </c>
-      <c r="B240" s="4" t="inlineStr">
+      <c r="B256" s="4" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C240" s="4" t="inlineStr">
+      <c r="C256" s="4" t="inlineStr">
         <is>
           <t>섭씨 2000도의 화산작용이 만든 기능성 미네럴,송이는 제주방언으로 가벼운 돌이라는 뜻, 황토와 참숯의 효과가 하나로!</t>
         </is>
       </c>
-      <c r="D240" s="4" t="n"/>
-    </row>
-    <row r="241" ht="30" customHeight="1">
-      <c r="A241" s="4" t="inlineStr">
+      <c r="D256" s="4" t="n"/>
+    </row>
+    <row r="257" ht="32" customHeight="1">
+      <c r="A257" s="4" t="inlineStr">
         <is>
           <t>알란토인(분말)</t>
         </is>
       </c>
-      <c r="B241" s="4" t="inlineStr">
+      <c r="B257" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C241" s="4" t="inlineStr">
+      <c r="C257" s="4" t="inlineStr">
         <is>
           <t>컴프리 등 뿌리에 존재, 진정</t>
         </is>
       </c>
-      <c r="D241" s="4" t="inlineStr">
+      <c r="D257" s="4" t="inlineStr">
         <is>
           <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="242" ht="14" customHeight="1">
-      <c r="A242" s="5" t="inlineStr">
+    <row r="258" ht="14" customHeight="1">
+      <c r="A258" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B242" s="6" t="n"/>
-      <c r="C242" s="6" t="n"/>
-      <c r="D242" s="6" t="n"/>
-    </row>
-    <row r="243" ht="525" customHeight="1">
-      <c r="A243" s="7" t="inlineStr">
+      <c r="B258" s="6" t="n"/>
+      <c r="C258" s="6" t="n"/>
+      <c r="D258" s="6" t="n"/>
+    </row>
+    <row r="259" ht="384" customHeight="1">
+      <c r="A259" s="7" t="inlineStr">
         <is>
           <t>제주화산송이는
 붉은 빛을 띤 다공질의 천연세라믹으로서
@@ -9019,8 +9075,14 @@
 ------------------------------------------------
 며칠 전 아임레알 화산송이팩하는 방법을 알려드렸어요.
 플로럴워터랑(정제수, 녹차우린 물 등) 화산송이분말만있으면 누구나 할 수
-있는 간단팩이였죠.
-업그레이드 화산송이마스크팩을 알려드릴께요.
+있는 간단팩이였죠.</t>
+        </is>
+      </c>
+    </row>
+    <row r="260" ht="176" customHeight="1">
+      <c r="A260" s="7" t="inlineStr">
+        <is>
+          <t>업그레이드 화산송이마스크팩을 알려드릴께요.
 크림처럼 만들어서 화산송이를 넣고 필요하실 때마다
 덜거나 짜서 사용할 수 있어
 간편해요. 건조될 때 가루 날림이 없어
@@ -9034,18 +9096,18 @@
         </is>
       </c>
     </row>
-    <row r="244" ht="14" customHeight="1">
-      <c r="A244" s="5" t="inlineStr">
+    <row r="261" ht="14" customHeight="1">
+      <c r="A261" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B244" s="6" t="n"/>
-      <c r="C244" s="6" t="n"/>
-      <c r="D244" s="6" t="n"/>
-    </row>
-    <row r="245" ht="420" customHeight="1">
-      <c r="A245" s="7" t="inlineStr">
+      <c r="B261" s="6" t="n"/>
+      <c r="C261" s="6" t="n"/>
+      <c r="D261" s="6" t="n"/>
+    </row>
+    <row r="262" ht="384" customHeight="1">
+      <c r="A262" s="7" t="inlineStr">
         <is>
           <t>1.미리 준비하세요. 첨가물로 사용하게 될 화산송이와 알란토인 분말을 미계량해서
 2. 지퍼비닐, 빈통 등을 잘 섞어놓으세요. 통일 경우 뚜껑 닫고 흔들어주시면 잘 섞입니다.
@@ -9066,198 +9128,207 @@
 메이크업을 지운 미지근한 물로 세안합니다.
 모공과 각질를 충분히 불린다음 화산송이마스크팩을 덜어서 얇게 펴발라주세요.
 10분정도 건조되면 물에 씻어주세요.
-덜 마른 부위는 휴지로 살짝 닦아내신 후 세안해도 됩니다.
-민감한 피부의 경우
+덜 마른 부위는 휴지로 살짝 닦아내신 후 세안해도 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="64" customHeight="1">
+      <c r="A263" s="7" t="inlineStr">
+        <is>
+          <t>민감한 피부의 경우
 일주일 1번 또는 T존 위주로
 팩하세요.
 (모공이 넓은 피부, 지성, 뾰루지가 많이 나는 피부는 주2~3회)</t>
         </is>
       </c>
     </row>
-    <row r="246" ht="14" customHeight="1">
-      <c r="A246" s="5" t="inlineStr">
+    <row r="264" ht="14" customHeight="1">
+      <c r="A264" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B246" s="6" t="n"/>
-      <c r="C246" s="6" t="n"/>
-      <c r="D246" s="6" t="n"/>
-    </row>
-    <row r="247" ht="342" customHeight="1"/>
-    <row r="248" ht="6" customHeight="1"/>
-    <row r="249" ht="22" customHeight="1">
-      <c r="A249" s="1" t="inlineStr">
+      <c r="B264" s="6" t="n"/>
+      <c r="C264" s="6" t="n"/>
+      <c r="D264" s="6" t="n"/>
+    </row>
+    <row r="265" ht="85.5" customHeight="1"/>
+    <row r="266" ht="85.5" customHeight="1"/>
+    <row r="267" ht="85.5" customHeight="1"/>
+    <row r="268" ht="85.5" customHeight="1"/>
+    <row r="269" ht="6" customHeight="1"/>
+    <row r="270" ht="22" customHeight="1">
+      <c r="A270" s="1" t="inlineStr">
         <is>
           <t>율무 미백 토너&amp;패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B249" s="2" t="n"/>
-      <c r="C249" s="2" t="n"/>
-      <c r="D249" s="2" t="n"/>
-    </row>
-    <row r="250" ht="15" customHeight="1">
-      <c r="A250" s="3" t="inlineStr">
+      <c r="B270" s="2" t="n"/>
+      <c r="C270" s="2" t="n"/>
+      <c r="D270" s="2" t="n"/>
+    </row>
+    <row r="271" ht="15" customHeight="1">
+      <c r="A271" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B250" s="3" t="inlineStr">
+      <c r="B271" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C250" s="3" t="inlineStr">
+      <c r="C271" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D250" s="3" t="inlineStr">
+      <c r="D271" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="251" ht="15" customHeight="1">
-      <c r="A251" s="8" t="inlineStr">
+    <row r="272" ht="16" customHeight="1">
+      <c r="A272" s="8" t="inlineStr">
         <is>
           <t>네롤리워터</t>
         </is>
       </c>
-      <c r="B251" s="8" t="inlineStr">
+      <c r="B272" s="8" t="inlineStr">
         <is>
           <t>42g</t>
         </is>
       </c>
-      <c r="C251" s="8" t="inlineStr">
+      <c r="C272" s="8" t="inlineStr">
         <is>
           <t>오렌지꽃수</t>
         </is>
       </c>
-      <c r="D251" s="8" t="inlineStr">
+      <c r="D272" s="8" t="inlineStr">
         <is>
           <t>로먼캐모마일워터</t>
         </is>
       </c>
     </row>
-    <row r="252" ht="15" customHeight="1">
-      <c r="A252" s="8" t="inlineStr">
+    <row r="273" ht="16" customHeight="1">
+      <c r="A273" s="8" t="inlineStr">
         <is>
           <t>율무추출물</t>
         </is>
       </c>
-      <c r="B252" s="8" t="inlineStr">
+      <c r="B273" s="8" t="inlineStr">
         <is>
           <t>33g</t>
         </is>
       </c>
-      <c r="C252" s="8" t="inlineStr">
+      <c r="C273" s="8" t="inlineStr">
         <is>
           <t>피부를 밝고 매끈하게</t>
         </is>
       </c>
-      <c r="D252" s="8" t="inlineStr">
+      <c r="D273" s="8" t="inlineStr">
         <is>
           <t>로먼캐모마일워터</t>
         </is>
       </c>
     </row>
-    <row r="253" ht="30" customHeight="1">
-      <c r="A253" s="8" t="inlineStr">
+    <row r="274" ht="32" customHeight="1">
+      <c r="A274" s="8" t="inlineStr">
         <is>
           <t>비타민 열매3</t>
         </is>
       </c>
-      <c r="B253" s="8" t="inlineStr">
+      <c r="B274" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C253" s="8" t="inlineStr">
+      <c r="C274" s="8" t="inlineStr">
         <is>
           <t>맑고 밝은 피부 도움 / (비타민나무 열매, 유자, 오미자 복합)</t>
         </is>
       </c>
-      <c r="D253" s="8" t="n"/>
-    </row>
-    <row r="254" ht="30" customHeight="1">
-      <c r="A254" s="8" t="inlineStr">
+      <c r="D274" s="8" t="n"/>
+    </row>
+    <row r="275" ht="48" customHeight="1">
+      <c r="A275" s="8" t="inlineStr">
         <is>
           <t>베타글루칸</t>
         </is>
       </c>
-      <c r="B254" s="8" t="inlineStr">
+      <c r="B275" s="8" t="inlineStr">
         <is>
           <t>5~10g</t>
         </is>
       </c>
-      <c r="C254" s="8" t="inlineStr">
+      <c r="C275" s="8" t="inlineStr">
         <is>
           <t>천연 다당류 / (귀리, 효모, 버섯류, 해조류) / 피부 보습, 보호막 형성</t>
         </is>
       </c>
-      <c r="D254" s="8" t="inlineStr">
+      <c r="D275" s="8" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="255" ht="15" customHeight="1">
-      <c r="A255" s="8" t="inlineStr">
+    <row r="276" ht="16" customHeight="1">
+      <c r="A276" s="8" t="inlineStr">
         <is>
           <t>(유기농)글리세린</t>
         </is>
       </c>
-      <c r="B255" s="8" t="inlineStr">
+      <c r="B276" s="8" t="inlineStr">
         <is>
           <t>0~3g</t>
         </is>
       </c>
-      <c r="C255" s="8" t="inlineStr">
+      <c r="C276" s="8" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D255" s="8" t="inlineStr">
+      <c r="D276" s="8" t="inlineStr">
         <is>
           <t>히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="256" ht="45" customHeight="1">
-      <c r="A256" s="8" t="inlineStr">
+    <row r="277" ht="48" customHeight="1">
+      <c r="A277" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B256" s="8" t="inlineStr">
+      <c r="B277" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C256" s="8" t="inlineStr">
+      <c r="C277" s="8" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="D256" s="8" t="inlineStr">
+      <c r="D277" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="257" ht="14" customHeight="1">
-      <c r="A257" s="5" t="inlineStr">
+    <row r="278" ht="14" customHeight="1">
+      <c r="A278" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B257" s="6" t="n"/>
-      <c r="C257" s="6" t="n"/>
-      <c r="D257" s="6" t="n"/>
-    </row>
-    <row r="258" ht="300" customHeight="1">
-      <c r="A258" s="9" t="inlineStr">
+      <c r="B278" s="6" t="n"/>
+      <c r="C278" s="6" t="n"/>
+      <c r="D278" s="6" t="n"/>
+    </row>
+    <row r="279" ht="320" customHeight="1">
+      <c r="A279" s="9" t="inlineStr">
         <is>
           <t>밝고 깨끗한 피부를 위한
 율무 미백 토너&amp;패드
@@ -9281,22 +9352,22 @@
 깨끗한 피부 유지에 도움이 됩니다.</t>
         </is>
       </c>
-      <c r="B258" s="10" t="n"/>
-      <c r="C258" s="10" t="n"/>
-      <c r="D258" s="10" t="n"/>
-    </row>
-    <row r="259" ht="14" customHeight="1">
-      <c r="A259" s="5" t="inlineStr">
+      <c r="B279" s="10" t="n"/>
+      <c r="C279" s="10" t="n"/>
+      <c r="D279" s="10" t="n"/>
+    </row>
+    <row r="280" ht="14" customHeight="1">
+      <c r="A280" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B259" s="6" t="n"/>
-      <c r="C259" s="6" t="n"/>
-      <c r="D259" s="6" t="n"/>
-    </row>
-    <row r="260" ht="150" customHeight="1">
-      <c r="A260" s="9" t="inlineStr">
+      <c r="B280" s="6" t="n"/>
+      <c r="C280" s="6" t="n"/>
+      <c r="D280" s="6" t="n"/>
+    </row>
+    <row r="281" ht="160" customHeight="1">
+      <c r="A281" s="9" t="inlineStr">
         <is>
           <t>율무 미백 토너&amp;패드 만들기
 1. 용기에 모든 재료를 계량한 후 섞어주세요.
@@ -9310,155 +9381,161 @@
 집게 사용으로 더욱 위생적으로 사용할 수 있어요.</t>
         </is>
       </c>
-      <c r="B260" s="10" t="n"/>
-      <c r="C260" s="10" t="n"/>
-      <c r="D260" s="10" t="n"/>
-    </row>
-    <row r="261" ht="14" customHeight="1">
-      <c r="A261" s="5" t="inlineStr">
+      <c r="B281" s="10" t="n"/>
+      <c r="C281" s="10" t="n"/>
+      <c r="D281" s="10" t="n"/>
+    </row>
+    <row r="282" ht="14" customHeight="1">
+      <c r="A282" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B261" s="6" t="n"/>
-      <c r="C261" s="6" t="n"/>
-      <c r="D261" s="6" t="n"/>
-    </row>
-    <row r="262" ht="171" customHeight="1">
-      <c r="A262" s="10" t="n"/>
-      <c r="B262" s="10" t="n"/>
-      <c r="C262" s="10" t="n"/>
-      <c r="D262" s="10" t="n"/>
-    </row>
-    <row r="263" ht="6" customHeight="1"/>
-    <row r="264" ht="22" customHeight="1">
-      <c r="A264" s="1" t="inlineStr">
+      <c r="B282" s="6" t="n"/>
+      <c r="C282" s="6" t="n"/>
+      <c r="D282" s="6" t="n"/>
+    </row>
+    <row r="283" ht="85.5" customHeight="1">
+      <c r="A283" s="10" t="n"/>
+      <c r="B283" s="10" t="n"/>
+      <c r="C283" s="10" t="n"/>
+      <c r="D283" s="10" t="n"/>
+    </row>
+    <row r="284" ht="85.5" customHeight="1">
+      <c r="A284" s="10" t="n"/>
+      <c r="B284" s="10" t="n"/>
+      <c r="C284" s="10" t="n"/>
+      <c r="D284" s="10" t="n"/>
+    </row>
+    <row r="285" ht="6" customHeight="1"/>
+    <row r="286" ht="22" customHeight="1">
+      <c r="A286" s="1" t="inlineStr">
         <is>
           <t>콤부차 멀티 패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B264" s="2" t="n"/>
-      <c r="C264" s="2" t="n"/>
-      <c r="D264" s="2" t="n"/>
-    </row>
-    <row r="265" ht="15" customHeight="1">
-      <c r="A265" s="3" t="inlineStr">
+      <c r="B286" s="2" t="n"/>
+      <c r="C286" s="2" t="n"/>
+      <c r="D286" s="2" t="n"/>
+    </row>
+    <row r="287" ht="15" customHeight="1">
+      <c r="A287" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B265" s="3" t="inlineStr">
+      <c r="B287" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C265" s="3" t="inlineStr">
+      <c r="C287" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D265" s="3" t="inlineStr">
+      <c r="D287" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="266" ht="45" customHeight="1">
-      <c r="A266" s="4" t="inlineStr">
+    <row r="288" ht="48" customHeight="1">
+      <c r="A288" s="4" t="inlineStr">
         <is>
           <t>콤부차 발효여과물</t>
         </is>
       </c>
-      <c r="B266" s="4" t="inlineStr">
+      <c r="B288" s="4" t="inlineStr">
         <is>
           <t>117g</t>
         </is>
       </c>
-      <c r="C266" s="4" t="inlineStr">
+      <c r="C288" s="4" t="inlineStr">
         <is>
           <t>강력한 항산화, / 피부 생기와 윤기, / 수분공급과 보유력증가, / 피부의 장벽 튼튼</t>
         </is>
       </c>
-      <c r="D266" s="4" t="n"/>
-    </row>
-    <row r="267" ht="30" customHeight="1">
-      <c r="A267" s="4" t="inlineStr">
+      <c r="D288" s="4" t="n"/>
+    </row>
+    <row r="289" ht="32" customHeight="1">
+      <c r="A289" s="4" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B267" s="4" t="inlineStr">
+      <c r="B289" s="4" t="inlineStr">
         <is>
           <t>6g</t>
         </is>
       </c>
-      <c r="C267" s="4" t="inlineStr">
+      <c r="C289" s="4" t="inlineStr">
         <is>
           <t>5%, 비타민B3, 식약처 인증 미백원료, / 피부장벽강화, 트러블 완화</t>
         </is>
       </c>
-      <c r="D267" s="4" t="inlineStr">
+      <c r="D289" s="4" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="268" ht="30" customHeight="1">
-      <c r="A268" s="4" t="inlineStr">
+    <row r="290" ht="32" customHeight="1">
+      <c r="A290" s="4" t="inlineStr">
         <is>
           <t>화이트 컴플렉스 6</t>
         </is>
       </c>
-      <c r="B268" s="4" t="inlineStr">
+      <c r="B290" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C268" s="4" t="inlineStr">
+      <c r="C290" s="4" t="inlineStr">
         <is>
           <t>5가지 콩과 갈근 / 특허 균주를 통한발효로 / 미백, 주름 효능 극대화</t>
         </is>
       </c>
-      <c r="D268" s="4" t="inlineStr">
+      <c r="D290" s="4" t="inlineStr">
         <is>
           <t>글루타치온 / 알부틴</t>
         </is>
       </c>
     </row>
-    <row r="269" ht="60" customHeight="1">
-      <c r="A269" s="4" t="inlineStr">
+    <row r="291" ht="64" customHeight="1">
+      <c r="A291" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제</t>
         </is>
       </c>
-      <c r="B269" s="4" t="inlineStr">
+      <c r="B291" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C269" s="4" t="inlineStr">
+      <c r="C291" s="4" t="inlineStr">
         <is>
           <t>균번식 억제</t>
         </is>
       </c>
-      <c r="D269" s="4" t="inlineStr">
+      <c r="D291" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="270" ht="14" customHeight="1">
-      <c r="A270" s="5" t="inlineStr">
+    <row r="292" ht="14" customHeight="1">
+      <c r="A292" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B270" s="6" t="n"/>
-      <c r="C270" s="6" t="n"/>
-      <c r="D270" s="6" t="n"/>
-    </row>
-    <row r="271" ht="390" customHeight="1">
-      <c r="A271" s="7" t="inlineStr">
+      <c r="B292" s="6" t="n"/>
+      <c r="C292" s="6" t="n"/>
+      <c r="D292" s="6" t="n"/>
+    </row>
+    <row r="293" ht="384" customHeight="1">
+      <c r="A293" s="7" t="inlineStr">
         <is>
           <t>닥토! 팩토! 촉촉~
 콤부차 멀티 패드
@@ -9483,24 +9560,30 @@
 · 피부 생기와 윤기
 · 수분공급과 보유력증가
 · 피부의 장벽 튼튼
-피부에 참 좋은 콤부차
-초간단 멀티 패드 만들기로
+피부에 참 좋은 콤부차</t>
+        </is>
+      </c>
+    </row>
+    <row r="294" ht="32" customHeight="1">
+      <c r="A294" s="7" t="inlineStr">
+        <is>
+          <t>초간단 멀티 패드 만들기로
 피부에 직접 바르세요!</t>
         </is>
       </c>
     </row>
-    <row r="272" ht="14" customHeight="1">
-      <c r="A272" s="5" t="inlineStr">
+    <row r="295" ht="14" customHeight="1">
+      <c r="A295" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B272" s="6" t="n"/>
-      <c r="C272" s="6" t="n"/>
-      <c r="D272" s="6" t="n"/>
-    </row>
-    <row r="273" ht="135" customHeight="1">
-      <c r="A273" s="7" t="inlineStr">
+      <c r="B295" s="6" t="n"/>
+      <c r="C295" s="6" t="n"/>
+      <c r="D295" s="6" t="n"/>
+    </row>
+    <row r="296" ht="144" customHeight="1">
+      <c r="A296" s="7" t="inlineStr">
         <is>
           <t>콤부차 멀티 패드 만들기
 1. 분량의 콤부차를 넣고
@@ -9513,168 +9596,169 @@
         </is>
       </c>
     </row>
-    <row r="274" ht="14" customHeight="1">
-      <c r="A274" s="5" t="inlineStr">
+    <row r="297" ht="14" customHeight="1">
+      <c r="A297" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B274" s="6" t="n"/>
-      <c r="C274" s="6" t="n"/>
-      <c r="D274" s="6" t="n"/>
-    </row>
-    <row r="275" ht="171" customHeight="1"/>
-    <row r="276" ht="6" customHeight="1"/>
-    <row r="277" ht="22" customHeight="1">
-      <c r="A277" s="1" t="inlineStr">
+      <c r="B297" s="6" t="n"/>
+      <c r="C297" s="6" t="n"/>
+      <c r="D297" s="6" t="n"/>
+    </row>
+    <row r="298" ht="85.5" customHeight="1"/>
+    <row r="299" ht="85.5" customHeight="1"/>
+    <row r="300" ht="6" customHeight="1"/>
+    <row r="301" ht="22" customHeight="1">
+      <c r="A301" s="1" t="inlineStr">
         <is>
           <t>매트릭실 토너&amp;패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B277" s="2" t="n"/>
-      <c r="C277" s="2" t="n"/>
-      <c r="D277" s="2" t="n"/>
-    </row>
-    <row r="278" ht="15" customHeight="1">
-      <c r="A278" s="3" t="inlineStr">
+      <c r="B301" s="2" t="n"/>
+      <c r="C301" s="2" t="n"/>
+      <c r="D301" s="2" t="n"/>
+    </row>
+    <row r="302" ht="15" customHeight="1">
+      <c r="A302" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B278" s="3" t="inlineStr">
+      <c r="B302" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C278" s="3" t="inlineStr">
+      <c r="C302" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D278" s="3" t="inlineStr">
+      <c r="D302" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="279" ht="15" customHeight="1">
-      <c r="A279" s="8" t="inlineStr">
+    <row r="303" ht="16" customHeight="1">
+      <c r="A303" s="8" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B279" s="8" t="inlineStr">
+      <c r="B303" s="8" t="inlineStr">
         <is>
           <t>82g</t>
         </is>
       </c>
-      <c r="C279" s="8" t="inlineStr">
+      <c r="C303" s="8" t="inlineStr">
         <is>
           <t>불가리아 장미수</t>
         </is>
       </c>
-      <c r="D279" s="8" t="inlineStr">
+      <c r="D303" s="8" t="inlineStr">
         <is>
           <t>네롤리워터</t>
         </is>
       </c>
     </row>
-    <row r="280" ht="30" customHeight="1">
-      <c r="A280" s="8" t="inlineStr">
+    <row r="304" ht="48" customHeight="1">
+      <c r="A304" s="8" t="inlineStr">
         <is>
           <t>11히아루론산</t>
         </is>
       </c>
-      <c r="B280" s="8" t="inlineStr">
+      <c r="B304" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C280" s="8" t="inlineStr">
+      <c r="C304" s="8" t="inlineStr">
         <is>
           <t>크기가 다른 11가지 히아루론산 배합. / 피부 속부터 겉까지 수분 채움,</t>
         </is>
       </c>
-      <c r="D280" s="8" t="inlineStr">
+      <c r="D304" s="8" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="281" ht="15" customHeight="1">
-      <c r="A281" s="8" t="inlineStr">
+    <row r="305" ht="16" customHeight="1">
+      <c r="A305" s="8" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B281" s="8" t="inlineStr">
+      <c r="B305" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C281" s="8" t="inlineStr">
+      <c r="C305" s="8" t="inlineStr">
         <is>
           <t>비타민B3, 식약처 기능성 고시 원료</t>
         </is>
       </c>
-      <c r="D281" s="8" t="inlineStr">
+      <c r="D305" s="8" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="282" ht="30" customHeight="1">
-      <c r="A282" s="8" t="inlineStr">
+    <row r="306" ht="48" customHeight="1">
+      <c r="A306" s="8" t="inlineStr">
         <is>
           <t>매트릭실 3000</t>
         </is>
       </c>
-      <c r="B282" s="8" t="inlineStr">
+      <c r="B306" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C282" s="8" t="inlineStr">
+      <c r="C306" s="8" t="inlineStr">
         <is>
           <t>피부 내부의 재생 신호를 자극하여 콜라겐 생성을 돕는 메신저 펩타이드</t>
         </is>
       </c>
-      <c r="D282" s="8" t="n"/>
-    </row>
-    <row r="283" ht="45" customHeight="1">
-      <c r="A283" s="8" t="inlineStr">
+      <c r="D306" s="8" t="n"/>
+    </row>
+    <row r="307" ht="48" customHeight="1">
+      <c r="A307" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B283" s="8" t="inlineStr">
+      <c r="B307" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C283" s="8" t="inlineStr">
+      <c r="C307" s="8" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="D283" s="8" t="inlineStr">
+      <c r="D307" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="284" ht="14" customHeight="1">
-      <c r="A284" s="5" t="inlineStr">
+    <row r="308" ht="14" customHeight="1">
+      <c r="A308" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B284" s="6" t="n"/>
-      <c r="C284" s="6" t="n"/>
-      <c r="D284" s="6" t="n"/>
-    </row>
-    <row r="285" ht="315" customHeight="1">
-      <c r="A285" s="9" t="inlineStr">
+      <c r="B308" s="6" t="n"/>
+      <c r="C308" s="6" t="n"/>
+      <c r="D308" s="6" t="n"/>
+    </row>
+    <row r="309" ht="336" customHeight="1">
+      <c r="A309" s="9" t="inlineStr">
         <is>
           <t>집중 탄력 보습
 매트릭실 토너&amp;패드
@@ -9699,22 +9783,22 @@
 매끈하고 촉촉한 피부결을 완성하세요.</t>
         </is>
       </c>
-      <c r="B285" s="10" t="n"/>
-      <c r="C285" s="10" t="n"/>
-      <c r="D285" s="10" t="n"/>
-    </row>
-    <row r="286" ht="14" customHeight="1">
-      <c r="A286" s="5" t="inlineStr">
+      <c r="B309" s="10" t="n"/>
+      <c r="C309" s="10" t="n"/>
+      <c r="D309" s="10" t="n"/>
+    </row>
+    <row r="310" ht="14" customHeight="1">
+      <c r="A310" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B286" s="6" t="n"/>
-      <c r="C286" s="6" t="n"/>
-      <c r="D286" s="6" t="n"/>
-    </row>
-    <row r="287" ht="120" customHeight="1">
-      <c r="A287" s="9" t="inlineStr">
+      <c r="B310" s="6" t="n"/>
+      <c r="C310" s="6" t="n"/>
+      <c r="D310" s="6" t="n"/>
+    </row>
+    <row r="311" ht="128" customHeight="1">
+      <c r="A311" s="9" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 용기에 모든 재료를 계량한 후 섞어주세요.
@@ -9726,195 +9810,201 @@
 집게 사용으로 더욱 위생적으로 사용할 수 있어요.</t>
         </is>
       </c>
-      <c r="B287" s="10" t="n"/>
-      <c r="C287" s="10" t="n"/>
-      <c r="D287" s="10" t="n"/>
-    </row>
-    <row r="288" ht="14" customHeight="1">
-      <c r="A288" s="5" t="inlineStr">
+      <c r="B311" s="10" t="n"/>
+      <c r="C311" s="10" t="n"/>
+      <c r="D311" s="10" t="n"/>
+    </row>
+    <row r="312" ht="14" customHeight="1">
+      <c r="A312" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B288" s="6" t="n"/>
-      <c r="C288" s="6" t="n"/>
-      <c r="D288" s="6" t="n"/>
-    </row>
-    <row r="289" ht="171" customHeight="1">
-      <c r="A289" s="10" t="n"/>
-      <c r="B289" s="10" t="n"/>
-      <c r="C289" s="10" t="n"/>
-      <c r="D289" s="10" t="n"/>
-    </row>
-    <row r="290" ht="6" customHeight="1"/>
-    <row r="291" ht="22" customHeight="1">
-      <c r="A291" s="1" t="inlineStr">
+      <c r="B312" s="6" t="n"/>
+      <c r="C312" s="6" t="n"/>
+      <c r="D312" s="6" t="n"/>
+    </row>
+    <row r="313" ht="85.5" customHeight="1">
+      <c r="A313" s="10" t="n"/>
+      <c r="B313" s="10" t="n"/>
+      <c r="C313" s="10" t="n"/>
+      <c r="D313" s="10" t="n"/>
+    </row>
+    <row r="314" ht="85.5" customHeight="1">
+      <c r="A314" s="10" t="n"/>
+      <c r="B314" s="10" t="n"/>
+      <c r="C314" s="10" t="n"/>
+      <c r="D314" s="10" t="n"/>
+    </row>
+    <row r="315" ht="6" customHeight="1"/>
+    <row r="316" ht="22" customHeight="1">
+      <c r="A316" s="1" t="inlineStr">
         <is>
           <t>PDRN 힐링 토너 &amp; 멀티 패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B291" s="2" t="n"/>
-      <c r="C291" s="2" t="n"/>
-      <c r="D291" s="2" t="n"/>
-    </row>
-    <row r="292" ht="15" customHeight="1">
-      <c r="A292" s="3" t="inlineStr">
+      <c r="B316" s="2" t="n"/>
+      <c r="C316" s="2" t="n"/>
+      <c r="D316" s="2" t="n"/>
+    </row>
+    <row r="317" ht="15" customHeight="1">
+      <c r="A317" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B292" s="3" t="inlineStr">
+      <c r="B317" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C292" s="3" t="inlineStr">
+      <c r="C317" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D292" s="3" t="inlineStr">
+      <c r="D317" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="293" ht="60" customHeight="1">
-      <c r="A293" s="4" t="inlineStr">
+    <row r="318" ht="80" customHeight="1">
+      <c r="A318" s="4" t="inlineStr">
         <is>
           <t>네롤리워터</t>
         </is>
       </c>
-      <c r="B293" s="4" t="inlineStr">
+      <c r="B318" s="4" t="inlineStr">
         <is>
           <t>80g</t>
         </is>
       </c>
-      <c r="C293" s="4" t="inlineStr">
+      <c r="C318" s="4" t="inlineStr">
         <is>
           <t>오렌지꽃수, 진정, 아로마테라피</t>
         </is>
       </c>
-      <c r="D293" s="4" t="inlineStr">
+      <c r="D318" s="4" t="inlineStr">
         <is>
           <t>피부타입별 워터 / 트러블, 남성-편백 / 민감, 베이비-캐모마일 / 노화-로즈 / 남성-로즈마리</t>
         </is>
       </c>
     </row>
-    <row r="294" ht="30" customHeight="1">
-      <c r="A294" s="4" t="inlineStr">
+    <row r="319" ht="48" customHeight="1">
+      <c r="A319" s="4" t="inlineStr">
         <is>
           <t>메디 7솔루션</t>
         </is>
       </c>
-      <c r="B294" s="4" t="inlineStr">
+      <c r="B319" s="4" t="inlineStr">
         <is>
           <t>9g</t>
         </is>
       </c>
-      <c r="C294" s="4" t="inlineStr">
+      <c r="C319" s="4" t="inlineStr">
         <is>
           <t>진정, 병풀, 감초, 녹차, 황금, 로즈마리, 캐모마일, 호장근뿌리 추출물</t>
         </is>
       </c>
-      <c r="D294" s="4" t="n"/>
-    </row>
-    <row r="295" ht="15" customHeight="1">
-      <c r="A295" s="4" t="inlineStr">
+      <c r="D319" s="4" t="n"/>
+    </row>
+    <row r="320" ht="16" customHeight="1">
+      <c r="A320" s="4" t="inlineStr">
         <is>
           <t>PDRN</t>
         </is>
       </c>
-      <c r="B295" s="4" t="inlineStr">
+      <c r="B320" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C295" s="4" t="inlineStr">
+      <c r="C320" s="4" t="inlineStr">
         <is>
           <t>연어DNA, 항염, 재생</t>
         </is>
       </c>
-      <c r="D295" s="4" t="n"/>
-    </row>
-    <row r="296" ht="30" customHeight="1">
-      <c r="A296" s="4" t="inlineStr">
+      <c r="D320" s="4" t="n"/>
+    </row>
+    <row r="321" ht="32" customHeight="1">
+      <c r="A321" s="4" t="inlineStr">
         <is>
           <t>덱스 판테놀</t>
         </is>
       </c>
-      <c r="B296" s="4" t="inlineStr">
+      <c r="B321" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C296" s="4" t="inlineStr">
+      <c r="C321" s="4" t="inlineStr">
         <is>
           <t>보습, 재생, 비타민B5</t>
         </is>
       </c>
-      <c r="D296" s="4" t="inlineStr">
+      <c r="D321" s="4" t="inlineStr">
         <is>
           <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
         </is>
       </c>
     </row>
-    <row r="297" ht="15" customHeight="1">
-      <c r="A297" s="4" t="inlineStr">
+    <row r="322" ht="16" customHeight="1">
+      <c r="A322" s="4" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B297" s="4" t="inlineStr">
+      <c r="B322" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C297" s="4" t="inlineStr">
+      <c r="C322" s="4" t="inlineStr">
         <is>
           <t>식약처 인증 미백 원료 / 비타민 B3</t>
         </is>
       </c>
-      <c r="D297" s="4" t="inlineStr">
+      <c r="D322" s="4" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="298" ht="45" customHeight="1">
-      <c r="A298" s="4" t="inlineStr">
+    <row r="323" ht="48" customHeight="1">
+      <c r="A323" s="4" t="inlineStr">
         <is>
           <t>1,2 헥산디올</t>
         </is>
       </c>
-      <c r="B298" s="4" t="inlineStr">
+      <c r="B323" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C298" s="4" t="inlineStr">
+      <c r="C323" s="4" t="inlineStr">
         <is>
           <t>방부, 보습</t>
         </is>
       </c>
-      <c r="D298" s="4" t="inlineStr">
+      <c r="D323" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="299" ht="14" customHeight="1">
-      <c r="A299" s="5" t="inlineStr">
+    <row r="324" ht="14" customHeight="1">
+      <c r="A324" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B299" s="6" t="n"/>
-      <c r="C299" s="6" t="n"/>
-      <c r="D299" s="6" t="n"/>
-    </row>
-    <row r="300" ht="345" customHeight="1">
-      <c r="A300" s="7" t="inlineStr">
+      <c r="B324" s="6" t="n"/>
+      <c r="C324" s="6" t="n"/>
+      <c r="D324" s="6" t="n"/>
+    </row>
+    <row r="325" ht="368" customHeight="1">
+      <c r="A325" s="7" t="inlineStr">
         <is>
           <t>매일 매일 피부 리셋! PDRN 힐링 토너 &amp; 멀티 패드
 (100g)
@@ -9942,18 +10032,18 @@
         </is>
       </c>
     </row>
-    <row r="301" ht="14" customHeight="1">
-      <c r="A301" s="5" t="inlineStr">
+    <row r="326" ht="14" customHeight="1">
+      <c r="A326" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B301" s="6" t="n"/>
-      <c r="C301" s="6" t="n"/>
-      <c r="D301" s="6" t="n"/>
-    </row>
-    <row r="302" ht="150" customHeight="1">
-      <c r="A302" s="7" t="inlineStr">
+      <c r="B326" s="6" t="n"/>
+      <c r="C326" s="6" t="n"/>
+      <c r="D326" s="6" t="n"/>
+    </row>
+    <row r="327" ht="160" customHeight="1">
+      <c r="A327" s="7" t="inlineStr">
         <is>
           <t>PDRN 토너 &amp; 멀티 패드 만들기
 1. 용기에 재료를 계량해주세요.
@@ -9966,212 +10056,213 @@
         </is>
       </c>
     </row>
-    <row r="303" ht="14" customHeight="1">
-      <c r="A303" s="5" t="inlineStr">
+    <row r="328" ht="14" customHeight="1">
+      <c r="A328" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B303" s="6" t="n"/>
-      <c r="C303" s="6" t="n"/>
-      <c r="D303" s="6" t="n"/>
-    </row>
-    <row r="304" ht="171" customHeight="1"/>
-    <row r="305" ht="6" customHeight="1"/>
-    <row r="306" ht="22" customHeight="1">
-      <c r="A306" s="1" t="inlineStr">
+      <c r="B328" s="6" t="n"/>
+      <c r="C328" s="6" t="n"/>
+      <c r="D328" s="6" t="n"/>
+    </row>
+    <row r="329" ht="85.5" customHeight="1"/>
+    <row r="330" ht="85.5" customHeight="1"/>
+    <row r="331" ht="6" customHeight="1"/>
+    <row r="332" ht="22" customHeight="1">
+      <c r="A332" s="1" t="inlineStr">
         <is>
           <t>뮤신 콜라겐 토너 &amp; 멀티패드    [1]    ↗ 원본</t>
         </is>
       </c>
-      <c r="B306" s="2" t="n"/>
-      <c r="C306" s="2" t="n"/>
-      <c r="D306" s="2" t="n"/>
-    </row>
-    <row r="307" ht="15" customHeight="1">
-      <c r="A307" s="3" t="inlineStr">
+      <c r="B332" s="2" t="n"/>
+      <c r="C332" s="2" t="n"/>
+      <c r="D332" s="2" t="n"/>
+    </row>
+    <row r="333" ht="15" customHeight="1">
+      <c r="A333" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B307" s="3" t="inlineStr">
+      <c r="B333" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C307" s="3" t="inlineStr">
+      <c r="C333" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D307" s="3" t="inlineStr">
+      <c r="D333" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="308" ht="30" customHeight="1">
-      <c r="A308" s="8" t="inlineStr">
+    <row r="334" ht="32" customHeight="1">
+      <c r="A334" s="8" t="inlineStr">
         <is>
           <t>글리세린</t>
         </is>
       </c>
-      <c r="B308" s="8" t="inlineStr">
+      <c r="B334" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C308" s="8" t="inlineStr">
+      <c r="C334" s="8" t="inlineStr">
         <is>
           <t>보습, 쟁탄검을 잘풀리게</t>
         </is>
       </c>
-      <c r="D308" s="8" t="inlineStr">
+      <c r="D334" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="309" ht="15" customHeight="1">
-      <c r="A309" s="8" t="inlineStr">
+    <row r="335" ht="16" customHeight="1">
+      <c r="A335" s="8" t="inlineStr">
         <is>
           <t>쟁탄검</t>
         </is>
       </c>
-      <c r="B309" s="8" t="inlineStr">
+      <c r="B335" s="8" t="inlineStr">
         <is>
           <t>0.3g</t>
         </is>
       </c>
-      <c r="C309" s="8" t="inlineStr">
+      <c r="C335" s="8" t="inlineStr">
         <is>
           <t>사탕수수 채취, 점증제</t>
         </is>
       </c>
-      <c r="D309" s="8" t="n"/>
-    </row>
-    <row r="310" ht="15" customHeight="1">
-      <c r="A310" s="8" t="inlineStr">
+      <c r="D335" s="8" t="n"/>
+    </row>
+    <row r="336" ht="16" customHeight="1">
+      <c r="A336" s="8" t="inlineStr">
         <is>
           <t>네롤리워터</t>
         </is>
       </c>
-      <c r="B310" s="8" t="inlineStr">
+      <c r="B336" s="8" t="inlineStr">
         <is>
           <t>74.7g</t>
         </is>
       </c>
-      <c r="C310" s="8" t="inlineStr">
+      <c r="C336" s="8" t="inlineStr">
         <is>
           <t>오렌지꽃워터</t>
         </is>
       </c>
-      <c r="D310" s="8" t="inlineStr">
+      <c r="D336" s="8" t="inlineStr">
         <is>
           <t>원하는 워터</t>
         </is>
       </c>
     </row>
-    <row r="311" ht="30" customHeight="1">
-      <c r="A311" s="8" t="inlineStr">
+    <row r="337" ht="32" customHeight="1">
+      <c r="A337" s="8" t="inlineStr">
         <is>
           <t>뮤신(블랙 스네일)</t>
         </is>
       </c>
-      <c r="B311" s="8" t="inlineStr">
+      <c r="B337" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C311" s="8" t="inlineStr">
+      <c r="C337" s="8" t="inlineStr">
         <is>
           <t>검은 달팽이 점액 유래</t>
         </is>
       </c>
-      <c r="D311" s="8" t="inlineStr">
+      <c r="D337" s="8" t="inlineStr">
         <is>
           <t>EGF, 아세틸헥사펩타이드, 콜라겐 등등...</t>
         </is>
       </c>
     </row>
-    <row r="312" ht="30" customHeight="1">
-      <c r="A312" s="8" t="inlineStr">
+    <row r="338" ht="32" customHeight="1">
+      <c r="A338" s="8" t="inlineStr">
         <is>
           <t>콜라겐7 컴플렉스</t>
         </is>
       </c>
-      <c r="B312" s="8" t="inlineStr">
+      <c r="B338" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C312" s="8" t="inlineStr">
+      <c r="C338" s="8" t="inlineStr">
         <is>
           <t>7가지 콜라겐 복합원료</t>
         </is>
       </c>
-      <c r="D312" s="8" t="inlineStr">
+      <c r="D338" s="8" t="inlineStr">
         <is>
           <t>콜라겐 펩타이드, 아미노산17</t>
         </is>
       </c>
     </row>
-    <row r="313" ht="30" customHeight="1">
-      <c r="A313" s="8" t="inlineStr">
+    <row r="339" ht="32" customHeight="1">
+      <c r="A339" s="8" t="inlineStr">
         <is>
           <t>알란토인(액상)</t>
         </is>
       </c>
-      <c r="B313" s="8" t="inlineStr">
+      <c r="B339" s="8" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C313" s="8" t="inlineStr">
+      <c r="C339" s="8" t="inlineStr">
         <is>
           <t>피부진정 및 완화 효과</t>
         </is>
       </c>
-      <c r="D313" s="8" t="inlineStr">
+      <c r="D339" s="8" t="inlineStr">
         <is>
           <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
-    <row r="314" ht="45" customHeight="1">
-      <c r="A314" s="8" t="inlineStr">
+    <row r="340" ht="48" customHeight="1">
+      <c r="A340" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B314" s="8" t="inlineStr">
+      <c r="B340" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C314" s="8" t="inlineStr">
+      <c r="C340" s="8" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="D314" s="8" t="inlineStr">
+      <c r="D340" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="315" ht="14" customHeight="1">
-      <c r="A315" s="5" t="inlineStr">
+    <row r="341" ht="14" customHeight="1">
+      <c r="A341" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B315" s="6" t="n"/>
-      <c r="C315" s="6" t="n"/>
-      <c r="D315" s="6" t="n"/>
-    </row>
-    <row r="316" ht="330" customHeight="1">
-      <c r="A316" s="9" t="inlineStr">
+      <c r="B341" s="6" t="n"/>
+      <c r="C341" s="6" t="n"/>
+      <c r="D341" s="6" t="n"/>
+    </row>
+    <row r="342" ht="352" customHeight="1">
+      <c r="A342" s="9" t="inlineStr">
         <is>
           <t>달팽이, 피부 시간을 느리게
 뮤신 콜라겐 토너 &amp; 멀티패드
@@ -10197,22 +10288,22 @@
 피부의 시간을 느리게 하세요.</t>
         </is>
       </c>
-      <c r="B316" s="10" t="n"/>
-      <c r="C316" s="10" t="n"/>
-      <c r="D316" s="10" t="n"/>
-    </row>
-    <row r="317" ht="14" customHeight="1">
-      <c r="A317" s="5" t="inlineStr">
+      <c r="B342" s="10" t="n"/>
+      <c r="C342" s="10" t="n"/>
+      <c r="D342" s="10" t="n"/>
+    </row>
+    <row r="343" ht="14" customHeight="1">
+      <c r="A343" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B317" s="6" t="n"/>
-      <c r="C317" s="6" t="n"/>
-      <c r="D317" s="6" t="n"/>
-    </row>
-    <row r="318" ht="150" customHeight="1">
-      <c r="A318" s="9" t="inlineStr">
+      <c r="B343" s="6" t="n"/>
+      <c r="C343" s="6" t="n"/>
+      <c r="D343" s="6" t="n"/>
+    </row>
+    <row r="344" ht="160" customHeight="1">
+      <c r="A344" s="9" t="inlineStr">
         <is>
           <t>뮤신 콜라겐 토너 &amp; 멀티 패드 만들기
 1. 먼저 글리세린과 쟁탄검을 계량한 후 골고루 섞어주세요.
@@ -10225,199 +10316,205 @@
 (매끈한 면은 에센스 팩용으로 엠보면은 각질, 노폐물 제거용으로 사용하세요.)</t>
         </is>
       </c>
-      <c r="B318" s="10" t="n"/>
-      <c r="C318" s="10" t="n"/>
-      <c r="D318" s="10" t="n"/>
-    </row>
-    <row r="319" ht="14" customHeight="1">
-      <c r="A319" s="5" t="inlineStr">
+      <c r="B344" s="10" t="n"/>
+      <c r="C344" s="10" t="n"/>
+      <c r="D344" s="10" t="n"/>
+    </row>
+    <row r="345" ht="14" customHeight="1">
+      <c r="A345" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B319" s="6" t="n"/>
-      <c r="C319" s="6" t="n"/>
-      <c r="D319" s="6" t="n"/>
-    </row>
-    <row r="320" ht="171" customHeight="1">
-      <c r="A320" s="10" t="n"/>
-      <c r="B320" s="10" t="n"/>
-      <c r="C320" s="10" t="n"/>
-      <c r="D320" s="10" t="n"/>
-    </row>
-    <row r="321" ht="6" customHeight="1"/>
-    <row r="322" ht="22" customHeight="1">
-      <c r="A322" s="1" t="inlineStr">
+      <c r="B345" s="6" t="n"/>
+      <c r="C345" s="6" t="n"/>
+      <c r="D345" s="6" t="n"/>
+    </row>
+    <row r="346" ht="85.5" customHeight="1">
+      <c r="A346" s="10" t="n"/>
+      <c r="B346" s="10" t="n"/>
+      <c r="C346" s="10" t="n"/>
+      <c r="D346" s="10" t="n"/>
+    </row>
+    <row r="347" ht="85.5" customHeight="1">
+      <c r="A347" s="10" t="n"/>
+      <c r="B347" s="10" t="n"/>
+      <c r="C347" s="10" t="n"/>
+      <c r="D347" s="10" t="n"/>
+    </row>
+    <row r="348" ht="6" customHeight="1"/>
+    <row r="349" ht="22" customHeight="1">
+      <c r="A349" s="1" t="inlineStr">
         <is>
           <t>TX 토닝 토너(미스트)&amp;패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B322" s="2" t="n"/>
-      <c r="C322" s="2" t="n"/>
-      <c r="D322" s="2" t="n"/>
-    </row>
-    <row r="323" ht="15" customHeight="1">
-      <c r="A323" s="3" t="inlineStr">
+      <c r="B349" s="2" t="n"/>
+      <c r="C349" s="2" t="n"/>
+      <c r="D349" s="2" t="n"/>
+    </row>
+    <row r="350" ht="15" customHeight="1">
+      <c r="A350" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B323" s="3" t="inlineStr">
+      <c r="B350" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C323" s="3" t="inlineStr">
+      <c r="C350" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D323" s="3" t="inlineStr">
+      <c r="D350" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="324" ht="30" customHeight="1">
-      <c r="A324" s="4" t="inlineStr">
+    <row r="351" ht="32" customHeight="1">
+      <c r="A351" s="4" t="inlineStr">
         <is>
           <t>로즈워터</t>
         </is>
       </c>
-      <c r="B324" s="4" t="inlineStr">
+      <c r="B351" s="4" t="inlineStr">
         <is>
           <t>83g</t>
         </is>
       </c>
-      <c r="C324" s="4" t="inlineStr">
+      <c r="C351" s="4" t="inlineStr">
         <is>
           <t>불가리아 장미수</t>
         </is>
       </c>
-      <c r="D324" s="4" t="inlineStr">
+      <c r="D351" s="4" t="inlineStr">
         <is>
           <t>라벤더, 티트리, 네롤리, 일랑일랑워터 등</t>
         </is>
       </c>
     </row>
-    <row r="325" ht="45" customHeight="1">
-      <c r="A325" s="4" t="inlineStr">
+    <row r="352" ht="48" customHeight="1">
+      <c r="A352" s="4" t="inlineStr">
         <is>
           <t>트라넥삼산 (펩타이드)</t>
         </is>
       </c>
-      <c r="B325" s="4" t="inlineStr">
+      <c r="B352" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C325" s="4" t="inlineStr">
+      <c r="C352" s="4" t="inlineStr">
         <is>
           <t>기미 개선효과가 뛰어난 트라넥사민산(을 펩타이드 말단에 합성으로 도입시킨 비타민 펩타이드)</t>
         </is>
       </c>
-      <c r="D325" s="4" t="inlineStr">
+      <c r="D352" s="4" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="326" ht="15" customHeight="1">
-      <c r="A326" s="4" t="inlineStr">
+    <row r="353" ht="16" customHeight="1">
+      <c r="A353" s="4" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B326" s="4" t="inlineStr">
+      <c r="B353" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C326" s="4" t="inlineStr">
+      <c r="C353" s="4" t="inlineStr">
         <is>
           <t>비타민B3, 식약처 기능성 고시원료</t>
         </is>
       </c>
-      <c r="D326" s="4" t="inlineStr">
+      <c r="D353" s="4" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="327" ht="15" customHeight="1">
-      <c r="A327" s="4" t="inlineStr">
+    <row r="354" ht="16" customHeight="1">
+      <c r="A354" s="4" t="inlineStr">
         <is>
           <t>글루타치온</t>
         </is>
       </c>
-      <c r="B327" s="4" t="inlineStr">
+      <c r="B354" s="4" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C327" s="4" t="inlineStr">
+      <c r="C354" s="4" t="inlineStr">
         <is>
           <t>미백 효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="D327" s="4" t="n"/>
-    </row>
-    <row r="328" ht="15" customHeight="1">
-      <c r="A328" s="4" t="inlineStr">
+      <c r="D354" s="4" t="n"/>
+    </row>
+    <row r="355" ht="16" customHeight="1">
+      <c r="A355" s="4" t="inlineStr">
         <is>
           <t>덱스판테놀</t>
         </is>
       </c>
-      <c r="B328" s="4" t="inlineStr">
+      <c r="B355" s="4" t="inlineStr">
         <is>
           <t>1g</t>
         </is>
       </c>
-      <c r="C328" s="4" t="inlineStr">
+      <c r="C355" s="4" t="inlineStr">
         <is>
           <t>비타민B5, 보습 재생</t>
         </is>
       </c>
-      <c r="D328" s="4" t="inlineStr">
+      <c r="D355" s="4" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
     </row>
-    <row r="329" ht="45" customHeight="1">
-      <c r="A329" s="4" t="inlineStr">
+    <row r="356" ht="48" customHeight="1">
+      <c r="A356" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B329" s="4" t="inlineStr">
+      <c r="B356" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C329" s="4" t="inlineStr">
+      <c r="C356" s="4" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="D329" s="4" t="inlineStr">
+      <c r="D356" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="330" ht="14" customHeight="1">
-      <c r="A330" s="5" t="inlineStr">
+    <row r="357" ht="14" customHeight="1">
+      <c r="A357" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B330" s="6" t="n"/>
-      <c r="C330" s="6" t="n"/>
-      <c r="D330" s="6" t="n"/>
-    </row>
-    <row r="331" ht="495" customHeight="1">
-      <c r="A331" s="7" t="inlineStr">
+      <c r="B357" s="6" t="n"/>
+      <c r="C357" s="6" t="n"/>
+      <c r="D357" s="6" t="n"/>
+    </row>
+    <row r="358" ht="384" customHeight="1">
+      <c r="A358" s="7" t="inlineStr">
         <is>
           <t>잡티, 기미 싹~~지우개!
 TX 토닝 토너&amp;패드
@@ -10442,8 +10539,14 @@
 이후 많은 논문이 발표되고 기미치료제로도 효능이 검증되었습니다.
 안정성 확보와 함께 먹는 기미약으로 처방되고 있습니다.
 (먹는 약으로 보령제약 트라*노정)
-바르는 기미화장품으로도 효능을 나타냅니다.
-미백에 효과적인 하이드로퀴논 성분은 자극감, 홍조 등 부작용이 있는데
+바르는 기미화장품으로도 효능을 나타냅니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="359" ht="144" customHeight="1">
+      <c r="A359" s="7" t="inlineStr">
+        <is>
+          <t>미백에 효과적인 하이드로퀴논 성분은 자극감, 홍조 등 부작용이 있는데
 트라넥삼산은 부작용은 거의 없고 효과는 비슷합니다.
 (트라넥삼산의 효과를 배가 시키기 위해
 펩타이드와 결합시킨 트레넥삼산 펩타이드도 사용 가능합니다.
@@ -10455,18 +10558,18 @@
         </is>
       </c>
     </row>
-    <row r="332" ht="14" customHeight="1">
-      <c r="A332" s="5" t="inlineStr">
+    <row r="360" ht="14" customHeight="1">
+      <c r="A360" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B332" s="6" t="n"/>
-      <c r="C332" s="6" t="n"/>
-      <c r="D332" s="6" t="n"/>
-    </row>
-    <row r="333" ht="120" customHeight="1">
-      <c r="A333" s="7" t="inlineStr">
+      <c r="B360" s="6" t="n"/>
+      <c r="C360" s="6" t="n"/>
+      <c r="D360" s="6" t="n"/>
+    </row>
+    <row r="361" ht="128" customHeight="1">
+      <c r="A361" s="7" t="inlineStr">
         <is>
           <t>TX 멜라 토너&amp;패드 만들기
 1. 용기에 모든 재료를 계량한 후 섞어주세요.
@@ -10478,230 +10581,231 @@
         </is>
       </c>
     </row>
-    <row r="334" ht="14" customHeight="1">
-      <c r="A334" s="5" t="inlineStr">
+    <row r="362" ht="14" customHeight="1">
+      <c r="A362" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B334" s="6" t="n"/>
-      <c r="C334" s="6" t="n"/>
-      <c r="D334" s="6" t="n"/>
-    </row>
-    <row r="335" ht="171" customHeight="1"/>
-    <row r="336" ht="6" customHeight="1"/>
-    <row r="337" ht="22" customHeight="1">
-      <c r="A337" s="1" t="inlineStr">
+      <c r="B362" s="6" t="n"/>
+      <c r="C362" s="6" t="n"/>
+      <c r="D362" s="6" t="n"/>
+    </row>
+    <row r="363" ht="85.5" customHeight="1"/>
+    <row r="364" ht="85.5" customHeight="1"/>
+    <row r="365" ht="6" customHeight="1"/>
+    <row r="366" ht="22" customHeight="1">
+      <c r="A366" s="1" t="inlineStr">
         <is>
           <t>비타민C 기미 토너&amp;실크패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B337" s="2" t="n"/>
-      <c r="C337" s="2" t="n"/>
-      <c r="D337" s="2" t="n"/>
-    </row>
-    <row r="338" ht="15" customHeight="1">
-      <c r="A338" s="3" t="inlineStr">
+      <c r="B366" s="2" t="n"/>
+      <c r="C366" s="2" t="n"/>
+      <c r="D366" s="2" t="n"/>
+    </row>
+    <row r="367" ht="15" customHeight="1">
+      <c r="A367" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B338" s="3" t="inlineStr">
+      <c r="B367" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C338" s="3" t="inlineStr">
+      <c r="C367" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D338" s="3" t="inlineStr">
+      <c r="D367" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="339" ht="45" customHeight="1">
-      <c r="A339" s="8" t="inlineStr">
+    <row r="368" ht="48" customHeight="1">
+      <c r="A368" s="8" t="inlineStr">
         <is>
           <t>프리미엄 비타민C / (에칠아스코빌에텔)</t>
         </is>
       </c>
-      <c r="B339" s="8" t="inlineStr">
+      <c r="B368" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C339" s="8" t="inlineStr">
+      <c r="C368" s="8" t="inlineStr">
         <is>
           <t>비타민C의 장점은 살리고 단점은 보완, / 식약처 미백 고시 원료, 미백, 탄력</t>
         </is>
       </c>
-      <c r="D339" s="8" t="n"/>
-    </row>
-    <row r="340" ht="30" customHeight="1">
-      <c r="A340" s="8" t="inlineStr">
+      <c r="D368" s="8" t="n"/>
+    </row>
+    <row r="369" ht="32" customHeight="1">
+      <c r="A369" s="8" t="inlineStr">
         <is>
           <t>나이아신아마이드</t>
         </is>
       </c>
-      <c r="B340" s="8" t="inlineStr">
+      <c r="B369" s="8" t="inlineStr">
         <is>
           <t>3g</t>
         </is>
       </c>
-      <c r="C340" s="8" t="inlineStr">
+      <c r="C369" s="8" t="inlineStr">
         <is>
           <t>비타민B3, 생긴 멜라닌 색소 발현 억제</t>
         </is>
       </c>
-      <c r="D340" s="8" t="inlineStr">
+      <c r="D369" s="8" t="inlineStr">
         <is>
           <t>화이트펩타이드</t>
         </is>
       </c>
     </row>
-    <row r="341" ht="30" customHeight="1">
-      <c r="A341" s="8" t="inlineStr">
+    <row r="370" ht="32" customHeight="1">
+      <c r="A370" s="8" t="inlineStr">
         <is>
           <t>(유기농) 글리세린</t>
         </is>
       </c>
-      <c r="B341" s="8" t="inlineStr">
+      <c r="B370" s="8" t="inlineStr">
         <is>
           <t>4g</t>
         </is>
       </c>
-      <c r="C341" s="8" t="inlineStr">
+      <c r="C370" s="8" t="inlineStr">
         <is>
           <t>보습</t>
         </is>
       </c>
-      <c r="D341" s="8" t="inlineStr">
+      <c r="D370" s="8" t="inlineStr">
         <is>
           <t>모이스틴가능. 히아루론산은 사용하지마세요.</t>
         </is>
       </c>
     </row>
-    <row r="342" ht="30" customHeight="1">
-      <c r="A342" s="8" t="inlineStr">
+    <row r="371" ht="32" customHeight="1">
+      <c r="A371" s="8" t="inlineStr">
         <is>
           <t>덱스판테놀</t>
         </is>
       </c>
-      <c r="B342" s="8" t="inlineStr">
+      <c r="B371" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C342" s="8" t="inlineStr">
+      <c r="C371" s="8" t="inlineStr">
         <is>
           <t>비타민B5, 보습, 재생</t>
         </is>
       </c>
-      <c r="D342" s="8" t="inlineStr">
+      <c r="D371" s="8" t="inlineStr">
         <is>
           <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
         </is>
       </c>
     </row>
-    <row r="343" ht="15" customHeight="1">
-      <c r="A343" s="8" t="inlineStr">
+    <row r="372" ht="16" customHeight="1">
+      <c r="A372" s="8" t="inlineStr">
         <is>
           <t>다중 히아루론산</t>
         </is>
       </c>
-      <c r="B343" s="8" t="inlineStr">
+      <c r="B372" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C343" s="8" t="inlineStr">
+      <c r="C372" s="8" t="inlineStr">
         <is>
           <t>촘촘 보습 고중저분자 히아루론산</t>
         </is>
       </c>
-      <c r="D343" s="8" t="inlineStr">
+      <c r="D372" s="8" t="inlineStr">
         <is>
           <t>에코 / 보습제</t>
         </is>
       </c>
     </row>
-    <row r="344" ht="30" customHeight="1">
-      <c r="A344" s="8" t="inlineStr">
+    <row r="373" ht="32" customHeight="1">
+      <c r="A373" s="8" t="inlineStr">
         <is>
           <t>비타민 열매 3</t>
         </is>
       </c>
-      <c r="B344" s="8" t="inlineStr">
+      <c r="B373" s="8" t="inlineStr">
         <is>
           <t>5g</t>
         </is>
       </c>
-      <c r="C344" s="8" t="inlineStr">
+      <c r="C373" s="8" t="inlineStr">
         <is>
           <t>미백 3종 복합 원료 / (비타민나무열매, 유자, 오미자)</t>
         </is>
       </c>
-      <c r="D344" s="8" t="n"/>
-    </row>
-    <row r="345" ht="15" customHeight="1">
-      <c r="A345" s="8" t="inlineStr">
+      <c r="D373" s="8" t="n"/>
+    </row>
+    <row r="374" ht="16" customHeight="1">
+      <c r="A374" s="8" t="inlineStr">
         <is>
           <t>비타민 나무 워터</t>
         </is>
       </c>
-      <c r="B345" s="8" t="inlineStr">
+      <c r="B374" s="8" t="inlineStr">
         <is>
           <t>77g</t>
         </is>
       </c>
-      <c r="C345" s="8" t="inlineStr">
+      <c r="C374" s="8" t="inlineStr">
         <is>
           <t>비타민 나무 열매 수증기 증류수</t>
         </is>
       </c>
-      <c r="D345" s="8" t="inlineStr">
+      <c r="D374" s="8" t="inlineStr">
         <is>
           <t>원하는 워터</t>
         </is>
       </c>
     </row>
-    <row r="346" ht="45" customHeight="1">
-      <c r="A346" s="8" t="inlineStr">
+    <row r="375" ht="48" customHeight="1">
+      <c r="A375" s="8" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B346" s="8" t="inlineStr">
+      <c r="B375" s="8" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C346" s="8" t="inlineStr">
+      <c r="C375" s="8" t="inlineStr">
         <is>
           <t>방부, 보습</t>
         </is>
       </c>
-      <c r="D346" s="8" t="inlineStr">
+      <c r="D375" s="8" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="347" ht="14" customHeight="1">
-      <c r="A347" s="5" t="inlineStr">
+    <row r="376" ht="14" customHeight="1">
+      <c r="A376" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B347" s="6" t="n"/>
-      <c r="C347" s="6" t="n"/>
-      <c r="D347" s="6" t="n"/>
-    </row>
-    <row r="348" ht="405" customHeight="1">
-      <c r="A348" s="9" t="inlineStr">
+      <c r="B376" s="6" t="n"/>
+      <c r="C376" s="6" t="n"/>
+      <c r="D376" s="6" t="n"/>
+    </row>
+    <row r="377" ht="384" customHeight="1">
+      <c r="A377" s="9" t="inlineStr">
         <is>
           <t>수분충전과 미백을 동시에~
 비타민C 기미 토너&amp;실크패드
@@ -10726,28 +10830,37 @@
 에칠아스코르빌에텔(EAA)입니다.
 비타민C 함량(86.3%)이 가장 높고 흡수력이 좋고
 적정 pH로 어디에든 적용이 가능합니다.
-산화 안정력도 좋습니다.
-토너와 실크패드로
+산화 안정력도 좋습니다.</t>
+        </is>
+      </c>
+      <c r="B377" s="10" t="n"/>
+      <c r="C377" s="10" t="n"/>
+      <c r="D377" s="10" t="n"/>
+    </row>
+    <row r="378" ht="48" customHeight="1">
+      <c r="A378" s="9" t="inlineStr">
+        <is>
+          <t>토너와 실크패드로
 데일리로 부담 없이 사용할 수 있는
 비타민C 미백 케어를 완성해보세요.</t>
         </is>
       </c>
-      <c r="B348" s="10" t="n"/>
-      <c r="C348" s="10" t="n"/>
-      <c r="D348" s="10" t="n"/>
-    </row>
-    <row r="349" ht="14" customHeight="1">
-      <c r="A349" s="5" t="inlineStr">
+      <c r="B378" s="10" t="n"/>
+      <c r="C378" s="10" t="n"/>
+      <c r="D378" s="10" t="n"/>
+    </row>
+    <row r="379" ht="14" customHeight="1">
+      <c r="A379" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B349" s="6" t="n"/>
-      <c r="C349" s="6" t="n"/>
-      <c r="D349" s="6" t="n"/>
-    </row>
-    <row r="350" ht="120" customHeight="1">
-      <c r="A350" s="9" t="inlineStr">
+      <c r="B379" s="6" t="n"/>
+      <c r="C379" s="6" t="n"/>
+      <c r="D379" s="6" t="n"/>
+    </row>
+    <row r="380" ht="128" customHeight="1">
+      <c r="A380" s="9" t="inlineStr">
         <is>
           <t>만들기 과정
 1. 용기에 모든 재료를 계량한 후 섞어주세요.
@@ -10759,195 +10872,201 @@
 집게 사용으로 더욱 위생적으로 사용할 수 있어요.</t>
         </is>
       </c>
-      <c r="B350" s="10" t="n"/>
-      <c r="C350" s="10" t="n"/>
-      <c r="D350" s="10" t="n"/>
-    </row>
-    <row r="351" ht="14" customHeight="1">
-      <c r="A351" s="5" t="inlineStr">
+      <c r="B380" s="10" t="n"/>
+      <c r="C380" s="10" t="n"/>
+      <c r="D380" s="10" t="n"/>
+    </row>
+    <row r="381" ht="14" customHeight="1">
+      <c r="A381" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B351" s="6" t="n"/>
-      <c r="C351" s="6" t="n"/>
-      <c r="D351" s="6" t="n"/>
-    </row>
-    <row r="352" ht="171" customHeight="1">
-      <c r="A352" s="10" t="n"/>
-      <c r="B352" s="10" t="n"/>
-      <c r="C352" s="10" t="n"/>
-      <c r="D352" s="10" t="n"/>
-    </row>
-    <row r="353" ht="6" customHeight="1"/>
-    <row r="354" ht="22" customHeight="1">
-      <c r="A354" s="1" t="inlineStr">
+      <c r="B381" s="6" t="n"/>
+      <c r="C381" s="6" t="n"/>
+      <c r="D381" s="6" t="n"/>
+    </row>
+    <row r="382" ht="85.5" customHeight="1">
+      <c r="A382" s="10" t="n"/>
+      <c r="B382" s="10" t="n"/>
+      <c r="C382" s="10" t="n"/>
+      <c r="D382" s="10" t="n"/>
+    </row>
+    <row r="383" ht="85.5" customHeight="1">
+      <c r="A383" s="10" t="n"/>
+      <c r="B383" s="10" t="n"/>
+      <c r="C383" s="10" t="n"/>
+      <c r="D383" s="10" t="n"/>
+    </row>
+    <row r="384" ht="6" customHeight="1"/>
+    <row r="385" ht="22" customHeight="1">
+      <c r="A385" s="1" t="inlineStr">
         <is>
           <t>개똥쑥 진정 토너&amp;패드    ↗ 원본</t>
         </is>
       </c>
-      <c r="B354" s="2" t="n"/>
-      <c r="C354" s="2" t="n"/>
-      <c r="D354" s="2" t="n"/>
-    </row>
-    <row r="355" ht="15" customHeight="1">
-      <c r="A355" s="3" t="inlineStr">
+      <c r="B385" s="2" t="n"/>
+      <c r="C385" s="2" t="n"/>
+      <c r="D385" s="2" t="n"/>
+    </row>
+    <row r="386" ht="15" customHeight="1">
+      <c r="A386" s="3" t="inlineStr">
         <is>
           <t>재료</t>
         </is>
       </c>
-      <c r="B355" s="3" t="inlineStr">
+      <c r="B386" s="3" t="inlineStr">
         <is>
           <t>용량</t>
         </is>
       </c>
-      <c r="C355" s="3" t="inlineStr">
+      <c r="C386" s="3" t="inlineStr">
         <is>
           <t>특징</t>
         </is>
       </c>
-      <c r="D355" s="3" t="inlineStr">
+      <c r="D386" s="3" t="inlineStr">
         <is>
           <t>대체재료</t>
         </is>
       </c>
     </row>
-    <row r="356" ht="45" customHeight="1">
-      <c r="A356" s="4" t="inlineStr">
+    <row r="387" ht="48" customHeight="1">
+      <c r="A387" s="4" t="inlineStr">
         <is>
           <t>로먼캐모마일워터</t>
         </is>
       </c>
-      <c r="B356" s="4" t="inlineStr">
+      <c r="B387" s="4" t="inlineStr">
         <is>
           <t>40g</t>
         </is>
       </c>
-      <c r="C356" s="4" t="inlineStr">
+      <c r="C387" s="4" t="inlineStr">
         <is>
           <t>로먼캐모마일 꽃을 증기추출</t>
         </is>
       </c>
-      <c r="D356" s="4" t="inlineStr">
+      <c r="D387" s="4" t="inlineStr">
         <is>
           <t>편백워터, 로즈마리워터, 라벤더워터 등 두피상태에 따라 선택.</t>
         </is>
       </c>
     </row>
-    <row r="357" ht="30" customHeight="1">
-      <c r="A357" s="4" t="inlineStr">
+    <row r="388" ht="32" customHeight="1">
+      <c r="A388" s="4" t="inlineStr">
         <is>
           <t>개똥쑥추출물</t>
         </is>
       </c>
-      <c r="B357" s="4" t="inlineStr">
+      <c r="B388" s="4" t="inlineStr">
         <is>
           <t>33g</t>
         </is>
       </c>
-      <c r="C357" s="4" t="inlineStr">
+      <c r="C388" s="4" t="inlineStr">
         <is>
           <t>노벨상 받은 쑥, / 비타민 풍부, 진정</t>
         </is>
       </c>
-      <c r="D357" s="4" t="n"/>
-    </row>
-    <row r="358" ht="30" customHeight="1">
-      <c r="A358" s="4" t="inlineStr">
+      <c r="D388" s="4" t="n"/>
+    </row>
+    <row r="389" ht="32" customHeight="1">
+      <c r="A389" s="4" t="inlineStr">
         <is>
           <t>프로바이오틱스3</t>
         </is>
       </c>
-      <c r="B358" s="4" t="inlineStr">
+      <c r="B389" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C358" s="4" t="inlineStr">
+      <c r="C389" s="4" t="inlineStr">
         <is>
           <t>유산균 복합 성분</t>
         </is>
       </c>
-      <c r="D358" s="4" t="inlineStr">
+      <c r="D389" s="4" t="inlineStr">
         <is>
           <t>피비다발효용해물, / 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
-    <row r="359" ht="30" customHeight="1">
-      <c r="A359" s="4" t="inlineStr">
+    <row r="390" ht="32" customHeight="1">
+      <c r="A390" s="4" t="inlineStr">
         <is>
           <t>다중히아루론산</t>
         </is>
       </c>
-      <c r="B359" s="4" t="inlineStr">
+      <c r="B390" s="4" t="inlineStr">
         <is>
           <t>3~5g</t>
         </is>
       </c>
-      <c r="C359" s="4" t="inlineStr">
+      <c r="C390" s="4" t="inlineStr">
         <is>
           <t>표피~진피 수분 충전 / 고분자+중분자+저분자</t>
         </is>
       </c>
-      <c r="D359" s="4" t="inlineStr">
+      <c r="D390" s="4" t="inlineStr">
         <is>
           <t>판테놀</t>
         </is>
       </c>
     </row>
-    <row r="360" ht="30" customHeight="1">
-      <c r="A360" s="4" t="inlineStr">
+    <row r="391" ht="32" customHeight="1">
+      <c r="A391" s="4" t="inlineStr">
         <is>
           <t>내추럴베타인</t>
         </is>
       </c>
-      <c r="B360" s="4" t="inlineStr">
+      <c r="B391" s="4" t="inlineStr">
         <is>
           <t>10g</t>
         </is>
       </c>
-      <c r="C360" s="4" t="inlineStr">
+      <c r="C391" s="4" t="inlineStr">
         <is>
           <t>사탕무우에서 추출하는 / 아미노산계 보습제</t>
         </is>
       </c>
-      <c r="D360" s="4" t="n"/>
-    </row>
-    <row r="361" ht="45" customHeight="1">
-      <c r="A361" s="4" t="inlineStr">
+      <c r="D391" s="4" t="n"/>
+    </row>
+    <row r="392" ht="48" customHeight="1">
+      <c r="A392" s="4" t="inlineStr">
         <is>
           <t>1,2-헥산디올</t>
         </is>
       </c>
-      <c r="B361" s="4" t="inlineStr">
+      <c r="B392" s="4" t="inlineStr">
         <is>
           <t>2g</t>
         </is>
       </c>
-      <c r="C361" s="4" t="inlineStr">
+      <c r="C392" s="4" t="inlineStr">
         <is>
           <t>항균, 방부, 보습</t>
         </is>
       </c>
-      <c r="D361" s="4" t="inlineStr">
+      <c r="D392" s="4" t="inlineStr">
         <is>
           <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
-    <row r="362" ht="14" customHeight="1">
-      <c r="A362" s="5" t="inlineStr">
+    <row r="393" ht="14" customHeight="1">
+      <c r="A393" s="5" t="inlineStr">
         <is>
           <t>— 상세내용 —</t>
         </is>
       </c>
-      <c r="B362" s="6" t="n"/>
-      <c r="C362" s="6" t="n"/>
-      <c r="D362" s="6" t="n"/>
-    </row>
-    <row r="363" ht="330" customHeight="1">
-      <c r="A363" s="7" t="inlineStr">
+      <c r="B393" s="6" t="n"/>
+      <c r="C393" s="6" t="n"/>
+      <c r="D393" s="6" t="n"/>
+    </row>
+    <row r="394" ht="352" customHeight="1">
+      <c r="A394" s="7" t="inlineStr">
         <is>
           <t>각질을 쑥! 잠재우는
 개똥쑥 진정 토너&amp;패드
@@ -10974,18 +11093,18 @@
         </is>
       </c>
     </row>
-    <row r="364" ht="14" customHeight="1">
-      <c r="A364" s="5" t="inlineStr">
+    <row r="395" ht="14" customHeight="1">
+      <c r="A395" s="5" t="inlineStr">
         <is>
           <t>— 만들기 —</t>
         </is>
       </c>
-      <c r="B364" s="6" t="n"/>
-      <c r="C364" s="6" t="n"/>
-      <c r="D364" s="6" t="n"/>
-    </row>
-    <row r="365" ht="135" customHeight="1">
-      <c r="A365" s="7" t="inlineStr">
+      <c r="B395" s="6" t="n"/>
+      <c r="C395" s="6" t="n"/>
+      <c r="D395" s="6" t="n"/>
+    </row>
+    <row r="396" ht="144" customHeight="1">
+      <c r="A396" s="7" t="inlineStr">
         <is>
           <t>1. 용기에 모든 재료를 계량한 후 섞어주세요.
 2. 다 섞일 때까지 흔들어 주세요.
@@ -10999,220 +11118,253 @@
         </is>
       </c>
     </row>
-    <row r="366" ht="14" customHeight="1">
-      <c r="A366" s="5" t="inlineStr">
+    <row r="397" ht="14" customHeight="1">
+      <c r="A397" s="5" t="inlineStr">
         <is>
           <t>— 이미지 —</t>
         </is>
       </c>
-      <c r="B366" s="6" t="n"/>
-      <c r="C366" s="6" t="n"/>
-      <c r="D366" s="6" t="n"/>
-    </row>
-    <row r="367" ht="171" customHeight="1"/>
-    <row r="368" ht="6" customHeight="1"/>
+      <c r="B397" s="6" t="n"/>
+      <c r="C397" s="6" t="n"/>
+      <c r="D397" s="6" t="n"/>
+    </row>
+    <row r="398" ht="85.5" customHeight="1"/>
+    <row r="399" ht="85.5" customHeight="1"/>
+    <row r="400" ht="6" customHeight="1"/>
   </sheetData>
-  <mergeCells count="173">
-    <mergeCell ref="A303:D303"/>
-    <mergeCell ref="A144:D144"/>
-    <mergeCell ref="A159:D159"/>
-    <mergeCell ref="A97:D97"/>
+  <mergeCells count="205">
+    <mergeCell ref="A150:D150"/>
+    <mergeCell ref="A263:D263"/>
+    <mergeCell ref="A122:D122"/>
+    <mergeCell ref="A215:D215"/>
+    <mergeCell ref="A224:D224"/>
+    <mergeCell ref="A395:D395"/>
     <mergeCell ref="A72:D72"/>
+    <mergeCell ref="A29:D29"/>
     <mergeCell ref="A200:D200"/>
-    <mergeCell ref="A318:D318"/>
     <mergeCell ref="A112:D112"/>
-    <mergeCell ref="A348:D348"/>
+    <mergeCell ref="A152:D152"/>
+    <mergeCell ref="A265:D265"/>
+    <mergeCell ref="A121:D121"/>
     <mergeCell ref="A13:D13"/>
-    <mergeCell ref="A288:D288"/>
+    <mergeCell ref="A357:D357"/>
     <mergeCell ref="A44:D44"/>
-    <mergeCell ref="A249:D249"/>
-    <mergeCell ref="A289:D289"/>
-    <mergeCell ref="A320:D320"/>
-    <mergeCell ref="A176:D176"/>
+    <mergeCell ref="A202:D202"/>
     <mergeCell ref="A258:D258"/>
-    <mergeCell ref="A114:D114"/>
+    <mergeCell ref="A58:D58"/>
+    <mergeCell ref="A314:D314"/>
+    <mergeCell ref="A329:D329"/>
     <mergeCell ref="A347:D347"/>
-    <mergeCell ref="A304:D304"/>
+    <mergeCell ref="A15:D15"/>
     <mergeCell ref="A186:D186"/>
-    <mergeCell ref="A257:D257"/>
     <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A73:D73"/>
     <mergeCell ref="A226:D226"/>
+    <mergeCell ref="A107:D107"/>
+    <mergeCell ref="A266:D266"/>
     <mergeCell ref="A260:D260"/>
-    <mergeCell ref="A291:D291"/>
+    <mergeCell ref="A60:D60"/>
     <mergeCell ref="A349:D349"/>
-    <mergeCell ref="A70:D70"/>
-    <mergeCell ref="A315:D315"/>
+    <mergeCell ref="A358:D358"/>
     <mergeCell ref="A228:D228"/>
-    <mergeCell ref="A54:D54"/>
+    <mergeCell ref="A399:D399"/>
+    <mergeCell ref="A124:D124"/>
+    <mergeCell ref="A360:D360"/>
     <mergeCell ref="A41:D41"/>
-    <mergeCell ref="A16:D16"/>
     <mergeCell ref="A172:D172"/>
     <mergeCell ref="A212:D212"/>
-    <mergeCell ref="A99:D99"/>
     <mergeCell ref="A243:D243"/>
-    <mergeCell ref="A277:D277"/>
-    <mergeCell ref="A335:D335"/>
+    <mergeCell ref="A283:D283"/>
+    <mergeCell ref="A292:D292"/>
+    <mergeCell ref="A397:D397"/>
+    <mergeCell ref="A108:D108"/>
     <mergeCell ref="A286:D286"/>
     <mergeCell ref="A56:D56"/>
     <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A154:D154"/>
+    <mergeCell ref="A267:D267"/>
     <mergeCell ref="A214:D214"/>
-    <mergeCell ref="A285:D285"/>
-    <mergeCell ref="A101:D101"/>
-    <mergeCell ref="A306:D306"/>
-    <mergeCell ref="A85:D85"/>
+    <mergeCell ref="A341:D341"/>
+    <mergeCell ref="A385:D385"/>
+    <mergeCell ref="A294:D294"/>
+    <mergeCell ref="A204:D204"/>
     <mergeCell ref="A42:D42"/>
-    <mergeCell ref="A188:D188"/>
+    <mergeCell ref="A278:D278"/>
+    <mergeCell ref="A361:D361"/>
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A126:D126"/>
     <mergeCell ref="A141:D141"/>
     <mergeCell ref="A259:D259"/>
-    <mergeCell ref="A53:D53"/>
+    <mergeCell ref="A311:D311"/>
+    <mergeCell ref="A135:D135"/>
+    <mergeCell ref="A377:D377"/>
     <mergeCell ref="A262:D262"/>
-    <mergeCell ref="A333:D333"/>
-    <mergeCell ref="A190:D190"/>
     <mergeCell ref="A28:D28"/>
-    <mergeCell ref="A117:D117"/>
     <mergeCell ref="A199:D199"/>
-    <mergeCell ref="A111:D111"/>
+    <mergeCell ref="A230:D230"/>
     <mergeCell ref="A9:D9"/>
     <mergeCell ref="A245:D245"/>
     <mergeCell ref="A362:D362"/>
-    <mergeCell ref="A127:D127"/>
-    <mergeCell ref="A319:D319"/>
+    <mergeCell ref="A167:D167"/>
     <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A232:D232"/>
     <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A142:D142"/>
     <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A182:D182"/>
     <mergeCell ref="A216:D216"/>
     <mergeCell ref="A98:D98"/>
     <mergeCell ref="A169:D169"/>
-    <mergeCell ref="A88:D88"/>
-    <mergeCell ref="A162:D162"/>
+    <mergeCell ref="A225:D225"/>
+    <mergeCell ref="A396:D396"/>
+    <mergeCell ref="A296:D296"/>
+    <mergeCell ref="A79:D79"/>
+    <mergeCell ref="A61:D61"/>
+    <mergeCell ref="A359:D359"/>
+    <mergeCell ref="A153:D153"/>
+    <mergeCell ref="A218:D218"/>
+    <mergeCell ref="A346:D346"/>
     <mergeCell ref="A227:D227"/>
     <mergeCell ref="A316:D316"/>
-    <mergeCell ref="A128:D128"/>
+    <mergeCell ref="A398:D398"/>
+    <mergeCell ref="A137:D137"/>
     <mergeCell ref="A364:D364"/>
     <mergeCell ref="A330:D330"/>
+    <mergeCell ref="A90:D90"/>
+    <mergeCell ref="A268:D268"/>
+    <mergeCell ref="A379:D379"/>
+    <mergeCell ref="A282:D282"/>
     <mergeCell ref="A366:D366"/>
+    <mergeCell ref="A136:D136"/>
     <mergeCell ref="A74:D74"/>
-    <mergeCell ref="A145:D145"/>
+    <mergeCell ref="A105:D105"/>
+    <mergeCell ref="A376:D376"/>
     <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A272:D272"/>
+    <mergeCell ref="A139:D139"/>
     <mergeCell ref="A210:D210"/>
-    <mergeCell ref="A302:D302"/>
+    <mergeCell ref="A381:D381"/>
     <mergeCell ref="A71:D71"/>
-    <mergeCell ref="A129:D129"/>
     <mergeCell ref="A242:D242"/>
-    <mergeCell ref="A322:D322"/>
-    <mergeCell ref="A203:D203"/>
+    <mergeCell ref="A313:D313"/>
+    <mergeCell ref="A76:D76"/>
+    <mergeCell ref="A181:D181"/>
+    <mergeCell ref="A309:D309"/>
     <mergeCell ref="A91:D91"/>
     <mergeCell ref="A184:D184"/>
-    <mergeCell ref="A131:D131"/>
     <mergeCell ref="A244:D244"/>
-    <mergeCell ref="A100:D100"/>
+    <mergeCell ref="A327:D327"/>
     <mergeCell ref="A140:D140"/>
     <mergeCell ref="A171:D171"/>
-    <mergeCell ref="A231:D231"/>
-    <mergeCell ref="A52:D52"/>
+    <mergeCell ref="A109:D109"/>
+    <mergeCell ref="A324:D324"/>
+    <mergeCell ref="A342:D342"/>
+    <mergeCell ref="A63:D63"/>
     <mergeCell ref="A299:D299"/>
     <mergeCell ref="A10:D10"/>
     <mergeCell ref="A155:D155"/>
-    <mergeCell ref="A115:D115"/>
-    <mergeCell ref="A68:D68"/>
-    <mergeCell ref="A102:D102"/>
-    <mergeCell ref="A173:D173"/>
+    <mergeCell ref="A293:D293"/>
+    <mergeCell ref="A93:D93"/>
+    <mergeCell ref="A308:D308"/>
+    <mergeCell ref="A344:D344"/>
     <mergeCell ref="A229:D229"/>
-    <mergeCell ref="A352:D352"/>
+    <mergeCell ref="A295:D295"/>
+    <mergeCell ref="A77:D77"/>
     <mergeCell ref="A143:D143"/>
-    <mergeCell ref="A157:D157"/>
+    <mergeCell ref="A92:D92"/>
+    <mergeCell ref="A270:D270"/>
     <mergeCell ref="A39:D39"/>
-    <mergeCell ref="A270:D270"/>
-    <mergeCell ref="A337:D337"/>
-    <mergeCell ref="A350:D350"/>
-    <mergeCell ref="A300:D300"/>
-    <mergeCell ref="A334:D334"/>
+    <mergeCell ref="A310:D310"/>
+    <mergeCell ref="A328:D328"/>
+    <mergeCell ref="A166:D166"/>
+    <mergeCell ref="A279:D279"/>
+    <mergeCell ref="A383:D383"/>
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A287:D287"/>
-    <mergeCell ref="A69:D69"/>
-    <mergeCell ref="A367:D367"/>
-    <mergeCell ref="A271:D271"/>
-    <mergeCell ref="A87:D87"/>
-    <mergeCell ref="A354:D354"/>
+    <mergeCell ref="A45:D45"/>
+    <mergeCell ref="A94:D94"/>
+    <mergeCell ref="A343:D343"/>
+    <mergeCell ref="A168:D168"/>
+    <mergeCell ref="A281:D281"/>
     <mergeCell ref="A363:D363"/>
-    <mergeCell ref="A133:D133"/>
-    <mergeCell ref="A246:D246"/>
-    <mergeCell ref="A317:D317"/>
+    <mergeCell ref="A345:D345"/>
     <mergeCell ref="A264:D264"/>
-    <mergeCell ref="A37:D37"/>
-    <mergeCell ref="A273:D273"/>
+    <mergeCell ref="A326:D326"/>
+    <mergeCell ref="A378:D378"/>
     <mergeCell ref="A89:D89"/>
+    <mergeCell ref="A120:D120"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A365:D365"/>
-    <mergeCell ref="A331:D331"/>
     <mergeCell ref="A104:D104"/>
+    <mergeCell ref="A297:D297"/>
     <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A113:D113"/>
+    <mergeCell ref="A32:D32"/>
     <mergeCell ref="A247:D247"/>
     <mergeCell ref="A14:D14"/>
     <mergeCell ref="A185:D185"/>
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A38:D38"/>
-    <mergeCell ref="A209:D209"/>
-    <mergeCell ref="A147:D147"/>
-    <mergeCell ref="A274:D274"/>
+    <mergeCell ref="A298:D298"/>
+    <mergeCell ref="A312:D312"/>
+    <mergeCell ref="A106:D106"/>
+    <mergeCell ref="A96:D96"/>
+    <mergeCell ref="A380:D380"/>
+    <mergeCell ref="A280:D280"/>
+    <mergeCell ref="A332:D332"/>
+    <mergeCell ref="A43:D43"/>
     <mergeCell ref="A156:D156"/>
-    <mergeCell ref="A332:D332"/>
     <mergeCell ref="A170:D170"/>
     <mergeCell ref="A40:D40"/>
     <mergeCell ref="A211:D211"/>
-    <mergeCell ref="A67:D67"/>
-    <mergeCell ref="A130:D130"/>
+    <mergeCell ref="A382:D382"/>
     <mergeCell ref="A201:D201"/>
     <mergeCell ref="A261:D261"/>
-    <mergeCell ref="A275:D275"/>
     <mergeCell ref="A284:D284"/>
+    <mergeCell ref="A123:D123"/>
+    <mergeCell ref="A138:D138"/>
     <mergeCell ref="A197:D197"/>
     <mergeCell ref="A110:D110"/>
+    <mergeCell ref="A325:D325"/>
+    <mergeCell ref="A119:D119"/>
     <mergeCell ref="A187:D187"/>
     <mergeCell ref="A25:D25"/>
     <mergeCell ref="A196:D196"/>
     <mergeCell ref="A174:D174"/>
     <mergeCell ref="A183:D183"/>
-    <mergeCell ref="A84:D84"/>
+    <mergeCell ref="A118:D118"/>
+    <mergeCell ref="A75:D75"/>
+    <mergeCell ref="A189:D189"/>
     <mergeCell ref="A158:D158"/>
+    <mergeCell ref="A394:D394"/>
     <mergeCell ref="A198:D198"/>
-    <mergeCell ref="A351:D351"/>
     <mergeCell ref="A55:D55"/>
-    <mergeCell ref="A86:D86"/>
     <mergeCell ref="A301:D301"/>
     <mergeCell ref="A213:D213"/>
-    <mergeCell ref="A160:D160"/>
+    <mergeCell ref="A95:D95"/>
+    <mergeCell ref="A151:D151"/>
+    <mergeCell ref="A393:D393"/>
+    <mergeCell ref="A47:D47"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A16" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A30" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A44" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A59" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A74" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A91" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A104" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A117" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A133" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A147" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A162" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A176" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A190" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A203" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A216" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A231" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A249" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A264" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A277" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A291" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A306" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A322" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A337" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A354" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A17" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A32" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A47" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A63" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A79" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A98" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A112" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A126" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A143" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A158" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A174" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A189" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A204" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A218" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A232" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A247" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A270" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A286" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A301" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A316" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A332" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A349" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A366" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A385" r:id="rId25"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId26"/>

--- a/카드_아키타입/04_팩·마스크·패드.xlsx
+++ b/카드_아키타입/04_팩·마스크·패드.xlsx
@@ -199,13 +199,8 @@
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  <absoluteAnchor>
+    <pos x="6162675" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -223,14 +218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -248,14 +238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -273,14 +258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>0</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -298,14 +278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -323,14 +298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -348,14 +318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>0</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -373,14 +338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="9639300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -398,14 +358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="9639300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -423,14 +378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="9639300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -448,14 +398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="9639300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -473,14 +418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="11487150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -498,14 +438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>13</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="11487150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -523,14 +458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>13</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="11487150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -548,14 +478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="18465800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -573,14 +498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="18465800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -598,14 +518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="18465800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -623,14 +538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>25</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="18465800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -648,14 +558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>25</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="20313650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -673,14 +578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>25</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="20313650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -698,14 +598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>25</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="20313650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -723,14 +618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="27698700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -748,14 +638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="27698700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -773,14 +658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="27698700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -798,14 +678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>37</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="27698700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -823,14 +698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>37</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="29546550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -848,14 +718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>37</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="29546550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -873,14 +738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>37</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="29546550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -898,14 +758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>37</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="29546550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -923,14 +778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>50</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="36931600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -948,14 +798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>50</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="36931600"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -973,14 +818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>50</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="36931600"/>
     <ext cx="1809750" cy="819150"/>
     <pic>
       <nvPicPr>
@@ -998,14 +838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>50</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="36931600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1023,14 +858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>50</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="38779450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1048,14 +878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>50</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="38779450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1073,14 +898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>50</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="38779450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1098,14 +918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>50</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="38779450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1123,14 +938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>50</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="40627300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1148,14 +958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="45148500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1173,14 +978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="45148500"/>
     <ext cx="1743075" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1198,14 +998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="45148500"/>
     <ext cx="1809750" cy="476250"/>
     <pic>
       <nvPicPr>
@@ -1223,14 +1018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>63</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="45148500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1248,14 +1038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="46996350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1273,14 +1058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>63</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="46996350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1298,14 +1078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>63</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="46996350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1323,14 +1098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>63</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="46996350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1348,14 +1118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>63</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="48844200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1373,14 +1138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>63</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="48844200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1398,14 +1158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>63</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="48844200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1423,14 +1178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>63</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="48844200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1448,14 +1198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1473,14 +1218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1498,14 +1238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1523,14 +1258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>78</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1548,14 +1278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>78</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="56635650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1573,14 +1298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>78</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="56635650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1598,14 +1318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>78</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="56635650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1623,14 +1338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="61785500"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1648,14 +1358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="61785500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1673,14 +1378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="61785500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1698,14 +1398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>89</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="61785500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1723,14 +1418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>89</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="63633350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1748,14 +1438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>89</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="63633350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1773,14 +1458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>89</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="63633350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1798,14 +1478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="71424800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1823,14 +1498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="71424800"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1848,14 +1518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="71424800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1873,14 +1538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>100</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="71424800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1898,14 +1558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>100</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="73272650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1923,14 +1578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>100</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="73272650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1948,14 +1598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>100</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="73272650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1973,14 +1618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>100</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="73272650"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -1998,14 +1638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="81064100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2023,14 +1658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="81064100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2048,14 +1678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="81064100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2073,14 +1698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>114</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="81064100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2098,14 +1718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>114</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="82911950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2123,14 +1738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>114</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="82911950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2148,14 +1758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>114</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="82911950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2173,14 +1778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="88671400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2198,14 +1798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="88671400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2223,14 +1818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="88671400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2248,14 +1838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>126</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="88671400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2273,14 +1858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>126</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="90519250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2298,14 +1878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>126</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="90519250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2323,14 +1898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>126</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="90519250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2348,14 +1918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>139</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="98107500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2373,14 +1938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>139</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="98107500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2398,14 +1958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>139</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="98107500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2423,14 +1978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>139</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="98107500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2448,14 +1998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>139</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="99955350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2473,14 +2018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>139</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="99955350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2498,14 +2038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>139</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="99955350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2523,14 +2058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="106527600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2548,14 +2078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="106527600"/>
     <ext cx="1209675" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2573,14 +2098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="106527600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2598,14 +2118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>151</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="106527600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2623,14 +2138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="108375450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2648,14 +2158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="108375450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2673,14 +2178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>151</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="108375450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2698,14 +2198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>163</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="116776500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2723,14 +2218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>163</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="116776500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2748,14 +2238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>163</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="116776500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2773,14 +2258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>163</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="116776500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2798,14 +2278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>163</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="118624350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2823,14 +2298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>163</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="118624350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2848,14 +2318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>163</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="118624350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2873,14 +2338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>174</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="126415800"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2898,14 +2358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>174</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="126415800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2923,14 +2378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>174</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="126415800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2948,14 +2398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>174</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="126415800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2973,14 +2418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>174</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="128263650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2998,14 +2438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>174</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="128263650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3023,14 +2458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>174</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="128263650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3048,14 +2478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>185</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="136055100"/>
     <ext cx="962025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3073,14 +2498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>198</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="144703800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -3098,14 +2518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>198</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="144703800"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3123,14 +2538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>198</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="144703800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3148,14 +2558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>198</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="144703800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3173,14 +2578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>198</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="146551650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3198,14 +2598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>198</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="146551650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3223,14 +2618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>198</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="146551650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3248,14 +2638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>198</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="146551650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3273,14 +2658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>198</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="148399500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3298,14 +2678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>198</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="148399500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3323,14 +2698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>198</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="148399500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3348,14 +2718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>198</row>
-      <rowOff>3695700</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="148399500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3373,14 +2738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>198</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="150247350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3398,14 +2758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>198</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="150247350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3423,14 +2778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>198</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="150247350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3448,14 +2798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>198</row>
-      <rowOff>5543550</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="150247350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -3473,14 +2818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>216</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="163283900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3498,14 +2838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>216</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="163283900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3523,14 +2858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>216</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="163283900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3548,14 +2878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>216</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="163283900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3573,14 +2898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>216</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="165131750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3598,14 +2918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>216</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="165131750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3623,14 +2938,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>216</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="165131750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3648,14 +2958,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>229</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="172516800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3673,14 +2978,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>229</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="172516800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3698,14 +2998,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>229</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="172516800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3723,14 +3018,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>229</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="172516800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3748,14 +3038,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>229</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="174364650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3773,14 +3058,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>229</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="174364650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3798,14 +3078,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>229</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="174364650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3823,14 +3098,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>241</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="182765700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3848,14 +3118,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>241</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="182765700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3873,14 +3138,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>241</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="182765700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3898,14 +3158,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>241</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="182765700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3923,14 +3178,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>241</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="184613550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3948,14 +3198,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>241</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="184613550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3973,14 +3218,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>241</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="184613550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3998,14 +3238,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>253</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="191795400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4023,14 +3258,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>253</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="191795400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4048,14 +3278,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>253</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="191795400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4073,14 +3298,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>253</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="191795400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4098,14 +3318,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>253</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="193643250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4123,14 +3338,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>253</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="193643250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4148,14 +3358,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>253</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="193643250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4173,14 +3378,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>266</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="202450700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4198,14 +3398,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>266</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="202450700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4223,14 +3418,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>266</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="202450700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4248,14 +3438,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>266</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="202450700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4273,14 +3458,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>266</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="204298550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4298,14 +3478,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>266</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="204298550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4323,14 +3498,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>266</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="204298550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4348,14 +3518,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>280</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="212496400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4373,14 +3538,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>280</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="212496400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4398,14 +3558,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>280</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="212496400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4423,14 +3578,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>280</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="212496400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4448,14 +3598,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>280</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="214344250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4473,14 +3618,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>280</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="214344250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4498,14 +3638,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>280</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="214344250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4523,14 +3658,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>294</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="223964500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4548,14 +3678,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>294</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="223964500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4573,14 +3698,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>294</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="223964500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4598,14 +3718,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>294</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="223964500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4623,14 +3738,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>294</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="225812350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4648,14 +3758,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>294</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="225812350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4673,14 +3778,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>294</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="225812350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4698,14 +3798,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>310</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="235229400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4723,14 +3818,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>310</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="235229400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4748,14 +3838,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>310</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="235229400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4773,14 +3858,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>5543550</colOff>
-      <row>310</row>
-      <rowOff>0</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="11706225" y="235229400"/>
     <ext cx="1743075" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4798,14 +3878,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>0</colOff>
-      <row>310</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="6162675" y="237077250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4823,14 +3898,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>1847850</colOff>
-      <row>310</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="8010525" y="237077250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4848,14 +3918,9 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>5</col>
-      <colOff>3695700</colOff>
-      <row>310</row>
-      <rowOff>1847850</rowOff>
-    </from>
+  </absoluteAnchor>
+  <absoluteAnchor>
+    <pos x="9858375" y="237077250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4873,7 +3938,7 @@
       </spPr>
     </pic>
     <clientData/>
-  </oneCellAnchor>
+  </absoluteAnchor>
 </wsDr>
 </file>
 

--- a/카드_아키타입/04_팩·마스크·패드.xlsx
+++ b/카드_아키타입/04_팩·마스크·패드.xlsx
@@ -200,7 +200,7 @@
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <absoluteAnchor>
-    <pos x="6162675" y="0"/>
+    <pos x="7391400" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -220,7 +220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="0"/>
+    <pos x="9239250" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -240,7 +240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="0"/>
+    <pos x="11087100" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -260,7 +260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="0"/>
+    <pos x="12934950" y="0"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -280,7 +280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="1847850"/>
+    <pos x="7391400" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -300,7 +300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="1847850"/>
+    <pos x="9239250" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -320,7 +320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="1847850"/>
+    <pos x="11087100" y="1847850"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -340,7 +340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="9639300"/>
+    <pos x="7391400" y="9639300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -360,7 +360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="9639300"/>
+    <pos x="9239250" y="9639300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -380,7 +380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="9639300"/>
+    <pos x="11087100" y="9639300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -400,7 +400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="9639300"/>
+    <pos x="12934950" y="9639300"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -420,7 +420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="11487150"/>
+    <pos x="7391400" y="11487150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -440,7 +440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="11487150"/>
+    <pos x="9239250" y="11487150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -460,7 +460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="11487150"/>
+    <pos x="11087100" y="11487150"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -480,7 +480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="18465800"/>
+    <pos x="7391400" y="18465800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -500,7 +500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="18465800"/>
+    <pos x="9239250" y="18465800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -520,7 +520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="18465800"/>
+    <pos x="11087100" y="18465800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -540,7 +540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="18465800"/>
+    <pos x="12934950" y="18465800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -560,7 +560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="20313650"/>
+    <pos x="7391400" y="20313650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -580,7 +580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="20313650"/>
+    <pos x="9239250" y="20313650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -600,7 +600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="20313650"/>
+    <pos x="11087100" y="20313650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -620,7 +620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="27698700"/>
+    <pos x="7391400" y="27698700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -640,7 +640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="27698700"/>
+    <pos x="9239250" y="27698700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -660,7 +660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="27698700"/>
+    <pos x="11087100" y="27698700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -680,7 +680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="27698700"/>
+    <pos x="12934950" y="27698700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -700,7 +700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="29546550"/>
+    <pos x="7391400" y="29546550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -720,7 +720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="29546550"/>
+    <pos x="9239250" y="29546550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -740,7 +740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="29546550"/>
+    <pos x="11087100" y="29546550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -760,7 +760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="29546550"/>
+    <pos x="12934950" y="29546550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -780,7 +780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="36931600"/>
+    <pos x="7391400" y="36931600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -800,7 +800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="36931600"/>
+    <pos x="9239250" y="36931600"/>
     <ext cx="1809750" cy="1533525"/>
     <pic>
       <nvPicPr>
@@ -820,7 +820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="36931600"/>
+    <pos x="11087100" y="36931600"/>
     <ext cx="1809750" cy="819150"/>
     <pic>
       <nvPicPr>
@@ -840,7 +840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="36931600"/>
+    <pos x="12934950" y="36931600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -860,7 +860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="38779450"/>
+    <pos x="7391400" y="38779450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -880,7 +880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="38779450"/>
+    <pos x="9239250" y="38779450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -900,7 +900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="38779450"/>
+    <pos x="11087100" y="38779450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -920,7 +920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="38779450"/>
+    <pos x="12934950" y="38779450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -940,7 +940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="40627300"/>
+    <pos x="7391400" y="40627300"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -960,7 +960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="45148500"/>
+    <pos x="7391400" y="45148500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -980,7 +980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="45148500"/>
+    <pos x="9239250" y="45148500"/>
     <ext cx="1743075" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1000,7 +1000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="45148500"/>
+    <pos x="11087100" y="45148500"/>
     <ext cx="1809750" cy="476250"/>
     <pic>
       <nvPicPr>
@@ -1020,7 +1020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="45148500"/>
+    <pos x="12934950" y="45148500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1040,7 +1040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="46996350"/>
+    <pos x="7391400" y="46996350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1060,7 +1060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="46996350"/>
+    <pos x="9239250" y="46996350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1080,7 +1080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="46996350"/>
+    <pos x="11087100" y="46996350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1100,7 +1100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="46996350"/>
+    <pos x="12934950" y="46996350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1120,7 +1120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="48844200"/>
+    <pos x="7391400" y="48844200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1140,7 +1140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="48844200"/>
+    <pos x="9239250" y="48844200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1160,7 +1160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="48844200"/>
+    <pos x="11087100" y="48844200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1180,7 +1180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="48844200"/>
+    <pos x="12934950" y="48844200"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1200,7 +1200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="54787800"/>
+    <pos x="7391400" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1220,7 +1220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="54787800"/>
+    <pos x="9239250" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1240,7 +1240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="54787800"/>
+    <pos x="11087100" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1260,7 +1260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="54787800"/>
+    <pos x="12934950" y="54787800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1280,7 +1280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="56635650"/>
+    <pos x="7391400" y="56635650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1300,7 +1300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="56635650"/>
+    <pos x="9239250" y="56635650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1320,7 +1320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="56635650"/>
+    <pos x="11087100" y="56635650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1340,7 +1340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="61785500"/>
+    <pos x="7391400" y="61785500"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1360,7 +1360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="61785500"/>
+    <pos x="9239250" y="61785500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1380,7 +1380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="61785500"/>
+    <pos x="11087100" y="61785500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1400,7 +1400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="61785500"/>
+    <pos x="12934950" y="61785500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1420,7 +1420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="63633350"/>
+    <pos x="7391400" y="63633350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1440,7 +1440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="63633350"/>
+    <pos x="9239250" y="63633350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1460,7 +1460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="63633350"/>
+    <pos x="11087100" y="63633350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1480,7 +1480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="71424800"/>
+    <pos x="7391400" y="71424800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1500,7 +1500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="71424800"/>
+    <pos x="9239250" y="71424800"/>
     <ext cx="1809750" cy="1352550"/>
     <pic>
       <nvPicPr>
@@ -1520,7 +1520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="71424800"/>
+    <pos x="11087100" y="71424800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1540,7 +1540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="71424800"/>
+    <pos x="12934950" y="71424800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1560,7 +1560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="73272650"/>
+    <pos x="7391400" y="73272650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1580,7 +1580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="73272650"/>
+    <pos x="9239250" y="73272650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1600,7 +1600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="73272650"/>
+    <pos x="11087100" y="73272650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1620,7 +1620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="73272650"/>
+    <pos x="12934950" y="73272650"/>
     <ext cx="1809750" cy="1628775"/>
     <pic>
       <nvPicPr>
@@ -1640,7 +1640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="81064100"/>
+    <pos x="7391400" y="81064100"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1660,7 +1660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="81064100"/>
+    <pos x="9239250" y="81064100"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1680,7 +1680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="81064100"/>
+    <pos x="11087100" y="81064100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1700,7 +1700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="81064100"/>
+    <pos x="12934950" y="81064100"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1720,7 +1720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="82911950"/>
+    <pos x="7391400" y="82911950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1740,7 +1740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="82911950"/>
+    <pos x="9239250" y="82911950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1760,7 +1760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="82911950"/>
+    <pos x="11087100" y="82911950"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1780,7 +1780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="88671400"/>
+    <pos x="7391400" y="88671400"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1800,7 +1800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="88671400"/>
+    <pos x="9239250" y="88671400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1820,7 +1820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="88671400"/>
+    <pos x="11087100" y="88671400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1840,7 +1840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="88671400"/>
+    <pos x="12934950" y="88671400"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1860,7 +1860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="90519250"/>
+    <pos x="7391400" y="90519250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1880,7 +1880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="90519250"/>
+    <pos x="9239250" y="90519250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1900,7 +1900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="90519250"/>
+    <pos x="11087100" y="90519250"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1920,7 +1920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="98107500"/>
+    <pos x="7391400" y="98107500"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -1940,7 +1940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="98107500"/>
+    <pos x="9239250" y="98107500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -1960,7 +1960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="98107500"/>
+    <pos x="11087100" y="98107500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -1980,7 +1980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="98107500"/>
+    <pos x="12934950" y="98107500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2000,7 +2000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="99955350"/>
+    <pos x="7391400" y="99955350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2020,7 +2020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="99955350"/>
+    <pos x="9239250" y="99955350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2040,7 +2040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="99955350"/>
+    <pos x="11087100" y="99955350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2060,7 +2060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="106527600"/>
+    <pos x="7391400" y="106527600"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2080,7 +2080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="106527600"/>
+    <pos x="9239250" y="106527600"/>
     <ext cx="1209675" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2100,7 +2100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="106527600"/>
+    <pos x="11087100" y="106527600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2120,7 +2120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="106527600"/>
+    <pos x="12934950" y="106527600"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2140,7 +2140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="108375450"/>
+    <pos x="7391400" y="108375450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2160,7 +2160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="108375450"/>
+    <pos x="9239250" y="108375450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2180,7 +2180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="108375450"/>
+    <pos x="11087100" y="108375450"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2200,7 +2200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="116776500"/>
+    <pos x="7391400" y="116776500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2220,7 +2220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="116776500"/>
+    <pos x="9239250" y="116776500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2240,7 +2240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="116776500"/>
+    <pos x="11087100" y="116776500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2260,7 +2260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="116776500"/>
+    <pos x="12934950" y="116776500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2280,7 +2280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="118624350"/>
+    <pos x="7391400" y="118624350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2300,7 +2300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="118624350"/>
+    <pos x="9239250" y="118624350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2320,7 +2320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="118624350"/>
+    <pos x="11087100" y="118624350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2340,7 +2340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="126415800"/>
+    <pos x="7391400" y="126415800"/>
     <ext cx="1504950" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2360,7 +2360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="126415800"/>
+    <pos x="9239250" y="126415800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2380,7 +2380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="126415800"/>
+    <pos x="11087100" y="126415800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2400,7 +2400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="126415800"/>
+    <pos x="12934950" y="126415800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2420,7 +2420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="128263650"/>
+    <pos x="7391400" y="128263650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2440,7 +2440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="128263650"/>
+    <pos x="9239250" y="128263650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2460,7 +2460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="128263650"/>
+    <pos x="11087100" y="128263650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2480,7 +2480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="136055100"/>
+    <pos x="7391400" y="136055100"/>
     <ext cx="962025" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2500,7 +2500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="144703800"/>
+    <pos x="7391400" y="144703800"/>
     <ext cx="9525" cy="9525"/>
     <pic>
       <nvPicPr>
@@ -2520,7 +2520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="144703800"/>
+    <pos x="9239250" y="144703800"/>
     <ext cx="1352550" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2540,7 +2540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="144703800"/>
+    <pos x="11087100" y="144703800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2560,7 +2560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="144703800"/>
+    <pos x="12934950" y="144703800"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2580,7 +2580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="146551650"/>
+    <pos x="7391400" y="146551650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2600,7 +2600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="146551650"/>
+    <pos x="9239250" y="146551650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2620,7 +2620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="146551650"/>
+    <pos x="11087100" y="146551650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2640,7 +2640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="146551650"/>
+    <pos x="12934950" y="146551650"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2660,7 +2660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="148399500"/>
+    <pos x="7391400" y="148399500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2680,7 +2680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="148399500"/>
+    <pos x="9239250" y="148399500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2700,7 +2700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="148399500"/>
+    <pos x="11087100" y="148399500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2720,7 +2720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="148399500"/>
+    <pos x="12934950" y="148399500"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2740,7 +2740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="150247350"/>
+    <pos x="7391400" y="150247350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2760,7 +2760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="150247350"/>
+    <pos x="9239250" y="150247350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2780,7 +2780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="150247350"/>
+    <pos x="11087100" y="150247350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2800,7 +2800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="150247350"/>
+    <pos x="12934950" y="150247350"/>
     <ext cx="1809750" cy="1714500"/>
     <pic>
       <nvPicPr>
@@ -2820,7 +2820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="163283900"/>
+    <pos x="7391400" y="163283900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2840,7 +2840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="163283900"/>
+    <pos x="9239250" y="163283900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2860,7 +2860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="163283900"/>
+    <pos x="11087100" y="163283900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2880,7 +2880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="163283900"/>
+    <pos x="12934950" y="163283900"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2900,7 +2900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="165131750"/>
+    <pos x="7391400" y="165131750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2920,7 +2920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="165131750"/>
+    <pos x="9239250" y="165131750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2940,7 +2940,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="165131750"/>
+    <pos x="11087100" y="165131750"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2960,7 +2960,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="172516800"/>
+    <pos x="7391400" y="172516800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -2980,7 +2980,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="172516800"/>
+    <pos x="9239250" y="172516800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3000,7 +3000,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="172516800"/>
+    <pos x="11087100" y="172516800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3020,7 +3020,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="172516800"/>
+    <pos x="12934950" y="172516800"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3040,7 +3040,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="174364650"/>
+    <pos x="7391400" y="174364650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3060,7 +3060,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="174364650"/>
+    <pos x="9239250" y="174364650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3080,7 +3080,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="174364650"/>
+    <pos x="11087100" y="174364650"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3100,7 +3100,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="182765700"/>
+    <pos x="7391400" y="182765700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3120,7 +3120,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="182765700"/>
+    <pos x="9239250" y="182765700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3140,7 +3140,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="182765700"/>
+    <pos x="11087100" y="182765700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3160,7 +3160,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="182765700"/>
+    <pos x="12934950" y="182765700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3180,7 +3180,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="184613550"/>
+    <pos x="7391400" y="184613550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3200,7 +3200,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="184613550"/>
+    <pos x="9239250" y="184613550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3220,7 +3220,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="184613550"/>
+    <pos x="11087100" y="184613550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3240,7 +3240,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="191795400"/>
+    <pos x="7391400" y="191795400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3260,7 +3260,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="191795400"/>
+    <pos x="9239250" y="191795400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3280,7 +3280,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="191795400"/>
+    <pos x="11087100" y="191795400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3300,7 +3300,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="191795400"/>
+    <pos x="12934950" y="191795400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3320,7 +3320,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="193643250"/>
+    <pos x="7391400" y="193643250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3340,7 +3340,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="193643250"/>
+    <pos x="9239250" y="193643250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3360,7 +3360,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="193643250"/>
+    <pos x="11087100" y="193643250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3380,7 +3380,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="202450700"/>
+    <pos x="7391400" y="202450700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3400,7 +3400,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="202450700"/>
+    <pos x="9239250" y="202450700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3420,7 +3420,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="202450700"/>
+    <pos x="11087100" y="202450700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3440,7 +3440,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="202450700"/>
+    <pos x="12934950" y="202450700"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3460,7 +3460,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="204298550"/>
+    <pos x="7391400" y="204298550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3480,7 +3480,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="204298550"/>
+    <pos x="9239250" y="204298550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3500,7 +3500,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="204298550"/>
+    <pos x="11087100" y="204298550"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3520,7 +3520,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="212496400"/>
+    <pos x="7391400" y="212496400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3540,7 +3540,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="212496400"/>
+    <pos x="9239250" y="212496400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3560,7 +3560,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="212496400"/>
+    <pos x="11087100" y="212496400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3580,7 +3580,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="212496400"/>
+    <pos x="12934950" y="212496400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3600,7 +3600,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="214344250"/>
+    <pos x="7391400" y="214344250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3620,7 +3620,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="214344250"/>
+    <pos x="9239250" y="214344250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3640,7 +3640,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="214344250"/>
+    <pos x="11087100" y="214344250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3660,7 +3660,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="223964500"/>
+    <pos x="7391400" y="223964500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3680,7 +3680,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="223964500"/>
+    <pos x="9239250" y="223964500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3700,7 +3700,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="223964500"/>
+    <pos x="11087100" y="223964500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3720,7 +3720,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="223964500"/>
+    <pos x="12934950" y="223964500"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3740,7 +3740,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="225812350"/>
+    <pos x="7391400" y="225812350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3760,7 +3760,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="225812350"/>
+    <pos x="9239250" y="225812350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3780,7 +3780,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="225812350"/>
+    <pos x="11087100" y="225812350"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3800,7 +3800,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="235229400"/>
+    <pos x="7391400" y="235229400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3820,7 +3820,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="235229400"/>
+    <pos x="9239250" y="235229400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3840,7 +3840,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="235229400"/>
+    <pos x="11087100" y="235229400"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3860,7 +3860,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="11706225" y="235229400"/>
+    <pos x="12934950" y="235229400"/>
     <ext cx="1743075" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3880,7 +3880,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="6162675" y="237077250"/>
+    <pos x="7391400" y="237077250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3900,7 +3900,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="8010525" y="237077250"/>
+    <pos x="9239250" y="237077250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -3920,7 +3920,7 @@
     <clientData/>
   </absoluteAnchor>
   <absoluteAnchor>
-    <pos x="9858375" y="237077250"/>
+    <pos x="11087100" y="237077250"/>
     <ext cx="1809750" cy="1809750"/>
     <pic>
       <nvPicPr>
@@ -4238,7 +4238,7 @@
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
-    <col width="2" customWidth="1" min="5" max="5"/>
+    <col width="3" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="22" customHeight="1">

--- a/카드_아키타입/04_팩·마스크·패드.xlsx
+++ b/카드_아키타입/04_팩·마스크·패드.xlsx
@@ -4502,10 +4502,10 @@
       </c>
       <c r="E8" s="10" t="inlineStr">
         <is>
-          <t>미백 효과 / 강력한 항산화 효과</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="n"/>
+          <t>미백 효과 · 강력한 항산화 효과</t>
+        </is>
+      </c>
+      <c r="F8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="32" customHeight="1">
       <c r="A9" s="10" t="inlineStr">
@@ -4530,10 +4530,10 @@
       </c>
       <c r="E9" s="10" t="inlineStr">
         <is>
-          <t>식약처인증 미백 고시 원료 / 멜라닌 색소 억제</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="n"/>
+          <t>식약처인증 미백 고시 원료 · 멜라닌 색소 억제</t>
+        </is>
+      </c>
+      <c r="F9" s="10" t="inlineStr"/>
     </row>
     <row r="10" ht="32" customHeight="1">
       <c r="A10" s="10" t="inlineStr">
@@ -4558,7 +4558,7 @@
       </c>
       <c r="E10" s="10" t="inlineStr">
         <is>
-          <t>미백 고시 원료, 비타민 B3, / 생긴 멜라닌 색소 발현 차단</t>
+          <t>미백 고시 원료, 비타민 B3 · 생긴 멜라닌 색소 발현 차단</t>
         </is>
       </c>
       <c r="F10" s="10" t="inlineStr">
@@ -4590,7 +4590,7 @@
       </c>
       <c r="E11" s="10" t="inlineStr">
         <is>
-          <t>오렌지꽃수 / 진정, 피부건강</t>
+          <t>오렌지꽃수 · 진정, 피부건강</t>
         </is>
       </c>
       <c r="F11" s="10" t="inlineStr">
@@ -4622,12 +4622,12 @@
       </c>
       <c r="E12" s="10" t="inlineStr">
         <is>
-          <t>수분 충전 / 고분자+중분자+저분자</t>
+          <t>수분 충전 · 고분자+중분자+저분자</t>
         </is>
       </c>
       <c r="F12" s="10" t="inlineStr">
         <is>
-          <t>에코 / 보습제</t>
+          <t>에코 · 보습제</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4659,7 @@
       </c>
       <c r="F13" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4810,7 @@
       </c>
       <c r="E22" s="20" t="inlineStr">
         <is>
-          <t>단백질 케어로 / 피부에 깊은 영양</t>
+          <t>단백질 케어로 · 피부에 깊은 영양</t>
         </is>
       </c>
       <c r="F22" s="20" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="E23" s="20" t="inlineStr">
         <is>
-          <t>발효여과물, / 보습, 탄력, 아미노산, / 미네럴 영양공급</t>
+          <t>발효여과물 · 보습, 탄력, 아미노산 · 미네럴 영양공급</t>
         </is>
       </c>
       <c r="F23" s="20" t="inlineStr">
@@ -4877,7 +4877,7 @@
           <t>비타민B7, 피부 진정</t>
         </is>
       </c>
-      <c r="F24" s="20" t="n"/>
+      <c r="F24" s="20" t="inlineStr"/>
     </row>
     <row r="25" ht="32" customHeight="1">
       <c r="A25" s="20" t="inlineStr">
@@ -4902,7 +4902,7 @@
       </c>
       <c r="E25" s="20" t="inlineStr">
         <is>
-          <t>비타민B5, 보습 / 식약처 기능성 고시원료</t>
+          <t>비타민B5, 보습 · 식약처 기능성 고시원료</t>
         </is>
       </c>
       <c r="F25" s="20" t="inlineStr">
@@ -4939,7 +4939,7 @@
       </c>
       <c r="F26" s="20" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E35" s="10" t="inlineStr">
         <is>
-          <t>모공 탄력, / 폴리페놀 풍부</t>
+          <t>모공 탄력 · 폴리페놀 풍부</t>
         </is>
       </c>
       <c r="F35" s="10" t="inlineStr">
         <is>
-          <t>녹소초 추출물, / 유기농 브라이트닝 5 등.</t>
+          <t>녹소초 추출물 · 유기농 브라이트닝 5 등.</t>
         </is>
       </c>
     </row>
@@ -5134,7 +5134,7 @@
       </c>
       <c r="F36" s="10" t="inlineStr">
         <is>
-          <t>프리미엄 / 녹차워터</t>
+          <t>프리미엄 · 녹차워터</t>
         </is>
       </c>
     </row>
@@ -5161,10 +5161,10 @@
       </c>
       <c r="E37" s="10" t="inlineStr">
         <is>
-          <t>AHA+ BHA+PHA 성분 / 각질제거, 노폐물정리</t>
-        </is>
-      </c>
-      <c r="F37" s="10" t="n"/>
+          <t>AHA+ BHA+PHA 성분 · 각질제거, 노폐물정리</t>
+        </is>
+      </c>
+      <c r="F37" s="10" t="inlineStr"/>
     </row>
     <row r="38" ht="32" customHeight="1">
       <c r="A38" s="10" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="E38" s="10" t="inlineStr">
         <is>
-          <t>표피~진피 수분 충전 / 고분자+중분자+저분자</t>
+          <t>표피~진피 수분 충전 · 고분자+중분자+저분자</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
@@ -5226,7 +5226,7 @@
       </c>
       <c r="F39" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -5411,7 +5411,7 @@
           <t>실제 피부 각질층 아미노산 구성과 유사한 17가지 아미노산, 보습·톤오버 유도·재생·톤업</t>
         </is>
       </c>
-      <c r="F49" s="20" t="n"/>
+      <c r="F49" s="20" t="inlineStr"/>
     </row>
     <row r="50" ht="32" customHeight="1">
       <c r="A50" s="20" t="inlineStr">
@@ -5537,7 +5537,7 @@
       </c>
       <c r="F53" s="20" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5757,7 @@
       </c>
       <c r="E64" s="10" t="inlineStr">
         <is>
-          <t>녹황색채소유래, 비타민B3, / 미백기능성 원료이기도 / 하지만 피부장벽을 강화효과</t>
+          <t>녹황색채소유래, 비타민B3 · 미백기능성 원료이기도 · 하지만 피부장벽을 강화효과</t>
         </is>
       </c>
       <c r="F64" s="10" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="F67" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -5995,12 +5995,12 @@
       </c>
       <c r="E76" s="20" t="inlineStr">
         <is>
-          <t>리놀렌산풍부, / 주름노화관리 도움</t>
+          <t>리놀렌산풍부 · 주름노화관리 도움</t>
         </is>
       </c>
       <c r="F76" s="20" t="inlineStr">
         <is>
-          <t>골든호호바 또는 / 원하는 베이스오일</t>
+          <t>골든호호바 또는 · 원하는 베이스오일</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="F77" s="20" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -6059,7 +6059,7 @@
       </c>
       <c r="E78" s="20" t="inlineStr">
         <is>
-          <t>순수한 물, / 완성품의 색을 고르게.</t>
+          <t>순수한 물 · 완성품의 색을 고르게.</t>
         </is>
       </c>
       <c r="F78" s="20" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="F79" s="20" t="inlineStr">
         <is>
-          <t>인삼줄기세포, / 장미줄기세포 등</t>
+          <t>인삼줄기세포 · 장미줄기세포 등</t>
         </is>
       </c>
     </row>
@@ -6128,7 +6128,7 @@
       </c>
       <c r="F80" s="20" t="inlineStr">
         <is>
-          <t>낫또모이스트, / 판테놀, 리피듀어, / 히아루론산 등</t>
+          <t>낫또모이스트 · 판테놀, 리피듀어 · 히아루론산 등</t>
         </is>
       </c>
     </row>
@@ -6155,7 +6155,7 @@
       </c>
       <c r="E81" s="20" t="inlineStr">
         <is>
-          <t>오일, 에코인증, / 미백 트러블진정 성분 / Candeia Tree에서 추출</t>
+          <t>오일, 에코인증 · 미백 트러블진정 성분 · Candeia Tree에서 추출</t>
         </is>
       </c>
       <c r="F81" s="20" t="inlineStr">
@@ -6187,12 +6187,12 @@
       </c>
       <c r="E82" s="20" t="inlineStr">
         <is>
-          <t>식물복합추출물 / 균번식 억제제</t>
+          <t>식물복합추출물 · 균번식 억제제</t>
         </is>
       </c>
       <c r="F82" s="20" t="inlineStr">
         <is>
-          <t>천연한방보존제, / 나트로틱스 / (워터류1g 줄이고 2g)</t>
+          <t>천연한방보존제 · 나트로틱스 · (워터류1g 줄이고 2g)</t>
         </is>
       </c>
     </row>
@@ -6379,7 +6379,7 @@
           <t>티스푼 1</t>
         </is>
       </c>
-      <c r="F92" s="10" t="n"/>
+      <c r="F92" s="10" t="inlineStr"/>
     </row>
     <row r="93" ht="16" customHeight="1">
       <c r="A93" s="10" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E94" s="10" t="inlineStr">
         <is>
-          <t>분말들의 2배, / 마요네즈 농도로 맞춰주세요.</t>
+          <t>분말들의 2배 · 마요네즈 농도로 맞춰주세요.</t>
         </is>
       </c>
       <c r="F94" s="10" t="inlineStr">
@@ -6468,12 +6468,12 @@
       </c>
       <c r="E95" s="10" t="inlineStr">
         <is>
-          <t>아래표를 참고하세요. / 좋아하거나 가지고 있는 / 오일 한가지 넣어도 됩니다.</t>
+          <t>아래표를 참고하세요. · 좋아하거나 가지고 있는 · 오일 한가지 넣어도 됩니다.</t>
         </is>
       </c>
       <c r="F95" s="10" t="inlineStr">
         <is>
-          <t>아로마테라피효과 / 원하는 에센셜오일</t>
+          <t>아로마테라피효과 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -6680,12 +6680,12 @@
       </c>
       <c r="E106" s="20" t="inlineStr">
         <is>
-          <t>분말들의 2배, / 마요네즈 농도로 맞춰주세요.</t>
+          <t>분말들의 2배 · 마요네즈 농도로 맞춰주세요.</t>
         </is>
       </c>
       <c r="F106" s="20" t="inlineStr">
         <is>
-          <t>정제수, / 로즈워터 등</t>
+          <t>정제수 · 로즈워터 등</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="F107" s="20" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="F117" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -6979,7 +6979,7 @@
           <t>피부보호막, 촉촉함이 오래오래</t>
         </is>
       </c>
-      <c r="F119" s="10" t="n"/>
+      <c r="F119" s="10" t="inlineStr"/>
     </row>
     <row r="120" ht="32" customHeight="1">
       <c r="A120" s="10" t="inlineStr">
@@ -7004,12 +7004,12 @@
       </c>
       <c r="E120" s="10" t="inlineStr">
         <is>
-          <t>헥사펩타이드, / 보톡스와 같이 노화,탄력관리 펩타이드</t>
+          <t>헥사펩타이드 · 보톡스와 같이 노화,탄력관리 펩타이드</t>
         </is>
       </c>
       <c r="F120" s="10" t="inlineStr">
         <is>
-          <t>아데노신, / EGF등</t>
+          <t>아데노신 · EGF등</t>
         </is>
       </c>
     </row>
@@ -7041,7 +7041,7 @@
       </c>
       <c r="F121" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (알로에베라겔의 양을 74g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (알로에베라겔의 양을 74g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -7219,7 +7219,7 @@
       </c>
       <c r="F131" s="20" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -7347,7 +7347,7 @@
       </c>
       <c r="F135" s="20" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (편백워터의 양을 9g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (편백워터의 양을 9g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -7503,7 +7503,7 @@
       </c>
       <c r="F144" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔. / 네롤리플라워겔</t>
+          <t>로즈플라워겔. · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -7631,7 +7631,7 @@
       </c>
       <c r="F148" s="10" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -7663,7 +7663,7 @@
       </c>
       <c r="F149" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (네롤리워터의 양을 15g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (네롤리워터의 양을 15g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="F158" s="20" t="inlineStr">
         <is>
-          <t>에코보습제, / 낫또모이스트 등 / 촉촉함을 원한다면 히아루론산을 더 / 추가해주세요.</t>
+          <t>에코보습제 · 낫또모이스트 등 · 촉촉함을 원한다면 히아루론산을 더 · 추가해주세요.</t>
         </is>
       </c>
     </row>
@@ -7942,7 +7942,7 @@
       </c>
       <c r="F162" s="20" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의 양을 50g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의 양을 50g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -8098,7 +8098,7 @@
       </c>
       <c r="F171" s="10" t="inlineStr">
         <is>
-          <t>로즈플라워겔, / 네롤리플라워겔</t>
+          <t>로즈플라워겔 · 네롤리플라워겔</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="F175" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올2g / (로즈워터의 양을 13g으로 줄여주세요.)</t>
+          <t>1,2-헥산디올2g · (로즈워터의 양을 13g으로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -8371,12 +8371,12 @@
       </c>
       <c r="E184" s="20" t="inlineStr">
         <is>
-          <t>90%, 누룩(천연효모)발효여과물, / 보습, 탄력, 아미노산, 미네럴 영양 공급</t>
+          <t>90%, 누룩(천연효모)발효여과물 · 보습, 탄력, 아미노산, 미네럴 영양 공급</t>
         </is>
       </c>
       <c r="F184" s="20" t="inlineStr">
         <is>
-          <t>사카로미세스 / 발효여과물, / 원하는 워터</t>
+          <t>사카로미세스 · 발효여과물 · 원하는 워터</t>
         </is>
       </c>
     </row>
@@ -8403,7 +8403,7 @@
       </c>
       <c r="E185" s="20" t="inlineStr">
         <is>
-          <t>5%, 비타민B3, 식약처 인증 미백원료, / 피부장벽강화, 트러블 완화</t>
+          <t>5%, 비타민B3, 식약처 인증 미백원료 · 피부장벽강화, 트러블 완화</t>
         </is>
       </c>
       <c r="F185" s="20" t="inlineStr">
@@ -8435,7 +8435,7 @@
       </c>
       <c r="E186" s="20" t="inlineStr">
         <is>
-          <t>5가지 콩과 갈근 / 특허 균주를 통한 발효로 / 미백, 주름 효능 극대화</t>
+          <t>5가지 콩과 갈근 · 특허 균주를 통한 발효로 · 미백, 주름 효능 극대화</t>
         </is>
       </c>
       <c r="F186" s="20" t="inlineStr">
@@ -8472,7 +8472,7 @@
       </c>
       <c r="F187" s="20" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -8694,12 +8694,12 @@
       </c>
       <c r="E198" s="10" t="inlineStr">
         <is>
-          <t>분말들의 2배, / 마요네즈 농도로 맞춰주세요.</t>
+          <t>분말들의 2배 · 마요네즈 농도로 맞춰주세요.</t>
         </is>
       </c>
       <c r="F198" s="10" t="inlineStr">
         <is>
-          <t>정제수, / 로즈워터 등</t>
+          <t>정제수 · 로즈워터 등</t>
         </is>
       </c>
     </row>
@@ -8731,7 +8731,7 @@
       </c>
       <c r="F199" s="10" t="inlineStr">
         <is>
-          <t>네롤리,카모마일저먼 / (:일때 양을줄임-2방울), / 로먼카모마일 등</t>
+          <t>네롤리,카모마일저먼 · (:일때 양을줄임-2방울) · 로먼카모마일 등</t>
         </is>
       </c>
     </row>
@@ -8880,7 +8880,7 @@
       </c>
       <c r="E208" s="20" t="inlineStr">
         <is>
-          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. / 남은 재료 활용 팁 : 젤타입스킨으로 사용가능, / 헤어에센스로 사용가능.</t>
+          <t>거제산 생알로에잎을 껍질제거한 후 갈아만듬. · 남은 재료 활용 팁 : 젤타입스킨으로 사용가능 · 헤어에센스로 사용가능.</t>
         </is>
       </c>
       <c r="F208" s="20" t="inlineStr">
@@ -8936,7 +8936,7 @@
       </c>
       <c r="E210" s="20" t="inlineStr">
         <is>
-          <t>귤껍질오일, / 임신기간 영아에게 안전하게 사용, / 모든 피부사용</t>
+          <t>귤껍질오일 · 임신기간 영아에게 안전하게 사용 · 모든 피부사용</t>
         </is>
       </c>
       <c r="F210" s="20" t="inlineStr">
@@ -9048,12 +9048,12 @@
       </c>
       <c r="E214" s="20" t="inlineStr">
         <is>
-          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 / 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
+          <t>천연한방보존제는 생약 중 항균력이 우수한 오배자, 가자, 석곡, 산초를 초음파 방식으로 · 추출하여 조합한 화장품용 천연유래 항균제입니다</t>
         </is>
       </c>
       <c r="F214" s="20" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -9081,7 +9081,7 @@
       </c>
       <c r="F215" s="20" t="inlineStr">
         <is>
-          <t>카렌듈라,달맞이오일, / 보리지오일,동백오일, / 호호바오일 등</t>
+          <t>카렌듈라,달맞이오일 · 보리지오일,동백오일 · 호호바오일 등</t>
         </is>
       </c>
     </row>
@@ -9185,12 +9185,12 @@
       </c>
       <c r="E221" s="10" t="inlineStr">
         <is>
-          <t>가벼운 오일, 콩과식물, / 피지와 성분과 흡사</t>
+          <t>가벼운 오일, 콩과식물 · 피지와 성분과 흡사</t>
         </is>
       </c>
       <c r="F221" s="10" t="inlineStr">
         <is>
-          <t>마카다미아넛오일, / 아몬드, 살구씨 오일 등</t>
+          <t>마카다미아넛오일 · 아몬드, 살구씨 오일 등</t>
         </is>
       </c>
     </row>
@@ -9217,12 +9217,12 @@
       </c>
       <c r="E222" s="10" t="inlineStr">
         <is>
-          <t>에코인증. 오일과 물이 분리되지 / 않도록 도와줌.</t>
+          <t>에코인증. 오일과 물이 분리되지 · 않도록 도와줌.</t>
         </is>
       </c>
       <c r="F222" s="10" t="inlineStr">
         <is>
-          <t>올리브유화왁스4g / (빠른 유화, 점도를 원할시)</t>
+          <t>올리브유화왁스4g · (빠른 유화, 점도를 원할시)</t>
         </is>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
       </c>
       <c r="F223" s="10" t="inlineStr">
         <is>
-          <t>원하는 플로럴워터 / 네롤리워터</t>
+          <t>원하는 플로럴워터 · 네롤리워터</t>
         </is>
       </c>
     </row>
@@ -9281,7 +9281,7 @@
       </c>
       <c r="E224" s="10" t="inlineStr">
         <is>
-          <t>수분공급, 자체점도 화산송이를 / 골고루 분산시키는 역할.</t>
+          <t>수분공급, 자체점도 화산송이를 · 골고루 분산시키는 역할.</t>
         </is>
       </c>
       <c r="F224" s="10" t="inlineStr">
@@ -9316,7 +9316,7 @@
           <t>모공 세정해독효소 활성화, 항산화</t>
         </is>
       </c>
-      <c r="F225" s="10" t="n"/>
+      <c r="F225" s="10" t="inlineStr"/>
     </row>
     <row r="226" ht="80" customHeight="1">
       <c r="A226" s="10" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="F226" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -9373,12 +9373,12 @@
       </c>
       <c r="E227" s="10" t="inlineStr">
         <is>
-          <t>무향을 원하시면 넣지 / 않아도 됩니다.</t>
+          <t>무향을 원하시면 넣지 · 않아도 됩니다.</t>
         </is>
       </c>
       <c r="F227" s="10" t="inlineStr">
         <is>
-          <t>아로마테라피효과 / 원하는 에센셜오일</t>
+          <t>아로마테라피효과 · 원하는 에센셜오일</t>
         </is>
       </c>
     </row>
@@ -9408,7 +9408,7 @@
           <t>섭씨 2000도의 화산작용이 만든 기능성 미네럴,송이는 제주방언으로 가벼운 돌이라는 뜻, 황토와 참숯의 효과가 하나로!</t>
         </is>
       </c>
-      <c r="F228" s="10" t="n"/>
+      <c r="F228" s="10" t="inlineStr"/>
     </row>
     <row r="229" ht="48" customHeight="1">
       <c r="A229" s="10" t="inlineStr">
@@ -9438,7 +9438,7 @@
       </c>
       <c r="F229" s="10" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -9692,10 +9692,10 @@
       </c>
       <c r="E242" s="20" t="inlineStr">
         <is>
-          <t>맑고 밝은 피부 도움 / (비타민나무 열매, 유자, 오미자 복합)</t>
-        </is>
-      </c>
-      <c r="F242" s="20" t="n"/>
+          <t>맑고 밝은 피부 도움 · (비타민나무 열매, 유자, 오미자 복합)</t>
+        </is>
+      </c>
+      <c r="F242" s="20" t="inlineStr"/>
     </row>
     <row r="243" ht="48" customHeight="1">
       <c r="A243" s="20" t="inlineStr">
@@ -9720,7 +9720,7 @@
       </c>
       <c r="E243" s="20" t="inlineStr">
         <is>
-          <t>천연 다당류 / (귀리, 효모, 버섯류, 해조류) / 피부 보습, 보호막 형성</t>
+          <t>천연 다당류 · (귀리, 효모, 버섯류, 해조류) · 피부 보습, 보호막 형성</t>
         </is>
       </c>
       <c r="F243" s="20" t="inlineStr">
@@ -9789,7 +9789,7 @@
       </c>
       <c r="F245" s="20" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -9949,10 +9949,10 @@
       </c>
       <c r="E254" s="10" t="inlineStr">
         <is>
-          <t>강력한 항산화, / 피부 생기와 윤기, / 수분공급과 보유력증가, / 피부의 장벽 튼튼</t>
-        </is>
-      </c>
-      <c r="F254" s="10" t="n"/>
+          <t>강력한 항산화 · 피부 생기와 윤기 · 수분공급과 보유력증가 · 피부의 장벽 튼튼</t>
+        </is>
+      </c>
+      <c r="F254" s="10" t="inlineStr"/>
     </row>
     <row r="255" ht="48" customHeight="1">
       <c r="A255" s="10" t="inlineStr">
@@ -9977,7 +9977,7 @@
       </c>
       <c r="E255" s="10" t="inlineStr">
         <is>
-          <t>5%, 비타민B3, 식약처 인증 미백원료, / 피부장벽강화, 트러블 완화</t>
+          <t>5%, 비타민B3, 식약처 인증 미백원료 · 피부장벽강화, 트러블 완화</t>
         </is>
       </c>
       <c r="F255" s="10" t="inlineStr">
@@ -10009,12 +10009,12 @@
       </c>
       <c r="E256" s="10" t="inlineStr">
         <is>
-          <t>5가지 콩과 갈근 / 특허 균주를 통한발효로 / 미백, 주름 효능 극대화</t>
+          <t>5가지 콩과 갈근 · 특허 균주를 통한발효로 · 미백, 주름 효능 극대화</t>
         </is>
       </c>
       <c r="F256" s="10" t="inlineStr">
         <is>
-          <t>글루타치온 / 알부틴</t>
+          <t>글루타치온 · 알부틴</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="F257" s="10" t="inlineStr">
         <is>
-          <t>1,2-헥산디올0.6g / (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
+          <t>1,2-헥산디올0.6g · (갈락토미세스 발효여과물의 양을 12.4g로 줄여주세요.)</t>
         </is>
       </c>
     </row>
@@ -10238,7 +10238,7 @@
       </c>
       <c r="E268" s="20" t="inlineStr">
         <is>
-          <t>크기가 다른 11가지 히아루론산 배합. / 피부 속부터 겉까지 수분 채움,</t>
+          <t>크기가 다른 11가지 히아루론산 배합. · 피부 속부터 겉까지 수분 채움</t>
         </is>
       </c>
       <c r="F268" s="20" t="inlineStr">
@@ -10305,7 +10305,7 @@
           <t>피부 내부의 재생 신호를 자극하여 콜라겐 생성을 돕는 메신저 펩타이드</t>
         </is>
       </c>
-      <c r="F270" s="20" t="n"/>
+      <c r="F270" s="20" t="inlineStr"/>
     </row>
     <row r="271" ht="64" customHeight="1">
       <c r="A271" s="20" t="inlineStr">
@@ -10335,7 +10335,7 @@
       </c>
       <c r="F271" s="20" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
       </c>
       <c r="F280" s="10" t="inlineStr">
         <is>
-          <t>피부타입별 워터 / 트러블, 남성-편백 / 민감, 베이비-캐모마일 / 노화-로즈 / 남성-로즈마리</t>
+          <t>피부타입별 워터 · 트러블, 남성-편백 · 민감, 베이비-캐모마일 · 노화-로즈 · 남성-로즈마리</t>
         </is>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
           <t>진정, 병풀, 감초, 녹차, 황금, 로즈마리, 캐모마일, 호장근뿌리 추출물</t>
         </is>
       </c>
-      <c r="F281" s="10" t="n"/>
+      <c r="F281" s="10" t="inlineStr"/>
     </row>
     <row r="282" ht="16" customHeight="1">
       <c r="A282" s="10" t="inlineStr">
@@ -10557,7 +10557,7 @@
           <t>연어DNA, 항염, 재생</t>
         </is>
       </c>
-      <c r="F282" s="10" t="n"/>
+      <c r="F282" s="10" t="inlineStr"/>
     </row>
     <row r="283" ht="48" customHeight="1">
       <c r="A283" s="10" t="inlineStr">
@@ -10587,7 +10587,7 @@
       </c>
       <c r="F283" s="10" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -10614,7 +10614,7 @@
       </c>
       <c r="E284" s="10" t="inlineStr">
         <is>
-          <t>식약처 인증 미백 원료 / 비타민 B3</t>
+          <t>식약처 인증 미백 원료 · 비타민 B3</t>
         </is>
       </c>
       <c r="F284" s="10" t="inlineStr">
@@ -10651,7 +10651,7 @@
       </c>
       <c r="F285" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -10837,7 +10837,7 @@
           <t>사탕수수 채취, 점증제</t>
         </is>
       </c>
-      <c r="F295" s="20" t="n"/>
+      <c r="F295" s="20" t="inlineStr"/>
     </row>
     <row r="296" ht="16" customHeight="1">
       <c r="A296" s="20" t="inlineStr">
@@ -10963,7 +10963,7 @@
       </c>
       <c r="F299" s="20" t="inlineStr">
         <is>
-          <t>세라마이드, / 알란토인분말 사용시 0.2g</t>
+          <t>세라마이드 · 알란토인분말 사용시 0.2g</t>
         </is>
       </c>
     </row>
@@ -10995,7 +10995,7 @@
       </c>
       <c r="F300" s="20" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -11255,7 +11255,7 @@
           <t>미백 효과, 항산화 효과</t>
         </is>
       </c>
-      <c r="F312" s="10" t="n"/>
+      <c r="F312" s="10" t="inlineStr"/>
     </row>
     <row r="313" ht="16" customHeight="1">
       <c r="A313" s="10" t="inlineStr">
@@ -11317,7 +11317,7 @@
       </c>
       <c r="F314" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -11483,10 +11483,10 @@
       </c>
       <c r="E324" s="20" t="inlineStr">
         <is>
-          <t>비타민C의 장점은 살리고 단점은 보완, / 식약처 미백 고시 원료, 미백, 탄력</t>
-        </is>
-      </c>
-      <c r="F324" s="20" t="n"/>
+          <t>비타민C의 장점은 살리고 단점은 보완 · 식약처 미백 고시 원료, 미백, 탄력</t>
+        </is>
+      </c>
+      <c r="F324" s="20" t="inlineStr"/>
     </row>
     <row r="325" ht="32" customHeight="1">
       <c r="A325" s="20" t="inlineStr">
@@ -11580,7 +11580,7 @@
       </c>
       <c r="F327" s="20" t="inlineStr">
         <is>
-          <t>다중)히아루론산, 에코보습제 / 글리세린 등</t>
+          <t>다중)히아루론산, 에코보습제 · 글리세린 등</t>
         </is>
       </c>
     </row>
@@ -11612,7 +11612,7 @@
       </c>
       <c r="F328" s="20" t="inlineStr">
         <is>
-          <t>에코 / 보습제</t>
+          <t>에코 · 보습제</t>
         </is>
       </c>
     </row>
@@ -11639,10 +11639,10 @@
       </c>
       <c r="E329" s="20" t="inlineStr">
         <is>
-          <t>미백 3종 복합 원료 / (비타민나무열매, 유자, 오미자)</t>
-        </is>
-      </c>
-      <c r="F329" s="20" t="n"/>
+          <t>미백 3종 복합 원료 · (비타민나무열매, 유자, 오미자)</t>
+        </is>
+      </c>
+      <c r="F329" s="20" t="inlineStr"/>
     </row>
     <row r="330" ht="32" customHeight="1">
       <c r="A330" s="20" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="F331" s="20" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
@@ -11912,10 +11912,10 @@
       </c>
       <c r="E342" s="10" t="inlineStr">
         <is>
-          <t>노벨상 받은 쑥, / 비타민 풍부, 진정</t>
-        </is>
-      </c>
-      <c r="F342" s="10" t="n"/>
+          <t>노벨상 받은 쑥 · 비타민 풍부, 진정</t>
+        </is>
+      </c>
+      <c r="F342" s="10" t="inlineStr"/>
     </row>
     <row r="343" ht="48" customHeight="1">
       <c r="A343" s="10" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="F343" s="10" t="inlineStr">
         <is>
-          <t>피비다발효용해물, / 사카로미세스발효여과물</t>
+          <t>피비다발효용해물 · 사카로미세스발효여과물</t>
         </is>
       </c>
     </row>
@@ -11972,7 +11972,7 @@
       </c>
       <c r="E344" s="10" t="inlineStr">
         <is>
-          <t>표피~진피 수분 충전 / 고분자+중분자+저분자</t>
+          <t>표피~진피 수분 충전 · 고분자+중분자+저분자</t>
         </is>
       </c>
       <c r="F344" s="10" t="inlineStr">
@@ -12004,10 +12004,10 @@
       </c>
       <c r="E345" s="10" t="inlineStr">
         <is>
-          <t>사탕무우에서 추출하는 / 아미노산계 보습제</t>
-        </is>
-      </c>
-      <c r="F345" s="10" t="n"/>
+          <t>사탕무우에서 추출하는 · 아미노산계 보습제</t>
+        </is>
+      </c>
+      <c r="F345" s="10" t="inlineStr"/>
     </row>
     <row r="346" ht="64" customHeight="1">
       <c r="A346" s="10" t="inlineStr">
@@ -12037,7 +12037,7 @@
       </c>
       <c r="F346" s="10" t="inlineStr">
         <is>
-          <t>천연한방보존제1g / (네롤리워터의 양을 59g으로 늘려주세요.)</t>
+          <t>천연한방보존제1g · (네롤리워터의 양을 59g으로 늘려주세요.)</t>
         </is>
       </c>
     </row>
